--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -567,7 +567,7 @@
         <v>45105</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44735</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>45568</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>45820</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>44216</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44343</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>45533</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45357</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>45224</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45733.64422453703</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>45211</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>45078</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45701.89549768518</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45194</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>44258</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>45078</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44151</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44271.71099537037</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44448</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44679</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>44825.70888888889</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44524</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>44495</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44809.40431712963</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44582</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45181</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>44461</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>45111</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>45372.69723379629</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45005</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45086</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45749.46063657408</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>44985</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45476.50744212963</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>44928</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>45555.65903935185</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45558.62674768519</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>45527.45695601852</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>45754</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45686.57611111111</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>44645</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>45642.60756944444</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45274.32131944445</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45819</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>45282</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>44232</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44082.65943287037</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>44357.34326388889</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>44231</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>44467.6135300926</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44309.65885416666</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44571.63828703704</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>44431</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>44186</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>44715.33956018519</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>44119</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>44811.66311342592</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>44568</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44853.50333333333</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44307.481875</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44622</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>44508.43092592592</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>44272</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>44152</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44271</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44134</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44285.5874537037</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44327.59131944444</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44357</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>44224</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>44245</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44230</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44441</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>44125.62782407407</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44410</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44459</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>44194</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44297</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44510.88893518518</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44809.54884259259</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>44607</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44461</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44461.57160879629</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44721.65634259259</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>44510</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44818</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>44848.3015625</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44125</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>44297</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44258</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44277.6141087963</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44230</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>44635.93181712963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44503.73802083333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44510.63989583333</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44587.59076388889</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44742.95375</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44386.6371412037</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>44592.65864583333</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>44370.39163194445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>44650.495</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44623.46204861111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44714</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44056</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>44847</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44847</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>44084</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>44257.83641203704</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44749</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>44292</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44186</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>44468</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44460</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>44441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44441</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44460</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>44404</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44259</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44110</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44258</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44474</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44880.48260416667</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44861</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44273.62519675926</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44245</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44221</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44140</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44304</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>44482</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>44837.42782407408</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>44315</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>44476</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>44476.58800925926</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44806.68451388889</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44145</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44211</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>44502.34869212963</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>44461.69494212963</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>44267</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>44165</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>44459</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>44137.73322916667</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>44441</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>44515</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>44495.68931712963</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>44169</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44715</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44381</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>44384.39226851852</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>44169</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44130</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>44476</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>44576</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>44229</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44426.34618055556</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>44421</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44295</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44882.66891203704</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44449</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>44882.6740162037</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44888.69445601852</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>44075</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>44322.68579861111</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>44175</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44187.74415509259</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>44825.35965277778</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>44460.62309027778</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44321.51725694445</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44064</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44363</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44147.70520833333</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44203</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44229</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44764</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44817</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44537.63180555555</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44806</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44712.30428240741</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44809.39019675926</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>44165</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44806</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44606</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44820.47135416666</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44565.61417824074</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44810</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>44739.3564699074</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44173</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>44417.77873842593</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44146</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>44186</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44369.93123842592</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44610.3157175926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44265</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44084</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44448.45023148148</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44448</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>44277.60974537037</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44446</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>44357.34568287037</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>44371</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>44127.46831018518</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44420.65103009259</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>44742.71378472223</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>44760.74060185185</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>44246</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>44715.33355324074</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>44732.43689814815</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>44169</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>44469</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>44109</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>44515</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>44069</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>44592.65989583333</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>44187</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>44204</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>44469</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>44530</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>44517</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>44595</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>44237</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44228</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44280</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44295.77248842592</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44550</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>44879.61497685185</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44497.430625</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>44536</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44070</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44810.40475694444</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>44831</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44810.35575231481</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44538.40638888889</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>44384.46910879629</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44588</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>44621.66707175926</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>44495.69234953704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>45730.65008101852</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>45111</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>45181</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>45111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45621</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>44209</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45267.46962962963</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>45643.45525462963</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>45119.58694444445</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>44991.35916666667</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>45742.89054398148</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>44991</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45761</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>44152</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44991.51193287037</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>44991</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>45212</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>44809</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45684.34170138889</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>45684.34384259259</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>45048</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>44152</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45602.91650462963</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>45187.48282407408</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45698</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>45187</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>45055.49951388889</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>44868.56361111111</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>44882</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45188</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45236.35502314815</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44819.34596064815</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44845</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>45735.45677083333</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>45463.39309027778</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45099</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>44862.38081018518</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44078</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>45394.35633101852</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>45334</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>44764</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>45735.46643518518</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>44565.57157407407</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44565</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45602.65810185186</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45169</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45715</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45672.591875</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45247.46569444444</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45620.46207175926</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45724</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45551</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44810.49734953704</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>44235</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>45773.44608796296</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44448</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44883</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44820.47260416667</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45714.84204861111</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45272</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>45723.50291666666</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45723.54547453704</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45713</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45614.50907407407</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45071.55216435185</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45071.55913194444</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45069.48967592593</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45730.63616898148</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45735.66598379629</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45068.45921296296</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45679.48483796296</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>45401.69138888889</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>44903</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>45410</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45103.67451388889</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>44900</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>44867</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45079</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45162</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45170</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45211.63446759259</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>45076.30560185185</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>45077</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44908</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44908</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45730.61275462963</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>44825.46571759259</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44852</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45324.71243055556</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45068.66135416667</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>45744.56912037037</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>45764.52859953704</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45301</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>44565.61265046296</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45089</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21018,7 +21018,7 @@
         <v>45700.66474537037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>45036.6734375</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>45700.69467592592</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45085.93778935185</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45065</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>44886</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44585</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45620.82185185186</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45734.59581018519</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>44126</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>45070</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>45440.4658449074</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44551.38699074074</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45594</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45121.70020833334</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45615.57574074074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45441</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>44809.39893518519</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>45702.6033912037</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>45764.48869212963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45146.71684027778</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>45632.51193287037</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>44928</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>44446</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45366.32900462963</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>44357.34482638889</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45546.84695601852</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>45546.84908564815</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>44421.51063657407</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>45698</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45210</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45054.85400462963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>45510</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22909,7 +22909,7 @@
         <v>44180</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>45775.40460648148</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>44160</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>44424</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45758.73520833333</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>44810.56070601852</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45603</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45300</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45723</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>44810.52567129629</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45748.90723379629</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>44454</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>44129</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45629</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45202.38372685185</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>45301.98247685185</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>44923</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45239</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>44881</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>45181.56171296296</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>45412</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45373.59099537037</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>44846.55085648148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>44895</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44895</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>44895.58759259259</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45763.84802083333</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45061</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>44896.30818287037</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>45561.7159837963</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>45747.78493055556</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45755.48740740741</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>44070</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>44993</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>45197</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>44228</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>45097</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45126</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>44551</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>45119.63947916667</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>44946.42413194444</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45519.55430555555</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>44917</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45709.64976851852</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>45223</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45713</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45713.62074074074</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45099</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>45250.44863425926</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45461</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>44903.53118055555</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45106.89616898148</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45260</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>45546</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>45355.4612037037</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45315.65375</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45317</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>45092.71057870371</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>44160</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>45236</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45112</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>45679.47949074074</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>45359.49635416667</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45686.60939814815</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>44823.61398148148</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45323</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>45339</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>45656.78905092592</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>45103</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>45119.57798611111</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>44466.48996527777</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>44971.69971064815</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27033,7 +27033,7 @@
         <v>45726.51144675926</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>44860.93721064815</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>44361.5662962963</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>45634</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>45610.36342592593</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>45281.62631944445</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>44587.40662037037</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45279</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>44384.39820601852</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         <v>45097</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>44075</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45459.30690972223</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
         <v>45188.49987268518</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>45470</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>45278.88578703703</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>45595.4272337963</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>45307</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45274</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>45065</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>45548.38636574074</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>45610.60157407408</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>45594.62287037037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>45594.6306712963</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>45077.43420138889</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>45265.48799768519</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>44376</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44974</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45747</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45714.80880787037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>45126</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>44924</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>44894.63579861111</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45075.53265046296</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>45635.84936342593</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>45035</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45272.62565972222</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>44061</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>44886.51197916667</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>44850</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45637.54557870371</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45339.66177083334</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>45722.31061342593</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45126</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45639</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>45483</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45483</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45509</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44146</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>45156</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45656.78329861111</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>45183.65436342593</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>45266</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>45223</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>45223</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>45164</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>45614.505625</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>44508</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>45679.49804398148</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45343.92605324074</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45707.64956018519</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>45707.66369212963</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45749.56019675926</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45730.6487037037</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>45441</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>45530</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>44124.48305555555</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44945.34497685185</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>45272</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>45476.50119212963</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45476.50480324074</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>44817</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>45672.58387731481</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45482</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>45483</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45747.79938657407</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31328,7 +31328,7 @@
         <v>44090</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>44523.46746527778</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31442,7 +31442,7 @@
         <v>45530</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31499,7 +31499,7 @@
         <v>45530.69050925926</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>45646</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>45181.58791666666</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>45685.35516203703</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45775.87377314815</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>45629</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>45470</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>45750.94241898148</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>45097</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>45534.67689814815</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>45775.87576388889</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44656.61335648148</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>45463</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>45708.48537037037</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>45777.61497685185</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>45777.73621527778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>45777.72737268519</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>44959</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>44908</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>44435.41690972223</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45782.33971064815</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>44181</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>45572.67497685185</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>44915</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>45357</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32949,7 +32949,7 @@
         <v>45372.68917824074</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45481.49108796296</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33063,7 +33063,7 @@
         <v>45783.67510416666</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33120,7 +33120,7 @@
         <v>45783.7002662037</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>45783.70811342593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>45783.71136574074</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>45784</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>45306</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>45783.71869212963</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45783.7308912037</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>45783.72262731481</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33576,7 +33576,7 @@
         <v>45357</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45161</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>45021</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>45783.73440972222</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>45783.74034722222</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>45784.73925925926</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45784.74020833334</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33975,7 +33975,7 @@
         <v>45137.90618055555</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>44174</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         <v>45708.4921412037</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>44874</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44098</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45646.67438657407</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>45647</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>45647</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>45647</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45567.33017361111</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>45512.53300925926</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>44847.46701388889</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>45567</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>45099</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45754.56905092593</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>45681.62265046296</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34892,7 +34892,7 @@
         <v>44848.30996527777</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34949,7 +34949,7 @@
         <v>45215.7849074074</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35006,7 +35006,7 @@
         <v>45217.3809837963</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>45617.68131944445</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>45628.46613425926</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>45425.69540509259</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>45525</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>45562</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>44160</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44886</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>44144</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>45372.36653935185</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>45359.50059027778</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>45734.55042824074</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45162.32709490741</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>45615.6362037037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>45617.72069444445</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>45181</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>45390</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>45720.3175462963</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>45350.91678240741</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>45350.91932870371</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>45789.70107638889</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45148.62439814815</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>45168.33265046297</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>45727</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>45188.49305555555</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44985</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44985</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45116.79090277778</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>45116.79268518519</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>45370.34275462963</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44937.71841435185</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>45510.89385416666</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>45470</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>45720.31155092592</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>45273</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>45533</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>45561.88243055555</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45593</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45593</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>44942</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>44995.44344907408</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44515</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45126</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45756.29003472222</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45212</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>45510</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>45166.62002314815</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>45614.63012731481</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>45628.56518518519</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>45754.52788194444</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>45524.49138888889</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45527.44498842592</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>44180</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45600</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45349.39254629629</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45079</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>45334</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45372.7019212963</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45145.57798611111</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44670.43472222222</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>44187</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>45246</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45089</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>45792.30664351852</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>45792.32596064815</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>44999.50538194444</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>45792.33170138889</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45629</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>45056.31962962963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38969,7 +38969,7 @@
         <v>45188.61378472222</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>45110</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>45510</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>45610.42850694444</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39197,7 +39197,7 @@
         <v>45637</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39254,7 +39254,7 @@
         <v>45642.57581018518</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>45604.47508101852</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>45167.68207175926</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39425,7 +39425,7 @@
         <v>45837.87837962963</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>45837.90292824074</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>45614.44239583334</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>45837.91177083334</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39653,7 +39653,7 @@
         <v>44104</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>45719</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45084.51329861111</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>45644.02509259259</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>45714.80106481481</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45796.36819444445</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>45796.55706018519</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40062,7 +40062,7 @@
         <v>45614.49559027778</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45796.56827546296</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>45796.60440972223</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>45796.38944444444</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>45216.52173611111</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45596.44083333333</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>44603.63212962963</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>44603</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>44603.6434375</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45594.6255787037</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45345</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>45734.57873842592</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45772.59259259259</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40823,7 +40823,7 @@
         <v>45701.6053125</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40880,7 +40880,7 @@
         <v>45796.38582175926</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>45835.40136574074</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40999,7 +40999,7 @@
         <v>45838.65454861111</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41056,7 +41056,7 @@
         <v>45838.66364583333</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>45837.90488425926</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41170,7 +41170,7 @@
         <v>45071.54651620371</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41227,7 +41227,7 @@
         <v>45071.54908564815</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>44573</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>44582.42422453704</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>45793.67677083334</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>45835.39804398148</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41517,7 +41517,7 @@
         <v>45272</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>45793.56537037037</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>44186</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>45796.56221064815</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45645.40951388889</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>45441</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>45441.54350694444</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41921,7 +41921,7 @@
         <v>45705.65206018519</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>45796.58149305556</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45638</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42097,7 +42097,7 @@
         <v>44988</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>45838.65708333333</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>45596.57131944445</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42268,7 +42268,7 @@
         <v>45610.60369212963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>45205.39787037037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>45205</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45205</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>44945.35765046296</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42573,7 +42573,7 @@
         <v>45567</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>45427</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>45176</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>44181</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45243</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45840.55074074074</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45005</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>44740.92936342592</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45797</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>45739.84453703704</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43153,7 +43153,7 @@
         <v>45272</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>45684.45225694445</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>45226.43175925926</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>45840.5487037037</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43386,7 +43386,7 @@
         <v>45798.50189814815</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43443,7 +43443,7 @@
         <v>45183.65034722222</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43500,7 +43500,7 @@
         <v>45082</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43557,7 +43557,7 @@
         <v>45610</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43619,7 +43619,7 @@
         <v>44946.62486111111</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>44927.74953703704</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>45747.39516203704</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43800,7 +43800,7 @@
         <v>45769.33756944445</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>44642.83407407408</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>45628.48590277778</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45686.54246527778</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45842.62019675926</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>45842.62362268518</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>44634.60929398148</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45271</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45615.57407407407</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45617.49510416666</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45667.4771412037</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45628.43445601852</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45084.67444444444</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>44634</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44598,7 +44598,7 @@
         <v>45156</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
         <v>45026</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44712,7 +44712,7 @@
         <v>45645.58603009259</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
         <v>45069.64322916666</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>45842.45201388889</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>44617</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>44959.68709490741</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>45799.40628472222</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>44923</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>44923.65486111111</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>45562.55799768519</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45230,7 +45230,7 @@
         <v>45730.61458333334</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>44266</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>45610.59956018518</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>45614.50349537037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>45677.37925925926</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45520,7 +45520,7 @@
         <v>44959</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>44251</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>44140</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45696,7 +45696,7 @@
         <v>45841.57072916667</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45753,7 +45753,7 @@
         <v>45301.83475694444</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45810,7 +45810,7 @@
         <v>45628.44303240741</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45867,7 +45867,7 @@
         <v>45205</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45924,7 +45924,7 @@
         <v>45240.67206018518</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45981,7 +45981,7 @@
         <v>45748.86240740741</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46038,7 +46038,7 @@
         <v>45358</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46095,7 +46095,7 @@
         <v>45754.38893518518</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46152,7 +46152,7 @@
         <v>45845.48228009259</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46209,7 +46209,7 @@
         <v>45179</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45621</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>45618.61243055556</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>45610.61537037037</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>45845</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46494,7 +46494,7 @@
         <v>45803.59722222222</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
         <v>45804.66229166667</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>45804</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46665,7 +46665,7 @@
         <v>45845.48898148148</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46722,7 +46722,7 @@
         <v>45845</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>45594.61994212963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46836,7 +46836,7 @@
         <v>44721.70876157407</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46893,7 +46893,7 @@
         <v>45775.58704861111</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>44851.61237268519</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>45804.6612962963</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>45701.58163194444</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47126,7 +47126,7 @@
         <v>45253</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47188,7 +47188,7 @@
         <v>45701.60341435186</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>45805.27778935185</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47307,7 +47307,7 @@
         <v>45805.31606481481</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47364,7 +47364,7 @@
         <v>45686.60648148148</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>45686.63332175926</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>44634</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>45847</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>44928.45686342593</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>44894.45888888889</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>45231</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47763,7 +47763,7 @@
         <v>45701.90762731482</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47820,7 +47820,7 @@
         <v>45700.51605324074</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>44628.47715277778</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47934,7 +47934,7 @@
         <v>45020</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>45593</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45684.34594907407</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48115,7 +48115,7 @@
         <v>45805.27396990741</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>45012</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48234,7 +48234,7 @@
         <v>45805.27659722222</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>45602</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>45446</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>45103</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48467,7 +48467,7 @@
         <v>45848.61030092592</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48524,7 +48524,7 @@
         <v>45847.3721412037</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>45749.56623842593</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48638,7 +48638,7 @@
         <v>45847.67871527778</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48695,7 +48695,7 @@
         <v>45181</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48752,7 +48752,7 @@
         <v>45323</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>44851.60855324074</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>45236.68318287037</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>45246.77350694445</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48990,7 +48990,7 @@
         <v>45152</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49047,7 +49047,7 @@
         <v>45195.85546296297</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49104,7 +49104,7 @@
         <v>45131</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49161,7 +49161,7 @@
         <v>45741.47434027777</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49218,7 +49218,7 @@
         <v>45645.58436342593</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>45145.58085648148</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49332,7 +49332,7 @@
         <v>45163.37561342592</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49389,7 +49389,7 @@
         <v>44706</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49446,7 +49446,7 @@
         <v>45483</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45188.4716550926</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49560,7 +49560,7 @@
         <v>45509.66609953704</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49622,7 +49622,7 @@
         <v>45848.6062962963</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>44999.50461805556</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45715.5681712963</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49793,7 +49793,7 @@
         <v>45126</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45371.85761574074</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>44802</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49964,7 +49964,7 @@
         <v>45645.58762731482</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50021,7 +50021,7 @@
         <v>44743.61965277778</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50078,7 +50078,7 @@
         <v>45847.67734953704</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         <v>45187.59305555555</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50192,7 +50192,7 @@
         <v>45632.31087962963</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50249,7 +50249,7 @@
         <v>44750</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>45581.49583333333</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50363,7 +50363,7 @@
         <v>45672.46096064815</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50420,7 +50420,7 @@
         <v>45225.49447916666</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>45707.66030092593</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50534,7 +50534,7 @@
         <v>45630.32984953704</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50591,7 +50591,7 @@
         <v>45131</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50648,7 +50648,7 @@
         <v>45812.59082175926</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50705,7 +50705,7 @@
         <v>45301.98100694444</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50762,7 +50762,7 @@
         <v>45207.49881944444</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>45811.48709490741</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50876,7 +50876,7 @@
         <v>45756.29621527778</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50933,7 +50933,7 @@
         <v>45811.39115740741</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>45811.39695601852</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51047,7 +51047,7 @@
         <v>45811.40674768519</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51104,7 +51104,7 @@
         <v>45811</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51161,7 +51161,7 @@
         <v>45811.55042824074</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51218,7 +51218,7 @@
         <v>45811.56310185185</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51275,7 +51275,7 @@
         <v>45811.56517361111</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51332,7 +51332,7 @@
         <v>45852.75837962963</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>45231</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51446,7 +51446,7 @@
         <v>45811.48321759259</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45811.4892824074</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51560,7 +51560,7 @@
         <v>45811.57001157408</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51617,7 +51617,7 @@
         <v>45152.37778935185</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51674,7 +51674,7 @@
         <v>45656.73612268519</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51731,7 +51731,7 @@
         <v>45852.33880787037</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51788,7 +51788,7 @@
         <v>45005</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51845,7 +51845,7 @@
         <v>45274.57935185185</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51902,7 +51902,7 @@
         <v>45264.68074074074</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51959,7 +51959,7 @@
         <v>45735.46112268518</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52016,7 +52016,7 @@
         <v>45748.59457175926</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52073,7 +52073,7 @@
         <v>45119</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52130,7 +52130,7 @@
         <v>44825.46825231481</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52187,7 +52187,7 @@
         <v>45754.57372685185</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>45647</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52301,7 +52301,7 @@
         <v>45475</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45315.65311342593</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>45713</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52477,7 +52477,7 @@
         <v>45686.51583333333</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52534,7 +52534,7 @@
         <v>45617.54989583333</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52591,7 +52591,7 @@
         <v>45817.39481481481</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52648,7 +52648,7 @@
         <v>45818.66649305556</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52705,7 +52705,7 @@
         <v>45712</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52762,7 +52762,7 @@
         <v>45280</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52824,7 +52824,7 @@
         <v>45817.39133101852</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52881,7 +52881,7 @@
         <v>45215.48378472222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52938,7 +52938,7 @@
         <v>45775.59978009259</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52995,7 +52995,7 @@
         <v>45775.60414351852</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53052,7 +53052,7 @@
         <v>45818</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53109,7 +53109,7 @@
         <v>45328</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53166,7 +53166,7 @@
         <v>45204.32359953703</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53223,7 +53223,7 @@
         <v>45762.60217592592</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53280,7 +53280,7 @@
         <v>45817</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>45225.63777777777</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53394,7 +53394,7 @@
         <v>45518</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53451,7 +53451,7 @@
         <v>45818.66446759259</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53508,7 +53508,7 @@
         <v>44980.62431712963</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53565,7 +53565,7 @@
         <v>45257.57825231482</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53622,7 +53622,7 @@
         <v>45301.98575231482</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53679,7 +53679,7 @@
         <v>45162.588125</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53736,7 +53736,7 @@
         <v>45820</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53798,7 +53798,7 @@
         <v>45224.59289351852</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53855,7 +53855,7 @@
         <v>44988.85038194444</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53912,7 +53912,7 @@
         <v>45860</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53969,7 +53969,7 @@
         <v>45727.34787037037</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>45510.89869212963</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54083,7 +54083,7 @@
         <v>45715.56667824074</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>45196</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54197,7 +54197,7 @@
         <v>45748.91101851852</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54254,7 +54254,7 @@
         <v>45676.57688657408</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54311,7 +54311,7 @@
         <v>45824.61681712963</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54368,7 +54368,7 @@
         <v>45356.68585648148</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54425,7 +54425,7 @@
         <v>45218.86829861111</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>45824.61572916667</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54539,7 +54539,7 @@
         <v>45747.78081018518</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54596,7 +54596,7 @@
         <v>45824.55555555555</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>44272</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54710,7 +54710,7 @@
         <v>44330.36730324074</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54767,7 +54767,7 @@
         <v>45195.85668981481</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54824,7 +54824,7 @@
         <v>45701.59954861111</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54881,7 +54881,7 @@
         <v>44908</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54943,7 +54943,7 @@
         <v>44858.63208333333</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55000,7 +55000,7 @@
         <v>45188</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55057,7 +55057,7 @@
         <v>45742.61196759259</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55114,7 +55114,7 @@
         <v>45224.70244212963</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55171,7 +55171,7 @@
         <v>45646.67726851852</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55228,7 +55228,7 @@
         <v>45647</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55285,7 +55285,7 @@
         <v>45647</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55342,7 +55342,7 @@
         <v>45647</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55399,7 +55399,7 @@
         <v>45647</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55456,7 +55456,7 @@
         <v>45035</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55513,7 +55513,7 @@
         <v>45826.41267361111</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55570,7 +55570,7 @@
         <v>44852.89560185185</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55627,7 +55627,7 @@
         <v>45099.91826388889</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55684,7 +55684,7 @@
         <v>45826</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55741,7 +55741,7 @@
         <v>45705.5654050926</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55798,7 +55798,7 @@
         <v>45712.57320601852</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55855,7 +55855,7 @@
         <v>45742.36822916667</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>45280</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55969,7 +55969,7 @@
         <v>45825.65555555555</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56026,7 +56026,7 @@
         <v>44820</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56083,7 +56083,7 @@
         <v>45747.39719907408</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56145,7 +56145,7 @@
         <v>45628.49322916667</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56202,7 +56202,7 @@
         <v>45826.47586805555</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56259,7 +56259,7 @@
         <v>44380</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56316,7 +56316,7 @@
         <v>45188.62355324074</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56373,7 +56373,7 @@
         <v>45826</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56430,7 +56430,7 @@
         <v>45869</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56492,7 +56492,7 @@
         <v>45869</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56554,7 +56554,7 @@
         <v>44712.32885416667</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56611,7 +56611,7 @@
         <v>45033</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56668,7 +56668,7 @@
         <v>45211.63712962963</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56725,7 +56725,7 @@
         <v>45793.65984953703</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56782,7 +56782,7 @@
         <v>45869</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56844,7 +56844,7 @@
         <v>45483</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56901,7 +56901,7 @@
         <v>45749.53158564815</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56958,7 +56958,7 @@
         <v>45869</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>45168.33028935185</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57077,7 +57077,7 @@
         <v>44377</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57134,7 +57134,7 @@
         <v>45831.3783912037</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57191,7 +57191,7 @@
         <v>45831.57793981482</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57248,7 +57248,7 @@
         <v>45714.80385416667</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57305,7 +57305,7 @@
         <v>45831.3978587963</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57362,7 +57362,7 @@
         <v>45279</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57419,7 +57419,7 @@
         <v>45264.68416666667</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57476,7 +57476,7 @@
         <v>45012</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57533,7 +57533,7 @@
         <v>44991.53373842593</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57590,7 +57590,7 @@
         <v>45762</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57647,7 +57647,7 @@
         <v>45099</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57704,7 +57704,7 @@
         <v>45831</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57761,7 +57761,7 @@
         <v>45832.28081018518</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57818,7 +57818,7 @@
         <v>45672.78414351852</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57875,7 +57875,7 @@
         <v>45831.36892361111</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57932,7 +57932,7 @@
         <v>45831.35077546296</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57989,7 +57989,7 @@
         <v>45831.34712962963</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58046,7 +58046,7 @@
         <v>45831</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58103,7 +58103,7 @@
         <v>45831.36045138889</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58160,7 +58160,7 @@
         <v>45394.73528935185</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58217,7 +58217,7 @@
         <v>45831.56630787037</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58274,7 +58274,7 @@
         <v>45833.74201388889</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58331,7 +58331,7 @@
         <v>45833.73708333333</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58388,7 +58388,7 @@
         <v>45876.62177083334</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58445,7 +58445,7 @@
         <v>45875.45658564815</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58502,7 +58502,7 @@
         <v>45225.63304398148</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58559,7 +58559,7 @@
         <v>45875.6449537037</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58616,7 +58616,7 @@
         <v>44337.48540509259</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58673,7 +58673,7 @@
         <v>45604.54047453704</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58730,7 +58730,7 @@
         <v>45874.65034722222</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58787,7 +58787,7 @@
         <v>44380</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58844,7 +58844,7 @@
         <v>45875.64696759259</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58901,7 +58901,7 @@
         <v>45734.93418981481</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58958,7 +58958,7 @@
         <v>45769.36023148148</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59015,7 +59015,7 @@
         <v>45733.60265046296</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59072,7 +59072,7 @@
         <v>44651</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59129,7 +59129,7 @@
         <v>45275.30907407407</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59186,7 +59186,7 @@
         <v>44573</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59248,7 +59248,7 @@
         <v>44620.45334490741</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59305,7 +59305,7 @@
         <v>45567.37547453704</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59362,7 +59362,7 @@
         <v>44887</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59419,7 +59419,7 @@
         <v>44938</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59476,7 +59476,7 @@
         <v>44441</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59533,7 +59533,7 @@
         <v>44974.57127314815</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59590,7 +59590,7 @@
         <v>44959.62519675926</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59652,7 +59652,7 @@
         <v>44959</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59709,7 +59709,7 @@
         <v>44959</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59766,7 +59766,7 @@
         <v>44812</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59823,7 +59823,7 @@
         <v>44810</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59880,7 +59880,7 @@
         <v>45188</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59937,7 +59937,7 @@
         <v>45162.65574074074</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59999,7 +59999,7 @@
         <v>44924.66556712963</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60056,7 +60056,7 @@
         <v>44158</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60118,7 +60118,7 @@
         <v>44657</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60175,7 +60175,7 @@
         <v>45758.72209490741</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60232,7 +60232,7 @@
         <v>45758.73298611111</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>45218.47658564815</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60346,7 +60346,7 @@
         <v>44151</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60403,7 +60403,7 @@
         <v>45260.32738425926</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60460,7 +60460,7 @@
         <v>44806.59946759259</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60517,7 +60517,7 @@
         <v>45191.55503472222</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60574,7 +60574,7 @@
         <v>45593</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60636,7 +60636,7 @@
         <v>44742.71030092592</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60693,7 +60693,7 @@
         <v>45359.50601851852</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60750,7 +60750,7 @@
         <v>45012</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         <v>45356.68475694444</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60864,7 +60864,7 @@
         <v>44487</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60921,7 +60921,7 @@
         <v>45562.53543981481</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -60983,7 +60983,7 @@
         <v>45546.85369212963</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61045,7 +61045,7 @@
         <v>45109</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61102,7 +61102,7 @@
         <v>45604.4971412037</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61159,7 +61159,7 @@
         <v>45593</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61221,7 +61221,7 @@
         <v>44260</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61278,7 +61278,7 @@
         <v>45226.44923611111</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61335,7 +61335,7 @@
         <v>45645</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61392,7 +61392,7 @@
         <v>45568.46310185185</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61449,7 +61449,7 @@
         <v>45097</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61506,7 +61506,7 @@
         <v>45097</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61563,7 +61563,7 @@
         <v>45764.48725694444</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -61620,7 +61620,7 @@
         <v>45081</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -61677,7 +61677,7 @@
         <v>44060</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -61734,7 +61734,7 @@
         <v>45093</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61791,7 +61791,7 @@
         <v>45305.57791666667</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61848,7 +61848,7 @@
         <v>45607.36863425926</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61905,7 +61905,7 @@
         <v>45097</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -61962,7 +61962,7 @@
         <v>45033</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62019,7 +62019,7 @@
         <v>45470.64299768519</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62076,7 +62076,7 @@
         <v>45470.64894675926</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62133,7 +62133,7 @@
         <v>44281</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62195,7 +62195,7 @@
         <v>45733.43582175926</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62252,7 +62252,7 @@
         <v>45733.44309027777</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62309,7 +62309,7 @@
         <v>45733.57615740741</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62366,7 +62366,7 @@
         <v>45747.39269675926</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62428,7 +62428,7 @@
         <v>45747.39408564815</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62490,7 +62490,7 @@
         <v>45726.54469907407</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62547,7 +62547,7 @@
         <v>45121.35078703704</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -62604,7 +62604,7 @@
         <v>44985</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -62661,7 +62661,7 @@
         <v>45757.94755787037</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -62718,7 +62718,7 @@
         <v>45349</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62775,7 +62775,7 @@
         <v>44978.59528935186</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62832,7 +62832,7 @@
         <v>44960.36971064815</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62889,7 +62889,7 @@
         <v>45396.86226851852</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -62946,7 +62946,7 @@
         <v>44712</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63003,7 +63003,7 @@
         <v>44929</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63060,7 +63060,7 @@
         <v>45281.63481481482</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63117,7 +63117,7 @@
         <v>45639.58114583333</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63174,7 +63174,7 @@
         <v>45686.3184375</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63231,7 +63231,7 @@
         <v>45253.54356481481</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -63288,7 +63288,7 @@
         <v>45754.52563657407</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -63345,7 +63345,7 @@
         <v>45754.52998842593</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -63402,7 +63402,7 @@
         <v>44881</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -63459,7 +63459,7 @@
         <v>45275</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -63521,7 +63521,7 @@
         <v>44991.34855324074</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -63578,7 +63578,7 @@
         <v>44971.45475694445</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -63635,7 +63635,7 @@
         <v>45594.62881944444</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -567,7 +567,7 @@
         <v>45105</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44735</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>45568</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>45820</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>44216</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44343</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>45533</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45357</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>45224</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45733.64422453703</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>45211</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>45078</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45701.89549768518</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45194</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>44258</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>45078</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44151</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44271.71099537037</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44448</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44679</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>44825.70888888889</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44524</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>44495</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44809.40431712963</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44582</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45181</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>44461</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>45111</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>45372.69723379629</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45005</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45086</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45749.46063657408</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>44985</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45476.50744212963</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>44928</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>45555.65903935185</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45558.62674768519</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>45527.45695601852</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>45754</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45686.57611111111</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>44645</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>45642.60756944444</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45274.32131944445</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45819</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>45282</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>44232</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44082.65943287037</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>44357.34326388889</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>44231</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>44467.6135300926</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44309.65885416666</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44571.63828703704</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>44431</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>44186</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>44715.33956018519</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>44119</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>44811.66311342592</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>44568</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44853.50333333333</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44307.481875</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44622</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>44508.43092592592</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>44272</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>44152</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44271</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44134</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44285.5874537037</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44327.59131944444</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44357</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>44224</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>44245</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44230</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44441</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>44125.62782407407</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44410</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44459</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>44194</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44297</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44510.88893518518</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44809.54884259259</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>44607</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44461</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44461.57160879629</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44721.65634259259</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>44510</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44818</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>44848.3015625</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44125</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>44297</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44258</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44277.6141087963</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44230</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>44635.93181712963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44503.73802083333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44510.63989583333</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44587.59076388889</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44742.95375</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44386.6371412037</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>44592.65864583333</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>44370.39163194445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>44650.495</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44623.46204861111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44714</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44056</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>44847</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44847</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>44084</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>44257.83641203704</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44749</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>44292</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44186</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>44468</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44460</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>44441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44441</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44460</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>44404</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44259</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44110</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44258</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44474</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44880.48260416667</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44861</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44273.62519675926</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44245</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44221</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44140</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44304</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>44482</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>44837.42782407408</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>44315</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>44476</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>44476.58800925926</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44806.68451388889</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44145</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44211</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>44502.34869212963</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>44461.69494212963</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>44267</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>44165</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>44459</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>44137.73322916667</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>44441</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>44515</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>44495.68931712963</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>44169</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44715</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44381</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>44384.39226851852</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>44169</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44130</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>44476</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>44576</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>44229</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44426.34618055556</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>44421</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44295</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44882.66891203704</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44449</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>44882.6740162037</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44888.69445601852</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>44075</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>44322.68579861111</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>44175</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44187.74415509259</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>44825.35965277778</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>44460.62309027778</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44321.51725694445</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44064</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44363</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44147.70520833333</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44203</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44229</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44764</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44817</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44537.63180555555</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44806</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44712.30428240741</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44809.39019675926</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>44165</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44806</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44606</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44820.47135416666</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44565.61417824074</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44810</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>44739.3564699074</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44173</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>44417.77873842593</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44146</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>44186</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44369.93123842592</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44610.3157175926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44265</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44084</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44448.45023148148</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44448</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>44277.60974537037</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44446</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>44357.34568287037</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>44371</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>44127.46831018518</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44420.65103009259</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>44742.71378472223</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>44760.74060185185</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>44246</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>44715.33355324074</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>44732.43689814815</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>44169</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>44469</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>44109</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>44515</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>44069</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>44592.65989583333</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>44187</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>44204</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>44469</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>44530</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>44517</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>44595</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>44237</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44228</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44280</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44295.77248842592</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44550</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>44879.61497685185</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44497.430625</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>44536</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44070</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44810.40475694444</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>44831</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44810.35575231481</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44538.40638888889</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>44384.46910879629</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44588</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>44621.66707175926</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>44495.69234953704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>45730.65008101852</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>45111</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>45181</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>45111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45621</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>44209</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45267.46962962963</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>45643.45525462963</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>45119.58694444445</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>44991.35916666667</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>45742.89054398148</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>44991</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45761</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>44152</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44991.51193287037</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>44991</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>45212</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>44809</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45684.34170138889</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>45684.34384259259</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>45048</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>44152</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45602.91650462963</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>45187.48282407408</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45698</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>45187</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>45055.49951388889</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>44868.56361111111</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>44882</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45188</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45236.35502314815</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44819.34596064815</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44845</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>45735.45677083333</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>45463.39309027778</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45099</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>44862.38081018518</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44078</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>45394.35633101852</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>45334</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>44764</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>45735.46643518518</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>44565.57157407407</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44565</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45602.65810185186</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45169</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45715</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45672.591875</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45247.46569444444</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45620.46207175926</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45724</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45551</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44810.49734953704</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>44235</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>45773.44608796296</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44448</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44883</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44820.47260416667</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45714.84204861111</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45272</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>45723.50291666666</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45723.54547453704</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45713</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45614.50907407407</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45071.55216435185</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45071.55913194444</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45069.48967592593</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45730.63616898148</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45735.66598379629</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45068.45921296296</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45679.48483796296</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>45401.69138888889</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>44903</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>45410</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45103.67451388889</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>44900</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>44867</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45079</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45162</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45170</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45211.63446759259</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>45076.30560185185</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>45077</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44908</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44908</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45730.61275462963</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>44825.46571759259</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44852</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45324.71243055556</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45068.66135416667</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>45744.56912037037</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>45764.52859953704</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45301</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>44565.61265046296</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45089</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21018,7 +21018,7 @@
         <v>45700.66474537037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>45036.6734375</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>45700.69467592592</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45085.93778935185</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45065</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>44886</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44585</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45620.82185185186</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45734.59581018519</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>44126</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>45070</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>45440.4658449074</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44551.38699074074</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45594</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45121.70020833334</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45615.57574074074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45441</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>44809.39893518519</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>45702.6033912037</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>45764.48869212963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45146.71684027778</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>45632.51193287037</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>44928</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>44446</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45366.32900462963</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>44357.34482638889</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45546.84695601852</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>45546.84908564815</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>44421.51063657407</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>45698</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45210</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45054.85400462963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>45510</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22909,7 +22909,7 @@
         <v>44180</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>45775.40460648148</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>44160</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>44424</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45758.73520833333</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>44810.56070601852</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45603</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45300</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45723</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>44810.52567129629</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45748.90723379629</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>44454</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>44129</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45629</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45202.38372685185</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>45301.98247685185</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>44923</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45239</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>44881</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>45181.56171296296</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>45412</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45373.59099537037</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>44846.55085648148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>44895</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44895</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>44895.58759259259</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45763.84802083333</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45061</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>44896.30818287037</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>45561.7159837963</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>45747.78493055556</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45755.48740740741</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>44070</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>44993</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>45197</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>44228</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>45097</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45126</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>44551</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>45119.63947916667</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>44946.42413194444</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45519.55430555555</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>44917</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45709.64976851852</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>45223</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45713</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45713.62074074074</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45099</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>45250.44863425926</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45461</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>44903.53118055555</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45106.89616898148</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45260</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>45546</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>45355.4612037037</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45315.65375</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45317</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>45092.71057870371</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>44160</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>45236</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45112</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>45679.47949074074</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>45359.49635416667</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45686.60939814815</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>44823.61398148148</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45323</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>45339</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>45656.78905092592</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>45103</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>45119.57798611111</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>44466.48996527777</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>44971.69971064815</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27033,7 +27033,7 @@
         <v>45726.51144675926</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>44860.93721064815</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>44361.5662962963</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>45634</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>45610.36342592593</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>45281.62631944445</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>44587.40662037037</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45279</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>44384.39820601852</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         <v>45097</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>44075</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45459.30690972223</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
         <v>45188.49987268518</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>45470</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>45278.88578703703</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>45595.4272337963</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>45307</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45274</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>45065</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>45548.38636574074</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>45610.60157407408</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>45594.62287037037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>45594.6306712963</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>45077.43420138889</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>45265.48799768519</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>44376</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44974</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45747</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45714.80880787037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>45126</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>44924</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>44894.63579861111</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45075.53265046296</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>45635.84936342593</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>45035</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45272.62565972222</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>44061</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>44886.51197916667</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>44850</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45637.54557870371</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45339.66177083334</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>45722.31061342593</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45126</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45639</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>45483</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45483</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45509</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44146</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>45156</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45656.78329861111</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>45183.65436342593</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>45266</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>45223</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>45223</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>45164</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>45614.505625</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>44508</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>45679.49804398148</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45343.92605324074</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45707.64956018519</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>45707.66369212963</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45749.56019675926</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45730.6487037037</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>45441</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>45530</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>44124.48305555555</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44945.34497685185</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>45272</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>45476.50119212963</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45476.50480324074</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>44817</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>45672.58387731481</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45482</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>45483</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45747.79938657407</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31328,7 +31328,7 @@
         <v>44090</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>44523.46746527778</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31442,7 +31442,7 @@
         <v>45530</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31499,7 +31499,7 @@
         <v>45530.69050925926</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>45646</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>45181.58791666666</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>45685.35516203703</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45775.87377314815</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>45629</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>45470</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>45750.94241898148</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>45097</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>45534.67689814815</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>45775.87576388889</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44656.61335648148</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>45463</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>45708.48537037037</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>45777.61497685185</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>45777.73621527778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>45777.72737268519</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>44959</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>44908</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>44435.41690972223</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45782.33971064815</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>44181</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>45572.67497685185</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>44915</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>45357</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32949,7 +32949,7 @@
         <v>45372.68917824074</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45481.49108796296</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33063,7 +33063,7 @@
         <v>45783.67510416666</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33120,7 +33120,7 @@
         <v>45783.7002662037</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>45783.70811342593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>45783.71136574074</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>45784</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>45306</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>45783.71869212963</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45783.7308912037</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>45783.72262731481</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33576,7 +33576,7 @@
         <v>45357</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45161</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>45021</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>45783.73440972222</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>45783.74034722222</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>45784.73925925926</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45784.74020833334</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33975,7 +33975,7 @@
         <v>45137.90618055555</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>44174</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         <v>45708.4921412037</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>44874</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44098</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45646.67438657407</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>45647</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>45647</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>45647</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45567.33017361111</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>45512.53300925926</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>44847.46701388889</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>45567</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>45099</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45754.56905092593</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>45681.62265046296</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34892,7 +34892,7 @@
         <v>44848.30996527777</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34949,7 +34949,7 @@
         <v>45215.7849074074</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35006,7 +35006,7 @@
         <v>45217.3809837963</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>45617.68131944445</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>45628.46613425926</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>45425.69540509259</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>45525</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>45562</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>44160</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44886</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>44144</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>45372.36653935185</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>45359.50059027778</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>45734.55042824074</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45162.32709490741</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>45615.6362037037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>45617.72069444445</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>45181</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>45390</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>45720.3175462963</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>45350.91678240741</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>45350.91932870371</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>45789.70107638889</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45148.62439814815</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>45168.33265046297</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>45727</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>45188.49305555555</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44985</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44985</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45116.79090277778</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>45116.79268518519</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>45370.34275462963</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44937.71841435185</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>45510.89385416666</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>45470</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>45720.31155092592</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>45273</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>45533</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>45561.88243055555</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45593</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45593</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>44942</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>44995.44344907408</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44515</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45126</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45756.29003472222</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45212</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>45510</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>45166.62002314815</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>45614.63012731481</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>45628.56518518519</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>45754.52788194444</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>45524.49138888889</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45527.44498842592</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>44180</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45600</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45349.39254629629</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45079</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>45334</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45372.7019212963</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45145.57798611111</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44670.43472222222</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>44187</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>45246</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45089</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>45792.30664351852</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>45792.32596064815</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>44999.50538194444</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>45792.33170138889</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45629</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>45056.31962962963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38969,7 +38969,7 @@
         <v>45188.61378472222</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>45110</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>45510</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>45610.42850694444</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39197,7 +39197,7 @@
         <v>45637</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39254,7 +39254,7 @@
         <v>45642.57581018518</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>45604.47508101852</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>45167.68207175926</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39425,7 +39425,7 @@
         <v>45837.87837962963</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>45837.90292824074</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>45614.44239583334</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>45837.91177083334</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39653,7 +39653,7 @@
         <v>44104</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>45719</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45084.51329861111</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>45644.02509259259</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>45714.80106481481</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45796.36819444445</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>45796.55706018519</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40062,7 +40062,7 @@
         <v>45614.49559027778</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45796.56827546296</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>45796.60440972223</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>45796.38944444444</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>45216.52173611111</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45596.44083333333</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>44603.63212962963</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>44603</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>44603.6434375</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45594.6255787037</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45345</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>45734.57873842592</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45772.59259259259</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40823,7 +40823,7 @@
         <v>45701.6053125</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40880,7 +40880,7 @@
         <v>45796.38582175926</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>45835.40136574074</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40999,7 +40999,7 @@
         <v>45838.65454861111</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41056,7 +41056,7 @@
         <v>45838.66364583333</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>45837.90488425926</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41170,7 +41170,7 @@
         <v>45071.54651620371</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41227,7 +41227,7 @@
         <v>45071.54908564815</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>44573</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>44582.42422453704</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>45793.67677083334</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>45835.39804398148</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41517,7 +41517,7 @@
         <v>45272</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>45793.56537037037</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>44186</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>45796.56221064815</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45645.40951388889</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>45441</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>45441.54350694444</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41921,7 +41921,7 @@
         <v>45705.65206018519</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>45796.58149305556</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45638</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42097,7 +42097,7 @@
         <v>44988</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>45838.65708333333</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>45596.57131944445</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42268,7 +42268,7 @@
         <v>45610.60369212963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>45205.39787037037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>45205</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45205</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>44945.35765046296</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42573,7 +42573,7 @@
         <v>45567</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>45427</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>45176</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>44181</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45243</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45840.55074074074</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45005</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>44740.92936342592</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45797</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>45739.84453703704</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43153,7 +43153,7 @@
         <v>45272</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>45684.45225694445</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>45226.43175925926</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>45840.5487037037</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43386,7 +43386,7 @@
         <v>45798.50189814815</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43443,7 +43443,7 @@
         <v>45183.65034722222</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43500,7 +43500,7 @@
         <v>45082</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43557,7 +43557,7 @@
         <v>45610</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43619,7 +43619,7 @@
         <v>44946.62486111111</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>44927.74953703704</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>45747.39516203704</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43800,7 +43800,7 @@
         <v>45769.33756944445</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>44642.83407407408</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>45628.48590277778</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45686.54246527778</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45842.62019675926</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>45842.62362268518</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>44634.60929398148</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45271</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45615.57407407407</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45617.49510416666</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45667.4771412037</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45628.43445601852</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45084.67444444444</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>44634</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44598,7 +44598,7 @@
         <v>45156</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
         <v>45026</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44712,7 +44712,7 @@
         <v>45645.58603009259</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
         <v>45069.64322916666</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>45842.45201388889</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>44617</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>44959.68709490741</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>45799.40628472222</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>44923</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>44923.65486111111</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>45562.55799768519</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45230,7 +45230,7 @@
         <v>45730.61458333334</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>44266</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>45610.59956018518</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>45614.50349537037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>45677.37925925926</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45520,7 +45520,7 @@
         <v>44959</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>44251</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>44140</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45696,7 +45696,7 @@
         <v>45841.57072916667</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45753,7 +45753,7 @@
         <v>45301.83475694444</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45810,7 +45810,7 @@
         <v>45628.44303240741</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45867,7 +45867,7 @@
         <v>45205</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45924,7 +45924,7 @@
         <v>45240.67206018518</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45981,7 +45981,7 @@
         <v>45748.86240740741</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46038,7 +46038,7 @@
         <v>45358</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46095,7 +46095,7 @@
         <v>45754.38893518518</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46152,7 +46152,7 @@
         <v>45845.48228009259</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46209,7 +46209,7 @@
         <v>45179</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45621</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>45618.61243055556</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>45610.61537037037</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>45845</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46494,7 +46494,7 @@
         <v>45803.59722222222</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
         <v>45804.66229166667</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>45804</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46665,7 +46665,7 @@
         <v>45845.48898148148</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46722,7 +46722,7 @@
         <v>45845</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>45594.61994212963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46836,7 +46836,7 @@
         <v>44721.70876157407</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46893,7 +46893,7 @@
         <v>45775.58704861111</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>44851.61237268519</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>45804.6612962963</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>45701.58163194444</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47126,7 +47126,7 @@
         <v>45253</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47188,7 +47188,7 @@
         <v>45701.60341435186</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>45805.27778935185</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47307,7 +47307,7 @@
         <v>45805.31606481481</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47364,7 +47364,7 @@
         <v>45686.60648148148</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>45686.63332175926</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>44634</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>45847</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>44928.45686342593</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>44894.45888888889</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>45231</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47763,7 +47763,7 @@
         <v>45701.90762731482</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47820,7 +47820,7 @@
         <v>45700.51605324074</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>44628.47715277778</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47934,7 +47934,7 @@
         <v>45020</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>45593</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45684.34594907407</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48115,7 +48115,7 @@
         <v>45805.27396990741</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>45012</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48234,7 +48234,7 @@
         <v>45805.27659722222</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>45602</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>45446</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>45103</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48467,7 +48467,7 @@
         <v>45848.61030092592</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48524,7 +48524,7 @@
         <v>45847.3721412037</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>45749.56623842593</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48638,7 +48638,7 @@
         <v>45847.67871527778</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48695,7 +48695,7 @@
         <v>45181</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48752,7 +48752,7 @@
         <v>45323</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>44851.60855324074</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>45236.68318287037</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>45246.77350694445</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48990,7 +48990,7 @@
         <v>45152</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49047,7 +49047,7 @@
         <v>45195.85546296297</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49104,7 +49104,7 @@
         <v>45131</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49161,7 +49161,7 @@
         <v>45741.47434027777</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49218,7 +49218,7 @@
         <v>45645.58436342593</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>45145.58085648148</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49332,7 +49332,7 @@
         <v>45163.37561342592</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49389,7 +49389,7 @@
         <v>44706</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49446,7 +49446,7 @@
         <v>45483</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45188.4716550926</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49560,7 +49560,7 @@
         <v>45509.66609953704</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49622,7 +49622,7 @@
         <v>45848.6062962963</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>44999.50461805556</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45715.5681712963</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49793,7 +49793,7 @@
         <v>45126</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45371.85761574074</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>44802</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49964,7 +49964,7 @@
         <v>45645.58762731482</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50021,7 +50021,7 @@
         <v>44743.61965277778</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50078,7 +50078,7 @@
         <v>45847.67734953704</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         <v>45187.59305555555</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50192,7 +50192,7 @@
         <v>45632.31087962963</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50249,7 +50249,7 @@
         <v>44750</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>45581.49583333333</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50363,7 +50363,7 @@
         <v>45672.46096064815</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50420,7 +50420,7 @@
         <v>45225.49447916666</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>45707.66030092593</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50534,7 +50534,7 @@
         <v>45630.32984953704</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50591,7 +50591,7 @@
         <v>45131</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50648,7 +50648,7 @@
         <v>45812.59082175926</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50705,7 +50705,7 @@
         <v>45301.98100694444</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50762,7 +50762,7 @@
         <v>45207.49881944444</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>45811.48709490741</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50876,7 +50876,7 @@
         <v>45756.29621527778</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50933,7 +50933,7 @@
         <v>45811.39115740741</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>45811.39695601852</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51047,7 +51047,7 @@
         <v>45811.40674768519</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51104,7 +51104,7 @@
         <v>45811</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51161,7 +51161,7 @@
         <v>45811.55042824074</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51218,7 +51218,7 @@
         <v>45811.56310185185</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51275,7 +51275,7 @@
         <v>45811.56517361111</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51332,7 +51332,7 @@
         <v>45852.75837962963</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>45231</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51446,7 +51446,7 @@
         <v>45811.48321759259</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45811.4892824074</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51560,7 +51560,7 @@
         <v>45811.57001157408</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51617,7 +51617,7 @@
         <v>45152.37778935185</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51674,7 +51674,7 @@
         <v>45656.73612268519</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51731,7 +51731,7 @@
         <v>45852.33880787037</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51788,7 +51788,7 @@
         <v>45005</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51845,7 +51845,7 @@
         <v>45274.57935185185</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51902,7 +51902,7 @@
         <v>45264.68074074074</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51959,7 +51959,7 @@
         <v>45735.46112268518</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52016,7 +52016,7 @@
         <v>45748.59457175926</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52073,7 +52073,7 @@
         <v>45119</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52130,7 +52130,7 @@
         <v>44825.46825231481</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52187,7 +52187,7 @@
         <v>45754.57372685185</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>45647</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52301,7 +52301,7 @@
         <v>45475</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45315.65311342593</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>45713</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52477,7 +52477,7 @@
         <v>45686.51583333333</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52534,7 +52534,7 @@
         <v>45617.54989583333</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52591,7 +52591,7 @@
         <v>45817.39481481481</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52648,7 +52648,7 @@
         <v>45818.66649305556</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52705,7 +52705,7 @@
         <v>45712</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52762,7 +52762,7 @@
         <v>45280</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52824,7 +52824,7 @@
         <v>45817.39133101852</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52881,7 +52881,7 @@
         <v>45215.48378472222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52938,7 +52938,7 @@
         <v>45775.59978009259</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52995,7 +52995,7 @@
         <v>45775.60414351852</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53052,7 +53052,7 @@
         <v>45818</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53109,7 +53109,7 @@
         <v>45328</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53166,7 +53166,7 @@
         <v>45204.32359953703</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53223,7 +53223,7 @@
         <v>45762.60217592592</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53280,7 +53280,7 @@
         <v>45817</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>45225.63777777777</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53394,7 +53394,7 @@
         <v>45518</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53451,7 +53451,7 @@
         <v>45818.66446759259</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53508,7 +53508,7 @@
         <v>44980.62431712963</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53565,7 +53565,7 @@
         <v>45257.57825231482</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53622,7 +53622,7 @@
         <v>45301.98575231482</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53679,7 +53679,7 @@
         <v>45162.588125</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53736,7 +53736,7 @@
         <v>45820</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53798,7 +53798,7 @@
         <v>45224.59289351852</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53855,7 +53855,7 @@
         <v>44988.85038194444</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53912,7 +53912,7 @@
         <v>45860</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53969,7 +53969,7 @@
         <v>45727.34787037037</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>45510.89869212963</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54083,7 +54083,7 @@
         <v>45715.56667824074</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>45196</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54197,7 +54197,7 @@
         <v>45748.91101851852</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54254,7 +54254,7 @@
         <v>45676.57688657408</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54311,7 +54311,7 @@
         <v>45824.61681712963</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54368,7 +54368,7 @@
         <v>45356.68585648148</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54425,7 +54425,7 @@
         <v>45218.86829861111</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>45824.61572916667</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54539,7 +54539,7 @@
         <v>45747.78081018518</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54596,7 +54596,7 @@
         <v>45824.55555555555</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>44272</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54710,7 +54710,7 @@
         <v>44330.36730324074</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54767,7 +54767,7 @@
         <v>45195.85668981481</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54824,7 +54824,7 @@
         <v>45701.59954861111</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54881,7 +54881,7 @@
         <v>44908</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54943,7 +54943,7 @@
         <v>44858.63208333333</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55000,7 +55000,7 @@
         <v>45188</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55057,7 +55057,7 @@
         <v>45742.61196759259</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55114,7 +55114,7 @@
         <v>45224.70244212963</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55171,7 +55171,7 @@
         <v>45646.67726851852</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55228,7 +55228,7 @@
         <v>45647</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55285,7 +55285,7 @@
         <v>45647</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55342,7 +55342,7 @@
         <v>45647</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55399,7 +55399,7 @@
         <v>45647</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55456,7 +55456,7 @@
         <v>45035</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55513,7 +55513,7 @@
         <v>45826.41267361111</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55570,7 +55570,7 @@
         <v>44852.89560185185</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55627,7 +55627,7 @@
         <v>45099.91826388889</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55684,7 +55684,7 @@
         <v>45826</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55741,7 +55741,7 @@
         <v>45705.5654050926</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55798,7 +55798,7 @@
         <v>45712.57320601852</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55855,7 +55855,7 @@
         <v>45742.36822916667</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>45280</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55969,7 +55969,7 @@
         <v>45825.65555555555</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56026,7 +56026,7 @@
         <v>44820</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56083,7 +56083,7 @@
         <v>45747.39719907408</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56145,7 +56145,7 @@
         <v>45628.49322916667</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56202,7 +56202,7 @@
         <v>45826.47586805555</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56259,7 +56259,7 @@
         <v>44380</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56316,7 +56316,7 @@
         <v>45188.62355324074</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56373,7 +56373,7 @@
         <v>45826</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56430,7 +56430,7 @@
         <v>45869</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56492,7 +56492,7 @@
         <v>45869</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56554,7 +56554,7 @@
         <v>44712.32885416667</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56611,7 +56611,7 @@
         <v>45033</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56668,7 +56668,7 @@
         <v>45211.63712962963</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56725,7 +56725,7 @@
         <v>45793.65984953703</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56782,7 +56782,7 @@
         <v>45869</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56844,7 +56844,7 @@
         <v>45483</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56901,7 +56901,7 @@
         <v>45749.53158564815</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56958,7 +56958,7 @@
         <v>45869</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>45168.33028935185</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57077,7 +57077,7 @@
         <v>44377</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57134,7 +57134,7 @@
         <v>45831.3783912037</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57191,7 +57191,7 @@
         <v>45831.57793981482</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57248,7 +57248,7 @@
         <v>45714.80385416667</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57305,7 +57305,7 @@
         <v>45831.3978587963</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57362,7 +57362,7 @@
         <v>45279</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57419,7 +57419,7 @@
         <v>45264.68416666667</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57476,7 +57476,7 @@
         <v>45012</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57533,7 +57533,7 @@
         <v>44991.53373842593</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57590,7 +57590,7 @@
         <v>45762</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57647,7 +57647,7 @@
         <v>45099</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57704,7 +57704,7 @@
         <v>45831</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57761,7 +57761,7 @@
         <v>45832.28081018518</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57818,7 +57818,7 @@
         <v>45672.78414351852</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57875,7 +57875,7 @@
         <v>45831.36892361111</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57932,7 +57932,7 @@
         <v>45831.35077546296</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57989,7 +57989,7 @@
         <v>45831.34712962963</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58046,7 +58046,7 @@
         <v>45831</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58103,7 +58103,7 @@
         <v>45831.36045138889</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58160,7 +58160,7 @@
         <v>45394.73528935185</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58217,7 +58217,7 @@
         <v>45831.56630787037</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58274,7 +58274,7 @@
         <v>45833.74201388889</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58331,7 +58331,7 @@
         <v>45833.73708333333</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58388,7 +58388,7 @@
         <v>45876.62177083334</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58445,7 +58445,7 @@
         <v>45875.45658564815</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58502,7 +58502,7 @@
         <v>45225.63304398148</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58559,7 +58559,7 @@
         <v>45875.6449537037</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58616,7 +58616,7 @@
         <v>44337.48540509259</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58673,7 +58673,7 @@
         <v>45604.54047453704</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58730,7 +58730,7 @@
         <v>45874.65034722222</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58787,7 +58787,7 @@
         <v>44380</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58844,7 +58844,7 @@
         <v>45875.64696759259</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58901,7 +58901,7 @@
         <v>45734.93418981481</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58958,7 +58958,7 @@
         <v>45769.36023148148</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59015,7 +59015,7 @@
         <v>45733.60265046296</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59072,7 +59072,7 @@
         <v>44651</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59129,7 +59129,7 @@
         <v>45275.30907407407</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59186,7 +59186,7 @@
         <v>44573</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59248,7 +59248,7 @@
         <v>44620.45334490741</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59305,7 +59305,7 @@
         <v>45567.37547453704</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59362,7 +59362,7 @@
         <v>44887</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59419,7 +59419,7 @@
         <v>44938</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59476,7 +59476,7 @@
         <v>44441</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59533,7 +59533,7 @@
         <v>44974.57127314815</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59590,7 +59590,7 @@
         <v>44959.62519675926</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59652,7 +59652,7 @@
         <v>44959</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59709,7 +59709,7 @@
         <v>44959</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59766,7 +59766,7 @@
         <v>44812</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59823,7 +59823,7 @@
         <v>44810</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59880,7 +59880,7 @@
         <v>45188</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59937,7 +59937,7 @@
         <v>45162.65574074074</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59999,7 +59999,7 @@
         <v>44924.66556712963</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60056,7 +60056,7 @@
         <v>44158</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60118,7 +60118,7 @@
         <v>44657</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60175,7 +60175,7 @@
         <v>45758.72209490741</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60232,7 +60232,7 @@
         <v>45758.73298611111</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>45218.47658564815</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60346,7 +60346,7 @@
         <v>44151</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60403,7 +60403,7 @@
         <v>45260.32738425926</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60460,7 +60460,7 @@
         <v>44806.59946759259</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60517,7 +60517,7 @@
         <v>45191.55503472222</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60574,7 +60574,7 @@
         <v>45593</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60636,7 +60636,7 @@
         <v>44742.71030092592</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60693,7 +60693,7 @@
         <v>45359.50601851852</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60750,7 +60750,7 @@
         <v>45012</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         <v>45356.68475694444</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60864,7 +60864,7 @@
         <v>44487</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60921,7 +60921,7 @@
         <v>45562.53543981481</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -60983,7 +60983,7 @@
         <v>45546.85369212963</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61045,7 +61045,7 @@
         <v>45109</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61102,7 +61102,7 @@
         <v>45604.4971412037</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61159,7 +61159,7 @@
         <v>45593</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61221,7 +61221,7 @@
         <v>44260</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61278,7 +61278,7 @@
         <v>45226.44923611111</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61335,7 +61335,7 @@
         <v>45645</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61392,7 +61392,7 @@
         <v>45568.46310185185</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61449,7 +61449,7 @@
         <v>45097</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61506,7 +61506,7 @@
         <v>45097</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61563,7 +61563,7 @@
         <v>45764.48725694444</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -61620,7 +61620,7 @@
         <v>45081</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -61677,7 +61677,7 @@
         <v>44060</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -61734,7 +61734,7 @@
         <v>45093</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61791,7 +61791,7 @@
         <v>45305.57791666667</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61848,7 +61848,7 @@
         <v>45607.36863425926</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61905,7 +61905,7 @@
         <v>45097</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -61962,7 +61962,7 @@
         <v>45033</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62019,7 +62019,7 @@
         <v>45470.64299768519</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62076,7 +62076,7 @@
         <v>45470.64894675926</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62133,7 +62133,7 @@
         <v>44281</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62195,7 +62195,7 @@
         <v>45733.43582175926</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62252,7 +62252,7 @@
         <v>45733.44309027777</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62309,7 +62309,7 @@
         <v>45733.57615740741</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62366,7 +62366,7 @@
         <v>45747.39269675926</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62428,7 +62428,7 @@
         <v>45747.39408564815</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62490,7 +62490,7 @@
         <v>45726.54469907407</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62547,7 +62547,7 @@
         <v>45121.35078703704</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -62604,7 +62604,7 @@
         <v>44985</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -62661,7 +62661,7 @@
         <v>45757.94755787037</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -62718,7 +62718,7 @@
         <v>45349</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62775,7 +62775,7 @@
         <v>44978.59528935186</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62832,7 +62832,7 @@
         <v>44960.36971064815</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62889,7 +62889,7 @@
         <v>45396.86226851852</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -62946,7 +62946,7 @@
         <v>44712</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63003,7 +63003,7 @@
         <v>44929</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63060,7 +63060,7 @@
         <v>45281.63481481482</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63117,7 +63117,7 @@
         <v>45639.58114583333</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63174,7 +63174,7 @@
         <v>45686.3184375</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63231,7 +63231,7 @@
         <v>45253.54356481481</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -63288,7 +63288,7 @@
         <v>45754.52563657407</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -63345,7 +63345,7 @@
         <v>45754.52998842593</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -63402,7 +63402,7 @@
         <v>44881</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -63459,7 +63459,7 @@
         <v>45275</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -63521,7 +63521,7 @@
         <v>44991.34855324074</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -63578,7 +63578,7 @@
         <v>44971.45475694445</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -63635,7 +63635,7 @@
         <v>45594.62881944444</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -567,7 +567,7 @@
         <v>45105</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44735</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>45568</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>45820</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>44216</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44343</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>45533</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45733.64422453703</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>44610</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45211</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44258</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45078</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45357</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45194</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>45224</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>45078</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>45701.89549768518</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44151</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44271.71099537037</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44448</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44679</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>44825.70888888889</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44524</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>44495</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44809.40431712963</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44582</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45372.69723379629</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45558.62674768519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>45527.45695601852</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>45686.57611111111</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>45642.60756944444</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44985</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>45476.50744212963</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45819</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>44928</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45555.65903935185</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>45754</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44645</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>45274.32131944445</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>45282</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44232</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45181</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>44461</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>45005</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45111</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>45086</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>45749.46063657408</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44082.65943287037</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>44357.34326388889</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>44231</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>44467.6135300926</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44309.65885416666</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44571.63828703704</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>44186</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>44431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>44811.66311342592</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>44715.33956018519</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>44568</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>44119</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44853.50333333333</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44307.481875</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44622</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>44508.43092592592</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>44272</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>44152</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44271</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44134</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44285.5874537037</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44327.59131944444</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44357</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>44224</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>44245</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44230</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44441</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>44410</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44125.62782407407</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44459</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>44194</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44297</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44510.88893518518</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44809.54884259259</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>44721.65634259259</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44461</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44461.57160879629</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44607</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>44510</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44818</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>44125</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44848.3015625</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>44297</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44258</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44230</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44277.6141087963</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>44635.93181712963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44503.73802083333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44510.63989583333</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44386.6371412037</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44587.59076388889</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44742.95375</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>44592.65864583333</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>44370.39163194445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>44623.46204861111</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44650.495</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44714</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44847</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>44847</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44084</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>44257.83641203704</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>44292</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44749</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>44186</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44468</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>44460</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44441</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>44441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44404</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>44258</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44460</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44110</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44474</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44880.48260416667</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44837.42782407408</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44861</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44273.62519675926</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44245</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44221</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44140</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44304</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>44482</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>44315</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>44476</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>44476.58800925926</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>44145</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44806.68451388889</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44211</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44502.34869212963</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>44461.69494212963</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>44267</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>44165</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>44137.73322916667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>44459</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>44441</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>44515</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>44495.68931712963</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>44169</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>44715</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44384.39226851852</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44381</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>44476</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>44169</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44130</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>44576</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>44229</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>44426.34618055556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44888.69445601852</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>44322.68579861111</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44175</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44825.35965277778</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44187.74415509259</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>44460.62309027778</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44363</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>44064</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>44321.51725694445</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>44147.70520833333</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44764</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>44203</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>44229</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44806</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44165</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44817</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44712.30428240741</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44537.63180555555</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44809.39019675926</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44806</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44565.61417824074</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44739.3564699074</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44606</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44820.47135416666</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44146</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>44369.93123842592</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44810</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44186</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44173</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44417.77873842593</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44610.3157175926</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>44265</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44448.45023148148</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>44448</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44084</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>44277.60974537037</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44446</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44357.34568287037</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44371</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44420.65103009259</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44127.46831018518</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44742.71378472223</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>44760.74060185185</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44246</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>44715.33355324074</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>44732.43689814815</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>44169</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44469</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>44515</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>44592.65989583333</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>44109</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>44187</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>44069</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>44469</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>44517</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>44595</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44530</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>44204</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>44237</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>44228</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44550</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>44280</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>44295.77248842592</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>44879.61497685185</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>44536</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>44810.40475694444</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44070</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44810.35575231481</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44538.40638888889</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44831</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>44497.430625</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44588</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>44384.46910879629</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44295</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44882.66891203704</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>44152</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44621.66707175926</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44495.69234953704</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>44845</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44449</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>44882.6740162037</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>44862.38081018518</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>44209</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>44075</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>44152</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>44421</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>44991.51193287037</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>44991</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>44809</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>45684.34170138889</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>45684.34384259259</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>45048</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>44900</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>44867</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45187.48282407408</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45187</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44819.34596064815</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>45735.45677083333</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>44974</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>44908</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44908</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45126</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>44924</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>44825.46571759259</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>45334</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>44764</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>45324.71243055556</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>45164</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45715</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>45035</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45272.62565972222</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44061</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>45089</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45247.46569444444</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>45085.93778935185</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45734.59581018519</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>44508</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>45440.4658449074</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45724</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45679.49804398148</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>45707.64956018519</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45707.66369212963</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45126</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45441</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45749.56019675926</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45730.6487037037</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45441</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>45702.6033912037</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45183.65436342593</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45223</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>45223</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>45764.48869212963</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>44235</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44928</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45773.44608796296</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45614.505625</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>44446</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>44357.34482638889</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>45343.92605324074</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45272</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>45723.50291666666</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45723.54547453704</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>44424</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45272</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45747.79938657407</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45713</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>44810.56070601852</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45646</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45300</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45181.58791666666</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45069.48967592593</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>44810.52567129629</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>45685.35516203703</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>45775.87377314815</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>45239</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45629</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45373.59099537037</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44895</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44895</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44895.58759259259</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45534.67689814815</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45775.87576388889</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44090</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45708.48537037037</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>45777.61497685185</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20309,7 +20309,7 @@
         <v>45777.73621527778</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45777.72737268519</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>44959</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45470</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>45750.94241898148</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45097</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>45061</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>45782.33971064815</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>44181</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45463</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>45572.67497685185</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>45372.68917824074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45481.49108796296</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45783.67510416666</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>45783.7002662037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>45783.70811342593</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>45783.71136574074</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45783.71869212963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45783.7308912037</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45783.72262731481</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45161</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>45021</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45306</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45783.73440972222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>45783.74034722222</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>45784.74020833334</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>45708.4921412037</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45512.53300925926</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>44847.46701388889</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>45567</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22034,7 +22034,7 @@
         <v>45681.62265046296</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>45099</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>45628.46613425926</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45754.56905092593</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>44848.30996527777</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>45372.36653935185</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>45734.55042824074</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>45425.69540509259</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45720.3175462963</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45789.70107638889</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45162.32709490741</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>45615.6362037037</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>45617.72069444445</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>45181</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45510.89385416666</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>45390</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>45720.31155092592</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>45148.62439814815</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>45168.33265046297</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>45727</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>45188.49305555555</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>44985</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>44985</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>45756.29003472222</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>45116.79090277778</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>45116.79268518519</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45166.62002314815</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>45628.56518518519</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>45370.34275462963</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>44937.71841435185</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45470</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45273</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45533</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>45561.88243055555</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>45792.30664351852</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>45792.32596064815</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45593</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>45593</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45792.33170138889</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>45510</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>44995.44344907408</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>44515</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>44070</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>45614.63012731481</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45754.52788194444</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45524.49138888889</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45527.44498842592</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>45600</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45349.39254629629</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45796.36819444445</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45796.55706018519</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45079</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45796.56827546296</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>45796.60440972223</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>45334</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>45796.38944444444</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>45197</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45596.44083333333</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>45734.57873842592</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>45796.38582175926</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>45089</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>44999.50538194444</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45629</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>45056.31962962963</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>45793.67677083334</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>45188.61378472222</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>45126</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>44551</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45119.63947916667</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>45272</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>45793.56537037037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>44186</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45796.56221064815</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>45610.42850694444</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>45637</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>45642.57581018518</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>45796.58149305556</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>45604.47508101852</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>45596.57131944445</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>45719</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>45084.51329861111</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>45644.02509259259</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26773,7 +26773,7 @@
         <v>45797</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>45714.80106481481</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>44946.42413194444</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45798.50189814815</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45614.49559027778</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>44927.74953703704</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>45216.52173611111</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44603.63212962963</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>44603</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>44603.6434375</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>45594.6255787037</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>45345</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>45701.6053125</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>45156</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45645.58603009259</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>45799.40628472222</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44582.42422453704</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>45562.55799768519</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>44251</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>44140</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>45748.86240740741</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         <v>45645.40951388889</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28042,7 +28042,7 @@
         <v>45845.48228009259</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>45638</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>44988</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>45845</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>45803.59722222222</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45804.66229166667</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>45804</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45845.48898148148</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45845</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45610.60369212963</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45427</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>45176</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>45804.6612962963</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>45253</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>45805.27778935185</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>45684.45225694445</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>45805.31606481481</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         <v>45461</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>45183.65034722222</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>45847</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45082</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29259,7 +29259,7 @@
         <v>45805.27396990741</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>45317</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>45610</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45805.27659722222</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>44160</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>45747.39516203704</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>45848.61030092592</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>45847.3721412037</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         <v>45236</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29792,7 +29792,7 @@
         <v>45112</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>45769.33756944445</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>44642.83407407408</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>45359.49635416667</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45749.56623842593</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>44823.61398148148</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>45847.67871527778</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>45628.48590277778</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45686.54246527778</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>45323</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>44634.60929398148</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>45615.57407407407</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>45617.49510416666</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>45667.4771412037</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>45628.43445601852</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>45119.57798611111</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44860.93721064815</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44384.39820601852</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45097</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>45069.64322916666</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44617</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>44075</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>45459.30690972223</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>45470</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>45278.88578703703</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>45848.6062962963</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         <v>45677.37925925926</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>45205</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>45371.85761574074</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>45265.48799768519</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31517,7 +31517,7 @@
         <v>45240.67206018518</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>45358</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45754.38893518518</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>44894.63579861111</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>45179</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>44886.51197916667</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>44850</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>44721.70876157407</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>45339.66177083334</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>45847.67734953704</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32087,7 +32087,7 @@
         <v>45775.58704861111</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32144,7 +32144,7 @@
         <v>45483</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>45483</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>45509</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>44146</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>45266</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>44851.61237268519</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45701.58163194444</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>45701.60341435186</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32610,7 +32610,7 @@
         <v>45686.60648148148</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>45686.63332175926</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32724,7 +32724,7 @@
         <v>45701.90762731482</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>45700.51605324074</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>45530</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>44124.48305555555</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>44628.47715277778</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>44945.34497685185</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33066,7 +33066,7 @@
         <v>45812.59082175926</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>45811.48709490741</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45476.50119212963</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>45476.50480324074</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>45811.39115740741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>45811.39695601852</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>45811.40674768519</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>45811</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45811.55042824074</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45811.56310185185</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>45446</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>45103</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45811.56517361111</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>45852.75837962963</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>45811.48321759259</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>45811.4892824074</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33978,7 +33978,7 @@
         <v>45181</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>45811.57001157408</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34092,7 +34092,7 @@
         <v>44817</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34149,7 +34149,7 @@
         <v>44851.60855324074</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34211,7 +34211,7 @@
         <v>45672.58387731481</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>45236.68318287037</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>45246.77350694445</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>45482</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>45483</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>45195.85546296297</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>45852.33880787037</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34610,7 +34610,7 @@
         <v>44523.46746527778</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34667,7 +34667,7 @@
         <v>45741.47434027777</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45530</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>45530.69050925926</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>45163.37561342592</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34895,7 +34895,7 @@
         <v>44706</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>44656.61335648148</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45188.4716550926</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>45686.51583333333</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35123,7 +35123,7 @@
         <v>45617.54989583333</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35180,7 +35180,7 @@
         <v>45817.39481481481</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
         <v>44908</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>44435.41690972223</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>45818.66649305556</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45715.5681712963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>45126</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>45817.39133101852</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>45818</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>44915</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>45357</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>45762.60217592592</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>45817</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>45518</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45357</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45818.66446759259</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>45187.59305555555</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36102,7 +36102,7 @@
         <v>44750</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
         <v>45581.49583333333</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>45137.90618055555</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>44174</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>44874</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>44098</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45646.67438657407</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45647</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45647</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>45647</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45225.49447916666</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>45707.66030092593</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>45820</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>45131</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>45301.98100694444</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45207.49881944444</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45860</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37081,7 +37081,7 @@
         <v>45756.29621527778</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>45231</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45676.57688657408</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>45274.57935185185</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>45264.68074074074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>45567.33017361111</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>45824.61681712963</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>45824.61572916667</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45735.46112268518</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45748.59457175926</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>45824.55555555555</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44825.46825231481</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>45826.41267361111</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>45826</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>45215.7849074074</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>45825.65555555555</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>45754.57372685185</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>45217.3809837963</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45617.68131944445</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38164,7 +38164,7 @@
         <v>45826.47586805555</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45525</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45475</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45562</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45315.65311342593</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38449,7 +38449,7 @@
         <v>44160</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>44886</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45713</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>45826</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>44144</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>45869</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>45869</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45359.50059027778</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45712</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45280</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45215.48378472222</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>45211.63712962963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>45775.59978009259</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>45775.60414351852</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45328</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45793.65984953703</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>45869</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45350.91678240741</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>45350.91932870371</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45869</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>45831.3783912037</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45831.57793981482</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>45831.3978587963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45225.63777777777</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45257.57825231482</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39909,7 +39909,7 @@
         <v>45301.98575231482</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>45162.588125</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
         <v>45831</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>45832.28081018518</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45831.36892361111</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40194,7 +40194,7 @@
         <v>45831.35077546296</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45831.34712962963</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>45831</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40365,7 +40365,7 @@
         <v>44988.85038194444</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40422,7 +40422,7 @@
         <v>44942</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>45831.36045138889</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40536,7 +40536,7 @@
         <v>45715.56667824074</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>45196</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>45748.91101851852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>45831.56630787037</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>45126</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40821,7 +40821,7 @@
         <v>45356.68585648148</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>45833.74201388889</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45833.73708333333</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45218.86829861111</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45212</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45195.85668981481</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45510</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>44908</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>44858.63208333333</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45875.45658564815</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41396,7 +41396,7 @@
         <v>44180</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>45875.6449537037</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41510,7 +41510,7 @@
         <v>44852.89560185185</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>45099.91826388889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41624,7 +41624,7 @@
         <v>45874.65034722222</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41681,7 +41681,7 @@
         <v>45875.64696759259</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>45880.86574074074</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>45876.62177083334</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>45712.57320601852</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>45742.36822916667</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41966,7 +41966,7 @@
         <v>45280</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>45372.7019212963</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45145.57798611111</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
         <v>44670.43472222222</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42194,7 +42194,7 @@
         <v>45279</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42251,7 +42251,7 @@
         <v>44187</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>45838.65454861111</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>45264.68416666667</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42422,7 +42422,7 @@
         <v>45838.66364583333</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42479,7 +42479,7 @@
         <v>45835.40136574074</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42536,7 +42536,7 @@
         <v>45246</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>45099</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>45880.56395833333</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42707,7 +42707,7 @@
         <v>45672.78414351852</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>45838.65708333333</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42821,7 +42821,7 @@
         <v>45877.42953703704</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>45837.87837962963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>45837.90488425926</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>45835.39804398148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45784</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>45394.73528935185</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>45840.55074074074</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45110</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43277,7 +43277,7 @@
         <v>45840.5487037037</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>45881</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43391,7 +43391,7 @@
         <v>45167.68207175926</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43448,7 +43448,7 @@
         <v>45614.44239583334</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43505,7 +43505,7 @@
         <v>45881.31761574074</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43562,7 +43562,7 @@
         <v>44104</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43619,7 +43619,7 @@
         <v>45837.90292824074</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
         <v>45837.91177083334</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>45881.66684027778</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>45880</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>45225.63304398148</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43904,7 +43904,7 @@
         <v>45884.62045138889</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>44337.48540509259</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44018,7 +44018,7 @@
         <v>45604.54047453704</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45772.59259259259</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44132,7 +44132,7 @@
         <v>44380</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44189,7 +44189,7 @@
         <v>45842.62019675926</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44246,7 +44246,7 @@
         <v>45842.62362268518</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44303,7 +44303,7 @@
         <v>45071.54651620371</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45071.54908564815</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44417,7 +44417,7 @@
         <v>44573</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>45841.57072916667</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>45734.93418981481</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44593,7 +44593,7 @@
         <v>45884.73457175926</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45769.36023148148</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44707,7 +44707,7 @@
         <v>45842.45201388889</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>45733.60265046296</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>44651</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>45441</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>45441.54350694444</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>45275.30907407407</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45049,7 +45049,7 @@
         <v>45705.65206018519</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>45205.39787037037</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>45205</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45240,7 +45240,7 @@
         <v>45205</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45297,7 +45297,7 @@
         <v>44945.35765046296</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45354,7 +45354,7 @@
         <v>44573</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45416,7 +45416,7 @@
         <v>45567</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>44181</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>45243</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45587,7 +45587,7 @@
         <v>45005</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>44740.92936342592</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45701,7 +45701,7 @@
         <v>44620.45334490741</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>45739.84453703704</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45815,7 +45815,7 @@
         <v>45272</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>45226.43175925926</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45929,7 +45929,7 @@
         <v>45567.37547453704</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         <v>44887</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>44938</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46100,7 +46100,7 @@
         <v>44441</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46157,7 +46157,7 @@
         <v>44946.62486111111</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46219,7 +46219,7 @@
         <v>44974.57127314815</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>44959.62519675926</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>44959</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>44959</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45271</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>44812</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>45084.67444444444</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>44810</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>44634</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46737,7 +46737,7 @@
         <v>45026</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>44959.68709490741</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>44923</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46908,7 +46908,7 @@
         <v>44923.65486111111</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46965,7 +46965,7 @@
         <v>45730.61458333334</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47022,7 +47022,7 @@
         <v>44266</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45610.59956018518</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>45614.50349537037</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>44959</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>45301.83475694444</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47312,7 +47312,7 @@
         <v>45628.44303240741</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>45188</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47426,7 +47426,7 @@
         <v>45162.65574074074</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>44924.66556712963</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47545,7 +47545,7 @@
         <v>45621</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>45618.61243055556</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>45610.61537037037</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>44158</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47778,7 +47778,7 @@
         <v>45594.61994212963</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47835,7 +47835,7 @@
         <v>44657</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47892,7 +47892,7 @@
         <v>44634</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47949,7 +47949,7 @@
         <v>44928.45686342593</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48006,7 +48006,7 @@
         <v>44894.45888888889</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>45231</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>45758.72209490741</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>45758.73298611111</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48234,7 +48234,7 @@
         <v>45218.47658564815</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48291,7 +48291,7 @@
         <v>44151</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>45020</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>45593</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>45260.32738425926</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>45684.34594907407</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>44806.59946759259</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48643,7 +48643,7 @@
         <v>45012</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>45602</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48757,7 +48757,7 @@
         <v>45191.55503472222</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>45593</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>44742.71030092592</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>45323</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48995,7 +48995,7 @@
         <v>45359.50601851852</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49052,7 +49052,7 @@
         <v>45152</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49109,7 +49109,7 @@
         <v>45131</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>45012</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49223,7 +49223,7 @@
         <v>45645.58436342593</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49280,7 +49280,7 @@
         <v>45356.68475694444</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
         <v>44487</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>45562.53543981481</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49456,7 +49456,7 @@
         <v>45145.58085648148</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49513,7 +49513,7 @@
         <v>45546.85369212963</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49575,7 +49575,7 @@
         <v>45109</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49632,7 +49632,7 @@
         <v>45604.4971412037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>45593</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49751,7 +49751,7 @@
         <v>45483</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>44260</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>45226.44923611111</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>45509.66609953704</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>44999.50461805556</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>45645</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>45568.46310185185</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>44802</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45645.58762731482</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50269,7 +50269,7 @@
         <v>44743.61965277778</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>45097</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50383,7 +50383,7 @@
         <v>45097</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50440,7 +50440,7 @@
         <v>45632.31087962963</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50497,7 +50497,7 @@
         <v>45764.48725694444</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>45081</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50611,7 +50611,7 @@
         <v>44060</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50668,7 +50668,7 @@
         <v>45093</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50725,7 +50725,7 @@
         <v>45672.46096064815</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50782,7 +50782,7 @@
         <v>45630.32984953704</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50839,7 +50839,7 @@
         <v>45305.57791666667</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50896,7 +50896,7 @@
         <v>45607.36863425926</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50953,7 +50953,7 @@
         <v>45097</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51010,7 +51010,7 @@
         <v>45033</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51067,7 +51067,7 @@
         <v>45470.64299768519</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51124,7 +51124,7 @@
         <v>45470.64894675926</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51181,7 +51181,7 @@
         <v>45152.37778935185</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45656.73612268519</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51295,7 +51295,7 @@
         <v>44281</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>45005</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51414,7 +51414,7 @@
         <v>45733.43582175926</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51471,7 +51471,7 @@
         <v>45733.44309027777</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51528,7 +51528,7 @@
         <v>45733.57615740741</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51585,7 +51585,7 @@
         <v>45747.39269675926</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51647,7 +51647,7 @@
         <v>45747.39408564815</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51709,7 +51709,7 @@
         <v>45119</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51766,7 +51766,7 @@
         <v>45726.54469907407</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         <v>45121.35078703704</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51880,7 +51880,7 @@
         <v>44985</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51937,7 +51937,7 @@
         <v>45647</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51994,7 +51994,7 @@
         <v>45757.94755787037</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52051,7 +52051,7 @@
         <v>45349</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52108,7 +52108,7 @@
         <v>45204.32359953703</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52165,7 +52165,7 @@
         <v>44978.59528935186</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52222,7 +52222,7 @@
         <v>44960.36971064815</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52279,7 +52279,7 @@
         <v>45396.86226851852</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52336,7 +52336,7 @@
         <v>44712</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52393,7 +52393,7 @@
         <v>44980.62431712963</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52450,7 +52450,7 @@
         <v>44929</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52507,7 +52507,7 @@
         <v>45224.59289351852</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52564,7 +52564,7 @@
         <v>45281.63481481482</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52621,7 +52621,7 @@
         <v>45727.34787037037</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52678,7 +52678,7 @@
         <v>45510.89869212963</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52735,7 +52735,7 @@
         <v>45639.58114583333</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52792,7 +52792,7 @@
         <v>45686.3184375</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52849,7 +52849,7 @@
         <v>45253.54356481481</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52906,7 +52906,7 @@
         <v>45754.52563657407</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52963,7 +52963,7 @@
         <v>45754.52998842593</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53020,7 +53020,7 @@
         <v>44881</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53077,7 +53077,7 @@
         <v>45275</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53139,7 +53139,7 @@
         <v>45747.78081018518</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53196,7 +53196,7 @@
         <v>44272</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53253,7 +53253,7 @@
         <v>44330.36730324074</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53310,7 +53310,7 @@
         <v>45701.59954861111</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53367,7 +53367,7 @@
         <v>44991.34855324074</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53424,7 +53424,7 @@
         <v>45188</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53481,7 +53481,7 @@
         <v>45742.61196759259</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>44971.45475694445</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53595,7 +53595,7 @@
         <v>45224.70244212963</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>45594.62881944444</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53709,7 +53709,7 @@
         <v>45646.67726851852</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>45647</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53823,7 +53823,7 @@
         <v>45111</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>45647</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53937,7 +53937,7 @@
         <v>45647</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53994,7 +53994,7 @@
         <v>45647</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>45181</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54108,7 +54108,7 @@
         <v>45035</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54165,7 +54165,7 @@
         <v>45119.58694444445</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54222,7 +54222,7 @@
         <v>45705.5654050926</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54279,7 +54279,7 @@
         <v>44820</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54336,7 +54336,7 @@
         <v>45747.39719907408</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54398,7 +54398,7 @@
         <v>45628.49322916667</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54455,7 +54455,7 @@
         <v>45602.91650462963</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54512,7 +54512,7 @@
         <v>44380</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54569,7 +54569,7 @@
         <v>45188.62355324074</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54626,7 +54626,7 @@
         <v>44868.56361111111</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54683,7 +54683,7 @@
         <v>44882</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54740,7 +54740,7 @@
         <v>45188</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54797,7 +54797,7 @@
         <v>45463.39309027778</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54854,7 +54854,7 @@
         <v>45099</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54911,7 +54911,7 @@
         <v>44712.32885416667</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54968,7 +54968,7 @@
         <v>45033</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55025,7 +55025,7 @@
         <v>45602.65810185186</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55082,7 +55082,7 @@
         <v>45483</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55139,7 +55139,7 @@
         <v>45672.591875</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55196,7 +55196,7 @@
         <v>45749.53158564815</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55253,7 +55253,7 @@
         <v>45168.33028935185</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55310,7 +55310,7 @@
         <v>44377</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55367,7 +55367,7 @@
         <v>45620.46207175926</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55424,7 +55424,7 @@
         <v>45714.80385416667</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55481,7 +55481,7 @@
         <v>45551</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55543,7 +55543,7 @@
         <v>45012</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55600,7 +55600,7 @@
         <v>44991.53373842593</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55657,7 +55657,7 @@
         <v>44883</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55714,7 +55714,7 @@
         <v>44820.47260416667</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55771,7 +55771,7 @@
         <v>45762</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55828,7 +55828,7 @@
         <v>45730.65008101852</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55885,7 +55885,7 @@
         <v>45111</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55942,7 +55942,7 @@
         <v>45621</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55999,7 +55999,7 @@
         <v>45267.46962962963</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>45614.50907407407</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56118,7 +56118,7 @@
         <v>45643.45525462963</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56175,7 +56175,7 @@
         <v>44991.35916666667</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56232,7 +56232,7 @@
         <v>45742.89054398148</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56289,7 +56289,7 @@
         <v>44991</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56346,7 +56346,7 @@
         <v>45761</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56403,7 +56403,7 @@
         <v>45068.45921296296</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56460,7 +56460,7 @@
         <v>45212</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56517,7 +56517,7 @@
         <v>45679.48483796296</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56574,7 +56574,7 @@
         <v>45401.69138888889</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56631,7 +56631,7 @@
         <v>45410</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56688,7 +56688,7 @@
         <v>45103.67451388889</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56745,7 +56745,7 @@
         <v>45698</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56802,7 +56802,7 @@
         <v>45055.49951388889</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56859,7 +56859,7 @@
         <v>45162</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56916,7 +56916,7 @@
         <v>45236.35502314815</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>44078</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57030,7 +57030,7 @@
         <v>45394.35633101852</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57087,7 +57087,7 @@
         <v>45735.46643518518</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57144,7 +57144,7 @@
         <v>45170</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57201,7 +57201,7 @@
         <v>45211.63446759259</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57258,7 +57258,7 @@
         <v>44565.57157407407</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57315,7 +57315,7 @@
         <v>44565</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57372,7 +57372,7 @@
         <v>45169</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57429,7 +57429,7 @@
         <v>45301</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57486,7 +57486,7 @@
         <v>44810.49734953704</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57543,7 +57543,7 @@
         <v>45700.66474537037</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57600,7 +57600,7 @@
         <v>45700.69467592592</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57657,7 +57657,7 @@
         <v>45065</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57714,7 +57714,7 @@
         <v>44448</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57776,7 +57776,7 @@
         <v>45714.84204861111</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57833,7 +57833,7 @@
         <v>45121.70020833334</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57890,7 +57890,7 @@
         <v>45615.57574074074</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57947,7 +57947,7 @@
         <v>45071.55216435185</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58004,7 +58004,7 @@
         <v>45071.55913194444</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58061,7 +58061,7 @@
         <v>45146.71684027778</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58118,7 +58118,7 @@
         <v>45632.51193287037</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58175,7 +58175,7 @@
         <v>45730.63616898148</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58232,7 +58232,7 @@
         <v>45735.66598379629</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58294,7 +58294,7 @@
         <v>44903</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58351,7 +58351,7 @@
         <v>45698</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58408,7 +58408,7 @@
         <v>45079</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58465,7 +58465,7 @@
         <v>45210</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58522,7 +58522,7 @@
         <v>45076.30560185185</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58579,7 +58579,7 @@
         <v>45775.40460648148</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58636,7 +58636,7 @@
         <v>45077</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58693,7 +58693,7 @@
         <v>45730.61275462963</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58750,7 +58750,7 @@
         <v>44852</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58807,7 +58807,7 @@
         <v>45603</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58869,7 +58869,7 @@
         <v>45723</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58926,7 +58926,7 @@
         <v>45068.66135416667</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58988,7 +58988,7 @@
         <v>45748.90723379629</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59045,7 +59045,7 @@
         <v>45744.56912037037</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59107,7 +59107,7 @@
         <v>45301.98247685185</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59164,7 +59164,7 @@
         <v>45764.52859953704</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59221,7 +59221,7 @@
         <v>44881</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59278,7 +59278,7 @@
         <v>45181.56171296296</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59335,7 +59335,7 @@
         <v>45412</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59392,7 +59392,7 @@
         <v>44565.61265046296</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59449,7 +59449,7 @@
         <v>45036.6734375</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59506,7 +59506,7 @@
         <v>44886</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59563,7 +59563,7 @@
         <v>44585</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59620,7 +59620,7 @@
         <v>45620.82185185186</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59677,7 +59677,7 @@
         <v>44126</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59734,7 +59734,7 @@
         <v>45561.7159837963</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59791,7 +59791,7 @@
         <v>45070</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59848,7 +59848,7 @@
         <v>45755.48740740741</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59905,7 +59905,7 @@
         <v>44551.38699074074</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59962,7 +59962,7 @@
         <v>45594</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60019,7 +60019,7 @@
         <v>44809.39893518519</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60076,7 +60076,7 @@
         <v>44993</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60133,7 +60133,7 @@
         <v>45366.32900462963</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60190,7 +60190,7 @@
         <v>45097</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60247,7 +60247,7 @@
         <v>45546.84695601852</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60309,7 +60309,7 @@
         <v>45546.84908564815</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60371,7 +60371,7 @@
         <v>44421.51063657407</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60428,7 +60428,7 @@
         <v>45519.55430555555</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60485,7 +60485,7 @@
         <v>45054.85400462963</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60542,7 +60542,7 @@
         <v>45510</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60599,7 +60599,7 @@
         <v>44180</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>45709.64976851852</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60713,7 +60713,7 @@
         <v>45223</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60770,7 +60770,7 @@
         <v>45713</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60832,7 +60832,7 @@
         <v>45713.62074074074</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60894,7 +60894,7 @@
         <v>44160</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60951,7 +60951,7 @@
         <v>45250.44863425926</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61008,7 +61008,7 @@
         <v>44903.53118055555</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61065,7 +61065,7 @@
         <v>45758.73520833333</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61122,7 +61122,7 @@
         <v>45106.89616898148</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61179,7 +61179,7 @@
         <v>44454</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61236,7 +61236,7 @@
         <v>45546</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61293,7 +61293,7 @@
         <v>44129</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61350,7 +61350,7 @@
         <v>45355.4612037037</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61407,7 +61407,7 @@
         <v>45315.65375</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61464,7 +61464,7 @@
         <v>45629</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61521,7 +61521,7 @@
         <v>45202.38372685185</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61578,7 +61578,7 @@
         <v>44923</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -61635,7 +61635,7 @@
         <v>45339</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>44846.55085648148</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -61749,7 +61749,7 @@
         <v>45656.78905092592</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61806,7 +61806,7 @@
         <v>45763.84802083333</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61863,7 +61863,7 @@
         <v>44896.30818287037</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61920,7 +61920,7 @@
         <v>45747.78493055556</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -61977,7 +61977,7 @@
         <v>44466.48996527777</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62034,7 +62034,7 @@
         <v>44971.69971064815</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62091,7 +62091,7 @@
         <v>45726.51144675926</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62148,7 +62148,7 @@
         <v>44361.5662962963</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62205,7 +62205,7 @@
         <v>45634</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62262,7 +62262,7 @@
         <v>45610.36342592593</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62319,7 +62319,7 @@
         <v>45281.62631944445</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62376,7 +62376,7 @@
         <v>44587.40662037037</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62433,7 +62433,7 @@
         <v>44228</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62490,7 +62490,7 @@
         <v>45279</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62552,7 +62552,7 @@
         <v>45188.49987268518</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -62609,7 +62609,7 @@
         <v>44917</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -62666,7 +62666,7 @@
         <v>45274</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -62723,7 +62723,7 @@
         <v>45548.38636574074</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62780,7 +62780,7 @@
         <v>45099</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62837,7 +62837,7 @@
         <v>45610.60157407408</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62894,7 +62894,7 @@
         <v>45594.62287037037</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -62951,7 +62951,7 @@
         <v>45594.6306712963</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63008,7 +63008,7 @@
         <v>45077.43420138889</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63065,7 +63065,7 @@
         <v>45260</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63122,7 +63122,7 @@
         <v>44376</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63179,7 +63179,7 @@
         <v>45747</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63236,7 +63236,7 @@
         <v>45092.71057870371</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -63293,7 +63293,7 @@
         <v>45714.80880787037</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -63350,7 +63350,7 @@
         <v>45075.53265046296</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -63407,7 +63407,7 @@
         <v>45679.47949074074</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -63464,7 +63464,7 @@
         <v>45686.60939814815</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -63521,7 +63521,7 @@
         <v>45103</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -63578,7 +63578,7 @@
         <v>45635.84936342593</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -63635,7 +63635,7 @@
         <v>45595.4272337963</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -63692,7 +63692,7 @@
         <v>45307</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -63749,7 +63749,7 @@
         <v>45637.54557870371</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -63806,7 +63806,7 @@
         <v>45065</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -63863,7 +63863,7 @@
         <v>45722.31061342593</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -63920,7 +63920,7 @@
         <v>45639</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -63977,7 +63977,7 @@
         <v>45156</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -64034,7 +64034,7 @@
         <v>45656.78329861111</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -567,7 +567,7 @@
         <v>45105</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44735</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>45568</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>45820</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>44216</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44343</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>45533</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45733.64422453703</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>44610</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45211</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44258</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45078</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45357</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45194</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>45224</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>45078</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>45701.89549768518</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44151</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44271.71099537037</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44448</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44679</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>44825.70888888889</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44524</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>44495</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44809.40431712963</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44582</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45372.69723379629</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45558.62674768519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>45527.45695601852</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>45686.57611111111</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>45642.60756944444</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44985</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>45476.50744212963</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45819</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>44928</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45555.65903935185</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>45754</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44645</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>45274.32131944445</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>45282</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44232</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45181</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>44461</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>45005</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45111</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>45086</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>45749.46063657408</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44082.65943287037</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>44357.34326388889</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>44231</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>44467.6135300926</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44309.65885416666</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44571.63828703704</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>44186</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>44431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>44811.66311342592</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>44715.33956018519</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>44568</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>44119</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44853.50333333333</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44307.481875</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44622</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>44508.43092592592</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>44272</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>44152</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44271</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44134</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44285.5874537037</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44327.59131944444</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44357</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>44224</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>44245</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44230</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44441</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>44410</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44125.62782407407</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44459</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>44194</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44297</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44510.88893518518</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44809.54884259259</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>44721.65634259259</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44461</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44461.57160879629</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44607</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>44510</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44818</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>44125</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44848.3015625</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>44297</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44258</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44230</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44277.6141087963</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>44635.93181712963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44503.73802083333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44510.63989583333</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44386.6371412037</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44587.59076388889</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44742.95375</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>44592.65864583333</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>44370.39163194445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>44623.46204861111</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44650.495</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44714</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44847</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>44847</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44084</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>44257.83641203704</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>44292</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44749</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>44186</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44468</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>44460</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44441</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>44441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44404</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>44258</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44460</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44110</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44474</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44880.48260416667</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44837.42782407408</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44861</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44273.62519675926</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44245</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44221</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44140</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44304</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>44482</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>44315</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>44476</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>44476.58800925926</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>44145</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44806.68451388889</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44211</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44502.34869212963</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>44461.69494212963</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>44267</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>44165</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>44137.73322916667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>44459</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>44441</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>44515</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>44495.68931712963</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>44169</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>44715</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44384.39226851852</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44381</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>44476</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>44169</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44130</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>44576</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>44229</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>44426.34618055556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44888.69445601852</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>44322.68579861111</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44175</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44825.35965277778</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44187.74415509259</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>44460.62309027778</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44363</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>44064</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>44321.51725694445</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>44147.70520833333</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44764</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>44203</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>44229</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44806</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44165</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44817</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44712.30428240741</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44537.63180555555</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44809.39019675926</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44806</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44565.61417824074</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44739.3564699074</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44606</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44820.47135416666</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44146</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>44369.93123842592</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44810</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44186</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44173</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44417.77873842593</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44610.3157175926</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>44265</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44448.45023148148</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>44448</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44084</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>44277.60974537037</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44446</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44357.34568287037</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44371</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44420.65103009259</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44127.46831018518</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44742.71378472223</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>44760.74060185185</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44246</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>44715.33355324074</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>44732.43689814815</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>44169</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44469</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>44515</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>44592.65989583333</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>44109</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>44187</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>44069</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>44469</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>44517</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>44595</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44530</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>44204</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>44237</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>44228</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44550</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>44280</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>44295.77248842592</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>44879.61497685185</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>44536</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>44810.40475694444</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44070</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44810.35575231481</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44538.40638888889</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44831</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>44497.430625</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44588</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>44384.46910879629</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44295</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44882.66891203704</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>44152</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44621.66707175926</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44495.69234953704</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>44845</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44449</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>44882.6740162037</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>44862.38081018518</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>44209</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>44075</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>44152</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>44421</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>44991.51193287037</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>44991</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>44809</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>45684.34170138889</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>45684.34384259259</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>45048</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>44900</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>44867</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45187.48282407408</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45187</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44819.34596064815</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>45735.45677083333</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>44974</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>44908</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44908</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45126</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>44924</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>44825.46571759259</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>45334</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>44764</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>45324.71243055556</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>45164</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45715</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>45035</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45272.62565972222</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44061</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>45089</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45247.46569444444</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>45085.93778935185</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45734.59581018519</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>44508</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>45440.4658449074</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45724</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45679.49804398148</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>45707.64956018519</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45707.66369212963</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45126</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45441</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45749.56019675926</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45730.6487037037</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45441</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>45702.6033912037</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45183.65436342593</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45223</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>45223</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>45764.48869212963</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>44235</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44928</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45773.44608796296</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45614.505625</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>44446</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>44357.34482638889</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>45343.92605324074</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45272</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>45723.50291666666</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45723.54547453704</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>44424</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45272</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45747.79938657407</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45713</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>44810.56070601852</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45646</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45300</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45181.58791666666</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45069.48967592593</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>44810.52567129629</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>45685.35516203703</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>45775.87377314815</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>45239</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45629</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45373.59099537037</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44895</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44895</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44895.58759259259</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45534.67689814815</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45775.87576388889</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44090</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45708.48537037037</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>45777.61497685185</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20309,7 +20309,7 @@
         <v>45777.73621527778</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45777.72737268519</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>44959</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45470</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>45750.94241898148</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45097</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>45061</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>45782.33971064815</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>44181</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45463</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>45572.67497685185</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>45372.68917824074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45481.49108796296</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45783.67510416666</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>45783.7002662037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>45783.70811342593</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>45783.71136574074</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45783.71869212963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45783.7308912037</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45783.72262731481</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45161</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>45021</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45306</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45783.73440972222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>45783.74034722222</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>45784.74020833334</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>45708.4921412037</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45512.53300925926</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>44847.46701388889</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>45567</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22034,7 +22034,7 @@
         <v>45681.62265046296</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>45099</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>45628.46613425926</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45754.56905092593</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>44848.30996527777</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>45372.36653935185</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>45734.55042824074</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>45425.69540509259</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45720.3175462963</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45789.70107638889</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45162.32709490741</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>45615.6362037037</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>45617.72069444445</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>45181</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45510.89385416666</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>45390</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>45720.31155092592</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>45148.62439814815</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>45168.33265046297</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>45727</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>45188.49305555555</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>44985</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>44985</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>45756.29003472222</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>45116.79090277778</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>45116.79268518519</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45166.62002314815</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>45628.56518518519</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>45370.34275462963</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>44937.71841435185</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45470</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45273</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45533</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>45561.88243055555</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>45792.30664351852</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>45792.32596064815</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45593</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>45593</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45792.33170138889</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>45510</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>44995.44344907408</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>44515</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>44070</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>45614.63012731481</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45754.52788194444</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45524.49138888889</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45527.44498842592</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>45600</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45349.39254629629</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45796.36819444445</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45796.55706018519</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45079</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45796.56827546296</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>45796.60440972223</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>45334</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>45796.38944444444</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>45197</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45596.44083333333</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>45734.57873842592</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>45796.38582175926</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>45089</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>44999.50538194444</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45629</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>45056.31962962963</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>45793.67677083334</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>45188.61378472222</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>45126</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>44551</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45119.63947916667</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>45272</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>45793.56537037037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>44186</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45796.56221064815</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>45610.42850694444</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>45637</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>45642.57581018518</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>45796.58149305556</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>45604.47508101852</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>45596.57131944445</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>45719</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>45084.51329861111</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>45644.02509259259</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26773,7 +26773,7 @@
         <v>45797</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>45714.80106481481</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>44946.42413194444</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45798.50189814815</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45614.49559027778</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>44927.74953703704</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>45216.52173611111</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44603.63212962963</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>44603</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>44603.6434375</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>45594.6255787037</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>45345</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>45701.6053125</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>45156</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45645.58603009259</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>45799.40628472222</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44582.42422453704</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>45562.55799768519</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>44251</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>44140</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>45748.86240740741</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         <v>45645.40951388889</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28042,7 +28042,7 @@
         <v>45845.48228009259</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>45638</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>44988</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>45845</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>45803.59722222222</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45804.66229166667</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>45804</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45845.48898148148</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45845</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45610.60369212963</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45427</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>45176</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>45804.6612962963</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>45253</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>45805.27778935185</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>45684.45225694445</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>45805.31606481481</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         <v>45461</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>45183.65034722222</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>45847</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45082</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29259,7 +29259,7 @@
         <v>45805.27396990741</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>45317</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>45610</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45805.27659722222</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>44160</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>45747.39516203704</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>45848.61030092592</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>45847.3721412037</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         <v>45236</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29792,7 +29792,7 @@
         <v>45112</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>45769.33756944445</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>44642.83407407408</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>45359.49635416667</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45749.56623842593</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>44823.61398148148</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>45847.67871527778</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>45628.48590277778</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45686.54246527778</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>45323</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>44634.60929398148</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>45615.57407407407</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>45617.49510416666</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>45667.4771412037</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>45628.43445601852</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>45119.57798611111</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44860.93721064815</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44384.39820601852</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45097</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>45069.64322916666</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44617</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>44075</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>45459.30690972223</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>45470</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>45278.88578703703</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>45848.6062962963</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         <v>45677.37925925926</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>45205</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>45371.85761574074</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>45265.48799768519</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31517,7 +31517,7 @@
         <v>45240.67206018518</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>45358</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45754.38893518518</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>44894.63579861111</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>45179</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>44886.51197916667</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>44850</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>44721.70876157407</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>45339.66177083334</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>45847.67734953704</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32087,7 +32087,7 @@
         <v>45775.58704861111</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32144,7 +32144,7 @@
         <v>45483</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>45483</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>45509</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>44146</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>45266</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>44851.61237268519</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45701.58163194444</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>45701.60341435186</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32610,7 +32610,7 @@
         <v>45686.60648148148</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>45686.63332175926</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32724,7 +32724,7 @@
         <v>45701.90762731482</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>45700.51605324074</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>45530</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>44124.48305555555</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>44628.47715277778</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>44945.34497685185</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33066,7 +33066,7 @@
         <v>45812.59082175926</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>45811.48709490741</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45476.50119212963</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>45476.50480324074</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>45811.39115740741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>45811.39695601852</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>45811.40674768519</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>45811</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45811.55042824074</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45811.56310185185</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>45446</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>45103</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45811.56517361111</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>45852.75837962963</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>45811.48321759259</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>45811.4892824074</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33978,7 +33978,7 @@
         <v>45181</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>45811.57001157408</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34092,7 +34092,7 @@
         <v>44817</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34149,7 +34149,7 @@
         <v>44851.60855324074</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34211,7 +34211,7 @@
         <v>45672.58387731481</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>45236.68318287037</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>45246.77350694445</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>45482</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>45483</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>45195.85546296297</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>45852.33880787037</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34610,7 +34610,7 @@
         <v>44523.46746527778</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34667,7 +34667,7 @@
         <v>45741.47434027777</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45530</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>45530.69050925926</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>45163.37561342592</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34895,7 +34895,7 @@
         <v>44706</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>44656.61335648148</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45188.4716550926</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>45686.51583333333</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35123,7 +35123,7 @@
         <v>45617.54989583333</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35180,7 +35180,7 @@
         <v>45817.39481481481</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
         <v>44908</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>44435.41690972223</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>45818.66649305556</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45715.5681712963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>45126</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>45817.39133101852</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>45818</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>44915</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>45357</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>45762.60217592592</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>45817</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>45518</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45357</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45818.66446759259</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>45187.59305555555</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36102,7 +36102,7 @@
         <v>44750</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
         <v>45581.49583333333</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>45137.90618055555</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>44174</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>44874</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>44098</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45646.67438657407</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45647</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45647</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>45647</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45225.49447916666</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>45707.66030092593</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>45820</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>45131</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>45301.98100694444</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45207.49881944444</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45860</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37081,7 +37081,7 @@
         <v>45756.29621527778</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>45231</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45676.57688657408</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>45274.57935185185</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>45264.68074074074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>45567.33017361111</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>45824.61681712963</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>45824.61572916667</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45735.46112268518</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45748.59457175926</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>45824.55555555555</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44825.46825231481</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>45826.41267361111</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>45826</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>45215.7849074074</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>45825.65555555555</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>45754.57372685185</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>45217.3809837963</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45617.68131944445</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38164,7 +38164,7 @@
         <v>45826.47586805555</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45525</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45475</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45562</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45315.65311342593</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38449,7 +38449,7 @@
         <v>44160</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>44886</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45713</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>45826</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>44144</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>45869</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>45869</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45359.50059027778</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45712</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45280</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45215.48378472222</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>45211.63712962963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>45775.59978009259</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>45775.60414351852</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45328</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45793.65984953703</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>45869</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45350.91678240741</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>45350.91932870371</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45869</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>45831.3783912037</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45831.57793981482</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>45831.3978587963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45225.63777777777</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45257.57825231482</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39909,7 +39909,7 @@
         <v>45301.98575231482</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>45162.588125</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
         <v>45831</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>45832.28081018518</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45831.36892361111</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40194,7 +40194,7 @@
         <v>45831.35077546296</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45831.34712962963</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>45831</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40365,7 +40365,7 @@
         <v>44988.85038194444</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40422,7 +40422,7 @@
         <v>44942</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>45831.36045138889</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40536,7 +40536,7 @@
         <v>45715.56667824074</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>45196</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>45748.91101851852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>45831.56630787037</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>45126</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40821,7 +40821,7 @@
         <v>45356.68585648148</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>45833.74201388889</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45833.73708333333</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45218.86829861111</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45212</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45195.85668981481</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45510</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>44908</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>44858.63208333333</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45875.45658564815</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41396,7 +41396,7 @@
         <v>44180</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>45875.6449537037</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41510,7 +41510,7 @@
         <v>44852.89560185185</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>45099.91826388889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41624,7 +41624,7 @@
         <v>45874.65034722222</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41681,7 +41681,7 @@
         <v>45875.64696759259</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>45880.86574074074</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>45876.62177083334</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>45712.57320601852</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>45742.36822916667</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41966,7 +41966,7 @@
         <v>45280</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>45372.7019212963</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45145.57798611111</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
         <v>44670.43472222222</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42194,7 +42194,7 @@
         <v>45279</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42251,7 +42251,7 @@
         <v>44187</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>45838.65454861111</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>45264.68416666667</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42422,7 +42422,7 @@
         <v>45838.66364583333</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42479,7 +42479,7 @@
         <v>45835.40136574074</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42536,7 +42536,7 @@
         <v>45246</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>45099</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>45880.56395833333</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42707,7 +42707,7 @@
         <v>45672.78414351852</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>45838.65708333333</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42821,7 +42821,7 @@
         <v>45877.42953703704</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>45837.87837962963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>45837.90488425926</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>45835.39804398148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45784</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>45394.73528935185</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>45840.55074074074</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45110</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43277,7 +43277,7 @@
         <v>45840.5487037037</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>45881</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43391,7 +43391,7 @@
         <v>45167.68207175926</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43448,7 +43448,7 @@
         <v>45614.44239583334</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43505,7 +43505,7 @@
         <v>45881.31761574074</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43562,7 +43562,7 @@
         <v>44104</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43619,7 +43619,7 @@
         <v>45837.90292824074</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
         <v>45837.91177083334</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>45881.66684027778</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>45880</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>45225.63304398148</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43904,7 +43904,7 @@
         <v>45884.62045138889</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>44337.48540509259</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44018,7 +44018,7 @@
         <v>45604.54047453704</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45772.59259259259</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44132,7 +44132,7 @@
         <v>44380</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44189,7 +44189,7 @@
         <v>45842.62019675926</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44246,7 +44246,7 @@
         <v>45842.62362268518</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44303,7 +44303,7 @@
         <v>45071.54651620371</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45071.54908564815</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44417,7 +44417,7 @@
         <v>44573</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>45841.57072916667</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>45734.93418981481</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44593,7 +44593,7 @@
         <v>45884.73457175926</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45769.36023148148</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44707,7 +44707,7 @@
         <v>45842.45201388889</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>45733.60265046296</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>44651</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>45441</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>45441.54350694444</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>45275.30907407407</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45049,7 +45049,7 @@
         <v>45705.65206018519</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>45205.39787037037</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>45205</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45240,7 +45240,7 @@
         <v>45205</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45297,7 +45297,7 @@
         <v>44945.35765046296</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45354,7 +45354,7 @@
         <v>44573</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45416,7 +45416,7 @@
         <v>45567</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>44181</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>45243</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45587,7 +45587,7 @@
         <v>45005</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>44740.92936342592</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45701,7 +45701,7 @@
         <v>44620.45334490741</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>45739.84453703704</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45815,7 +45815,7 @@
         <v>45272</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>45226.43175925926</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45929,7 +45929,7 @@
         <v>45567.37547453704</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         <v>44887</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>44938</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46100,7 +46100,7 @@
         <v>44441</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46157,7 +46157,7 @@
         <v>44946.62486111111</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46219,7 +46219,7 @@
         <v>44974.57127314815</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>44959.62519675926</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>44959</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>44959</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45271</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>44812</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>45084.67444444444</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>44810</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>44634</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46737,7 +46737,7 @@
         <v>45026</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>44959.68709490741</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>44923</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46908,7 +46908,7 @@
         <v>44923.65486111111</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46965,7 +46965,7 @@
         <v>45730.61458333334</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47022,7 +47022,7 @@
         <v>44266</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45610.59956018518</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>45614.50349537037</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>44959</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>45301.83475694444</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47312,7 +47312,7 @@
         <v>45628.44303240741</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>45188</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47426,7 +47426,7 @@
         <v>45162.65574074074</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>44924.66556712963</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47545,7 +47545,7 @@
         <v>45621</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>45618.61243055556</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>45610.61537037037</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>44158</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47778,7 +47778,7 @@
         <v>45594.61994212963</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47835,7 +47835,7 @@
         <v>44657</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47892,7 +47892,7 @@
         <v>44634</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47949,7 +47949,7 @@
         <v>44928.45686342593</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48006,7 +48006,7 @@
         <v>44894.45888888889</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>45231</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>45758.72209490741</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>45758.73298611111</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48234,7 +48234,7 @@
         <v>45218.47658564815</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48291,7 +48291,7 @@
         <v>44151</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>45020</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>45593</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>45260.32738425926</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>45684.34594907407</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>44806.59946759259</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48643,7 +48643,7 @@
         <v>45012</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>45602</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48757,7 +48757,7 @@
         <v>45191.55503472222</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>45593</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>44742.71030092592</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>45323</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48995,7 +48995,7 @@
         <v>45359.50601851852</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49052,7 +49052,7 @@
         <v>45152</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49109,7 +49109,7 @@
         <v>45131</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>45012</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49223,7 +49223,7 @@
         <v>45645.58436342593</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49280,7 +49280,7 @@
         <v>45356.68475694444</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
         <v>44487</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>45562.53543981481</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49456,7 +49456,7 @@
         <v>45145.58085648148</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49513,7 +49513,7 @@
         <v>45546.85369212963</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49575,7 +49575,7 @@
         <v>45109</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49632,7 +49632,7 @@
         <v>45604.4971412037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>45593</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49751,7 +49751,7 @@
         <v>45483</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>44260</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>45226.44923611111</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>45509.66609953704</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>44999.50461805556</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>45645</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>45568.46310185185</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>44802</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45645.58762731482</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50269,7 +50269,7 @@
         <v>44743.61965277778</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>45097</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50383,7 +50383,7 @@
         <v>45097</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50440,7 +50440,7 @@
         <v>45632.31087962963</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50497,7 +50497,7 @@
         <v>45764.48725694444</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>45081</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50611,7 +50611,7 @@
         <v>44060</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50668,7 +50668,7 @@
         <v>45093</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50725,7 +50725,7 @@
         <v>45672.46096064815</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50782,7 +50782,7 @@
         <v>45630.32984953704</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50839,7 +50839,7 @@
         <v>45305.57791666667</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50896,7 +50896,7 @@
         <v>45607.36863425926</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50953,7 +50953,7 @@
         <v>45097</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51010,7 +51010,7 @@
         <v>45033</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51067,7 +51067,7 @@
         <v>45470.64299768519</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51124,7 +51124,7 @@
         <v>45470.64894675926</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51181,7 +51181,7 @@
         <v>45152.37778935185</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45656.73612268519</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51295,7 +51295,7 @@
         <v>44281</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>45005</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51414,7 +51414,7 @@
         <v>45733.43582175926</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51471,7 +51471,7 @@
         <v>45733.44309027777</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51528,7 +51528,7 @@
         <v>45733.57615740741</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51585,7 +51585,7 @@
         <v>45747.39269675926</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51647,7 +51647,7 @@
         <v>45747.39408564815</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51709,7 +51709,7 @@
         <v>45119</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51766,7 +51766,7 @@
         <v>45726.54469907407</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         <v>45121.35078703704</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51880,7 +51880,7 @@
         <v>44985</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51937,7 +51937,7 @@
         <v>45647</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51994,7 +51994,7 @@
         <v>45757.94755787037</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52051,7 +52051,7 @@
         <v>45349</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52108,7 +52108,7 @@
         <v>45204.32359953703</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52165,7 +52165,7 @@
         <v>44978.59528935186</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52222,7 +52222,7 @@
         <v>44960.36971064815</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52279,7 +52279,7 @@
         <v>45396.86226851852</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52336,7 +52336,7 @@
         <v>44712</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52393,7 +52393,7 @@
         <v>44980.62431712963</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52450,7 +52450,7 @@
         <v>44929</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52507,7 +52507,7 @@
         <v>45224.59289351852</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52564,7 +52564,7 @@
         <v>45281.63481481482</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52621,7 +52621,7 @@
         <v>45727.34787037037</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52678,7 +52678,7 @@
         <v>45510.89869212963</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52735,7 +52735,7 @@
         <v>45639.58114583333</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52792,7 +52792,7 @@
         <v>45686.3184375</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52849,7 +52849,7 @@
         <v>45253.54356481481</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52906,7 +52906,7 @@
         <v>45754.52563657407</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52963,7 +52963,7 @@
         <v>45754.52998842593</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53020,7 +53020,7 @@
         <v>44881</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53077,7 +53077,7 @@
         <v>45275</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53139,7 +53139,7 @@
         <v>45747.78081018518</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53196,7 +53196,7 @@
         <v>44272</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53253,7 +53253,7 @@
         <v>44330.36730324074</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53310,7 +53310,7 @@
         <v>45701.59954861111</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53367,7 +53367,7 @@
         <v>44991.34855324074</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53424,7 +53424,7 @@
         <v>45188</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53481,7 +53481,7 @@
         <v>45742.61196759259</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>44971.45475694445</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53595,7 +53595,7 @@
         <v>45224.70244212963</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>45594.62881944444</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53709,7 +53709,7 @@
         <v>45646.67726851852</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>45647</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53823,7 +53823,7 @@
         <v>45111</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>45647</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53937,7 +53937,7 @@
         <v>45647</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53994,7 +53994,7 @@
         <v>45647</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>45181</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54108,7 +54108,7 @@
         <v>45035</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54165,7 +54165,7 @@
         <v>45119.58694444445</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54222,7 +54222,7 @@
         <v>45705.5654050926</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54279,7 +54279,7 @@
         <v>44820</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54336,7 +54336,7 @@
         <v>45747.39719907408</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54398,7 +54398,7 @@
         <v>45628.49322916667</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54455,7 +54455,7 @@
         <v>45602.91650462963</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54512,7 +54512,7 @@
         <v>44380</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54569,7 +54569,7 @@
         <v>45188.62355324074</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54626,7 +54626,7 @@
         <v>44868.56361111111</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54683,7 +54683,7 @@
         <v>44882</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54740,7 +54740,7 @@
         <v>45188</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54797,7 +54797,7 @@
         <v>45463.39309027778</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54854,7 +54854,7 @@
         <v>45099</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54911,7 +54911,7 @@
         <v>44712.32885416667</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54968,7 +54968,7 @@
         <v>45033</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55025,7 +55025,7 @@
         <v>45602.65810185186</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55082,7 +55082,7 @@
         <v>45483</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55139,7 +55139,7 @@
         <v>45672.591875</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55196,7 +55196,7 @@
         <v>45749.53158564815</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55253,7 +55253,7 @@
         <v>45168.33028935185</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55310,7 +55310,7 @@
         <v>44377</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55367,7 +55367,7 @@
         <v>45620.46207175926</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55424,7 +55424,7 @@
         <v>45714.80385416667</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55481,7 +55481,7 @@
         <v>45551</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55543,7 +55543,7 @@
         <v>45012</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55600,7 +55600,7 @@
         <v>44991.53373842593</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55657,7 +55657,7 @@
         <v>44883</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55714,7 +55714,7 @@
         <v>44820.47260416667</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55771,7 +55771,7 @@
         <v>45762</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55828,7 +55828,7 @@
         <v>45730.65008101852</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55885,7 +55885,7 @@
         <v>45111</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55942,7 +55942,7 @@
         <v>45621</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55999,7 +55999,7 @@
         <v>45267.46962962963</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>45614.50907407407</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56118,7 +56118,7 @@
         <v>45643.45525462963</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56175,7 +56175,7 @@
         <v>44991.35916666667</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56232,7 +56232,7 @@
         <v>45742.89054398148</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56289,7 +56289,7 @@
         <v>44991</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56346,7 +56346,7 @@
         <v>45761</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56403,7 +56403,7 @@
         <v>45068.45921296296</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56460,7 +56460,7 @@
         <v>45212</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56517,7 +56517,7 @@
         <v>45679.48483796296</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56574,7 +56574,7 @@
         <v>45401.69138888889</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56631,7 +56631,7 @@
         <v>45410</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56688,7 +56688,7 @@
         <v>45103.67451388889</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56745,7 +56745,7 @@
         <v>45698</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56802,7 +56802,7 @@
         <v>45055.49951388889</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56859,7 +56859,7 @@
         <v>45162</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56916,7 +56916,7 @@
         <v>45236.35502314815</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>44078</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57030,7 +57030,7 @@
         <v>45394.35633101852</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57087,7 +57087,7 @@
         <v>45735.46643518518</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57144,7 +57144,7 @@
         <v>45170</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57201,7 +57201,7 @@
         <v>45211.63446759259</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57258,7 +57258,7 @@
         <v>44565.57157407407</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57315,7 +57315,7 @@
         <v>44565</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57372,7 +57372,7 @@
         <v>45169</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57429,7 +57429,7 @@
         <v>45301</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57486,7 +57486,7 @@
         <v>44810.49734953704</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57543,7 +57543,7 @@
         <v>45700.66474537037</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57600,7 +57600,7 @@
         <v>45700.69467592592</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57657,7 +57657,7 @@
         <v>45065</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57714,7 +57714,7 @@
         <v>44448</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57776,7 +57776,7 @@
         <v>45714.84204861111</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57833,7 +57833,7 @@
         <v>45121.70020833334</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57890,7 +57890,7 @@
         <v>45615.57574074074</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57947,7 +57947,7 @@
         <v>45071.55216435185</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58004,7 +58004,7 @@
         <v>45071.55913194444</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58061,7 +58061,7 @@
         <v>45146.71684027778</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58118,7 +58118,7 @@
         <v>45632.51193287037</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58175,7 +58175,7 @@
         <v>45730.63616898148</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58232,7 +58232,7 @@
         <v>45735.66598379629</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58294,7 +58294,7 @@
         <v>44903</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58351,7 +58351,7 @@
         <v>45698</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58408,7 +58408,7 @@
         <v>45079</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58465,7 +58465,7 @@
         <v>45210</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58522,7 +58522,7 @@
         <v>45076.30560185185</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58579,7 +58579,7 @@
         <v>45775.40460648148</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58636,7 +58636,7 @@
         <v>45077</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58693,7 +58693,7 @@
         <v>45730.61275462963</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58750,7 +58750,7 @@
         <v>44852</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58807,7 +58807,7 @@
         <v>45603</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58869,7 +58869,7 @@
         <v>45723</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58926,7 +58926,7 @@
         <v>45068.66135416667</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58988,7 +58988,7 @@
         <v>45748.90723379629</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59045,7 +59045,7 @@
         <v>45744.56912037037</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59107,7 +59107,7 @@
         <v>45301.98247685185</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59164,7 +59164,7 @@
         <v>45764.52859953704</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59221,7 +59221,7 @@
         <v>44881</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59278,7 +59278,7 @@
         <v>45181.56171296296</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59335,7 +59335,7 @@
         <v>45412</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59392,7 +59392,7 @@
         <v>44565.61265046296</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59449,7 +59449,7 @@
         <v>45036.6734375</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59506,7 +59506,7 @@
         <v>44886</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59563,7 +59563,7 @@
         <v>44585</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59620,7 +59620,7 @@
         <v>45620.82185185186</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59677,7 +59677,7 @@
         <v>44126</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59734,7 +59734,7 @@
         <v>45561.7159837963</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59791,7 +59791,7 @@
         <v>45070</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59848,7 +59848,7 @@
         <v>45755.48740740741</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59905,7 +59905,7 @@
         <v>44551.38699074074</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59962,7 +59962,7 @@
         <v>45594</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60019,7 +60019,7 @@
         <v>44809.39893518519</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60076,7 +60076,7 @@
         <v>44993</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60133,7 +60133,7 @@
         <v>45366.32900462963</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60190,7 +60190,7 @@
         <v>45097</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60247,7 +60247,7 @@
         <v>45546.84695601852</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60309,7 +60309,7 @@
         <v>45546.84908564815</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60371,7 +60371,7 @@
         <v>44421.51063657407</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60428,7 +60428,7 @@
         <v>45519.55430555555</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60485,7 +60485,7 @@
         <v>45054.85400462963</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60542,7 +60542,7 @@
         <v>45510</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60599,7 +60599,7 @@
         <v>44180</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>45709.64976851852</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60713,7 +60713,7 @@
         <v>45223</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60770,7 +60770,7 @@
         <v>45713</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60832,7 +60832,7 @@
         <v>45713.62074074074</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60894,7 +60894,7 @@
         <v>44160</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60951,7 +60951,7 @@
         <v>45250.44863425926</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61008,7 +61008,7 @@
         <v>44903.53118055555</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61065,7 +61065,7 @@
         <v>45758.73520833333</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61122,7 +61122,7 @@
         <v>45106.89616898148</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61179,7 +61179,7 @@
         <v>44454</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61236,7 +61236,7 @@
         <v>45546</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61293,7 +61293,7 @@
         <v>44129</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61350,7 +61350,7 @@
         <v>45355.4612037037</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61407,7 +61407,7 @@
         <v>45315.65375</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61464,7 +61464,7 @@
         <v>45629</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61521,7 +61521,7 @@
         <v>45202.38372685185</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61578,7 +61578,7 @@
         <v>44923</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -61635,7 +61635,7 @@
         <v>45339</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>44846.55085648148</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -61749,7 +61749,7 @@
         <v>45656.78905092592</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61806,7 +61806,7 @@
         <v>45763.84802083333</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61863,7 +61863,7 @@
         <v>44896.30818287037</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61920,7 +61920,7 @@
         <v>45747.78493055556</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -61977,7 +61977,7 @@
         <v>44466.48996527777</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62034,7 +62034,7 @@
         <v>44971.69971064815</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62091,7 +62091,7 @@
         <v>45726.51144675926</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62148,7 +62148,7 @@
         <v>44361.5662962963</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62205,7 +62205,7 @@
         <v>45634</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62262,7 +62262,7 @@
         <v>45610.36342592593</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62319,7 +62319,7 @@
         <v>45281.62631944445</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62376,7 +62376,7 @@
         <v>44587.40662037037</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62433,7 +62433,7 @@
         <v>44228</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62490,7 +62490,7 @@
         <v>45279</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62552,7 +62552,7 @@
         <v>45188.49987268518</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -62609,7 +62609,7 @@
         <v>44917</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -62666,7 +62666,7 @@
         <v>45274</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -62723,7 +62723,7 @@
         <v>45548.38636574074</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62780,7 +62780,7 @@
         <v>45099</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62837,7 +62837,7 @@
         <v>45610.60157407408</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62894,7 +62894,7 @@
         <v>45594.62287037037</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -62951,7 +62951,7 @@
         <v>45594.6306712963</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63008,7 +63008,7 @@
         <v>45077.43420138889</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63065,7 +63065,7 @@
         <v>45260</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63122,7 +63122,7 @@
         <v>44376</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63179,7 +63179,7 @@
         <v>45747</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63236,7 +63236,7 @@
         <v>45092.71057870371</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -63293,7 +63293,7 @@
         <v>45714.80880787037</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -63350,7 +63350,7 @@
         <v>45075.53265046296</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -63407,7 +63407,7 @@
         <v>45679.47949074074</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -63464,7 +63464,7 @@
         <v>45686.60939814815</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -63521,7 +63521,7 @@
         <v>45103</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -63578,7 +63578,7 @@
         <v>45635.84936342593</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -63635,7 +63635,7 @@
         <v>45595.4272337963</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -63692,7 +63692,7 @@
         <v>45307</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -63749,7 +63749,7 @@
         <v>45637.54557870371</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -63806,7 +63806,7 @@
         <v>45065</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -63863,7 +63863,7 @@
         <v>45722.31061342593</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -63920,7 +63920,7 @@
         <v>45639</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -63977,7 +63977,7 @@
         <v>45156</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -64034,7 +64034,7 @@
         <v>45656.78329861111</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -567,7 +567,7 @@
         <v>45105</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44735</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>45568</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>45820</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>44216</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44343</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>45533</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45357</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>44610</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45194</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>45701.89549768518</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>45224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>45078</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>44258</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>45078</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>45733.64422453703</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>45211</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44151</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44271.71099537037</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44448</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44679</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>44825.70888888889</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44524</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>44495</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44809.40431712963</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44582</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45372.69723379629</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>44461</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>45476.50744212963</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>45749.46063657408</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>44645</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45686.57611111111</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>45558.62674768519</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45181</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>44928</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45274.32131944445</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>45282</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45086</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>45819</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44232</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>45005</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>45642.60756944444</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>45754</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45111</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45527.45695601852</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>44985</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>45555.65903935185</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44082.65943287037</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>44231</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>44357.34326388889</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>44467.6135300926</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44571.63828703704</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44431</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>44309.65885416666</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>44715.33956018519</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>44811.66311342592</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>44119</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>44568</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>44186</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44853.50333333333</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44307.481875</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44508.43092592592</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>44622</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>44272</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>44152</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44271</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44134</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44285.5874537037</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44327.59131944444</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44357</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>44245</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>44224</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44441</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44230</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>44410</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44125.62782407407</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44459</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>44194</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44297</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44510.88893518518</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44809.54884259259</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>44607</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44721.65634259259</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44461</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44461.57160879629</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>44510</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44818</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>44848.3015625</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44297</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>44258</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44277.6141087963</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44230</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44635.93181712963</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>44125</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44503.73802083333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44510.63989583333</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44386.6371412037</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44592.65864583333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>44587.59076388889</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44742.95375</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>44370.39163194445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>44650.495</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44623.46204861111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44714</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44847</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>44847</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44084</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>44257.83641203704</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>44292</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44749</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>44186</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44460</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>44441</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44441</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>44468</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44258</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44460</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>44404</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44259</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44474</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44880.48260416667</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44837.42782407408</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44110</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44861</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44273.62519675926</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44245</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44140</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44221</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44304</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>44482</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>44315</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>44145</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>44806.68451388889</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>44476</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>44476.58800925926</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44211</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44502.34869212963</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>44461.69494212963</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>44267</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>44165</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>44137.73322916667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>44459</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>44441</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>44515</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>44495.68931712963</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>44169</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>44715</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44381</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44384.39226851852</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>44476</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>44169</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44130</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>44576</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>44229</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>44426.34618055556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44421</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>44295</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44882.66891203704</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44449</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44882.6740162037</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>44888.69445601852</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44075</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>44175</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>44322.68579861111</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>44187.74415509259</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44321.51725694445</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>44825.35965277778</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>44460.62309027778</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44147.70520833333</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44363</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44203</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44229</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44764</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44817</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44537.63180555555</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44806</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44712.30428240741</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44809.39019675926</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44165</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44806</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>44820.47135416666</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44606</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44739.3564699074</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44810</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44173</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44565.61417824074</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>44146</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44417.77873842593</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>44369.93123842592</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44610.3157175926</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>44186</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44277.60974537037</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44084</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44446</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44357.34568287037</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44371</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44420.65103009259</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>44246</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44742.71378472223</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>44265</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>44448.45023148148</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>44448</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44715.33355324074</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>44169</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>44127.46831018518</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>44515</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>44592.65989583333</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>44760.74060185185</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>44187</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>44109</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>44069</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>44517</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>44595</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>44204</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>44530</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44228</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>44732.43689814815</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>44237</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>44469</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>44879.61497685185</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>44280</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44295.77248842592</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44497.430625</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44070</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44469</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>44831</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44621.66707175926</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>44495.69234953704</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44209</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44228</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45672.591875</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44152</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44550</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>45748.59457175926</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>45748.91101851852</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>44384.46910879629</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>44536</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>45187</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>45607.36863425926</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>44810.40475694444</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>44810.35575231481</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45775.59978009259</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>45775.60414351852</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45615.57574074074</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44538.40638888889</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>45075.53265046296</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>45572.67497685185</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>44588</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45470</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45594.61994212963</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>44929</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>45614.50907407407</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>44850</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>44515</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>45602.65810185186</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45339</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45097</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44152</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45594.6255787037</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44764</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45103</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>44104</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45223</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>45223</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44845</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>45169</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45715</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         <v>45279</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>44862.38081018518</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>45071.55216435185</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>45071.55913194444</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45097</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45727</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45614.49559027778</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45211.63446759259</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>45275</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>44642.83407407408</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>45109</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>45595.4272337963</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>45359.50059027778</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>44867</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>44852</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>45726.54469907407</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>45301.83475694444</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>44712.32885416667</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45082</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45065</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45195.85668981481</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>45071.54651620371</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45071.54908564815</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>44825.46571759259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>44928.45686342593</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>44881</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45225.49447916666</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>45116.79090277778</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45116.79268518519</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>44377</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45068.66135416667</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45610.36342592593</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>44448</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>45705.5654050926</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>45156</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>45701.90762731482</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>45218.86829861111</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45628.48590277778</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45551</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45749.53158564815</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>44971.45475694445</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>44974.57127314815</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45061</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>45581.49583333333</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45054.85400462963</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>45714.80880787037</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>45754.52788194444</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>45747.78493055556</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>45747.79938657407</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45349</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>45372.68917824074</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>44466.48996527777</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45761</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>45250.44863425926</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>44937.71841435185</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>45629</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45103.67451388889</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45747</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45610.59956018518</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>45610.60157407408</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>45713</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>44620.45334490741</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>45218.47658564815</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>44819.34596064815</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45684.34594907407</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45020</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>45152</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>45334</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>45097</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>45750.94241898148</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45604.47508101852</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>45131</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45742.36822916667</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>45628.49322916667</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45483</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45714.84204861111</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>45603</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>44281</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>45425.69540509259</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45735.46643518518</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
         <v>45301.98247685185</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21992,7 +21992,7 @@
         <v>44874</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45742.61196759259</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>45324.71243055556</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45735.45677083333</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45602</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>44985</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>45698</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>45533</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>45733.43582175926</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45733.44309027777</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45733.57615740741</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45733.60265046296</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>45005</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45266</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45510.89869212963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>45301.98100694444</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22909,7 +22909,7 @@
         <v>45441</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>44820.47260416667</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>45131</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45617.72069444445</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>44617</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45713</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45713.62074074074</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>45188</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>45672.78414351852</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>45615.57407407407</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>45033</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>45307</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45764.52859953704</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45764.48869212963</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>45345</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45181</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45097</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>45356.68475694444</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>44886.51197916667</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44883</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>45758.73520833333</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>45656.78329861111</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45264.68074074074</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>45111</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24292,7 +24292,7 @@
         <v>44895</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>44895</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>44895.58759259259</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>45110</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>45630.32984953704</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>45546.84908564815</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45226.43175925926</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45188.62355324074</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>45306</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45548.38636574074</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>44985</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>44985</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45048</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>45679.49804398148</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>45394.73528935185</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>44995.44344907408</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>45562</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>45773.44608796296</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>45594</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>44078</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>44959.62519675926</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45170</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45762</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>44881</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45272.62565972222</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>45741.47434027777</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         <v>45272</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>45754.56905092593</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>44235</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45713</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45620.46207175926</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>45639</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>45639.58114583333</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44924</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>45628.43445601852</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45643.45525462963</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44823.61398148148</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44657</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>45359.50601851852</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>45600</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>45281.62631944445</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44886</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>45735.46112268518</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>45265.48799768519</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45179</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45756.29621527778</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44160</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44260</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45749.56019675926</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45561.7159837963</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44634</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>45401.69138888889</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>45637.54557870371</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>45610.42850694444</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>45099</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>45099.91826388889</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45747.39719907408</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>44999.50538194444</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>44330.36730324074</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>44900</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>45719</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45301.98575231482</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45637</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45164</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45593</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44508</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45629</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>44858.63208333333</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>45441</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>45775.87377314815</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45534.67689814815</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>45775.87576388889</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>45777.73621527778</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>45777.72737268519</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>45708.48537037037</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>45181.56171296296</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>44852.89560185185</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>44917</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>45483</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44634</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>45617.49510416666</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>44959</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44181</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44435.41690972223</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>45783.71136574074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>45782.33971064815</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>45226.44923611111</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45783.7002662037</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45672.58387731481</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>45396.86226851852</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>45783.74034722222</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>45021</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>45223</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45783.67510416666</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>44882</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>45783.73440972222</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>45714.80106481481</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>45145.58085648148</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>44923</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>44946.62486111111</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>45730.63616898148</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>45700.69467592592</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>45783.72262731481</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>45783.70811342593</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45783.71869212963</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45783.7308912037</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         <v>45239</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>44847.46701388889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>45512.53300925926</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>44851.61237268519</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>45784.74020833334</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>45026</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>44742.71030092592</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45708.4921412037</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45610</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>45236</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45707.66030092593</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45279</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>44974</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45628.46613425926</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>44587.40662037037</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45161</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>45475</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>45734.55042824074</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45372.36653935185</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>45315.65311342593</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>44959.68709490741</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>44959</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>45188.4716550926</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44380</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44380</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>45103</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>45461</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45747.39269675926</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31995,7 +31995,7 @@
         <v>45747.39408564815</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>45747.78081018518</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>45278.88578703703</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>44706</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>45145.57798611111</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>45163.37561342592</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>45644.02509259259</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>45638</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32461,7 +32461,7 @@
         <v>45789.70107638889</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>45166.62002314815</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>45036.6734375</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32632,7 +32632,7 @@
         <v>45756.29003472222</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>45510.89385416666</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         <v>45593</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>44817</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45615.6362037037</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>45483</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45483</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>44421.51063657407</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>44151</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33150,7 +33150,7 @@
         <v>45709.64976851852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>45628.44303240741</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>44146</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>45181</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>45681.62265046296</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         <v>45390</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>44551.38699074074</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>45267.46962962963</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>45744.56912037037</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45510</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>45628.56518518519</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45183.65436342593</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>45204.32359953703</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>44971.69971064815</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33953,7 +33953,7 @@
         <v>45272</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>44750</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>45106.89616898148</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>45510</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45274.57935185185</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>45720.31155092592</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>45446</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>45720.3175462963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34409,7 +34409,7 @@
         <v>45084.51329861111</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>45701.58163194444</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>45701.60341435186</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>45792.30664351852</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>45792.32596064815</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>45793.56537037037</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>45724</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>44126</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>45121.70020833334</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>45188</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45056.31962962963</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>45792.33170138889</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45621</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45272</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>45596.57131944445</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>44927.74953703704</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>45246</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>45700.66474537037</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>45796.56827546296</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>45796.60440972223</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>45470.64299768519</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>45470.64894675926</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>45796.55706018519</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>45796.56221064815</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>44384.39820601852</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>45797</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45712.57320601852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45079</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>45604.54047453704</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44802</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45216.52173611111</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44186</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>45734.57873842592</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45596.44083333333</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45260.32738425926</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45240.67206018518</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45275.30907407407</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>45796.58149305556</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>45441</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>45593</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>44825.46825231481</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>45796.36819444445</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>45796.38582175926</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36905,7 +36905,7 @@
         <v>45796.38944444444</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>44376</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45686.54246527778</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37081,7 +37081,7 @@
         <v>45686.60648148148</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>45686.63332175926</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>44361.5662962963</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>45769.33756944445</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>45119.63947916667</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>45281.63481481482</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>45799.40628472222</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>45273</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45274</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45081</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>45162.65574074074</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>45350.91678240741</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>45350.91932870371</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>45667.4771412037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>45546.84695601852</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45463</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>45202.38372685185</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>45126</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>44158</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>44928</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45656.78905092592</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>44860.93721064815</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>44582.42422453704</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45205</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45215.7849074074</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45561.88243055555</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45798.50189814815</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45055.49951388889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45349.39254629629</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45152.37778935185</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>45739.84453703704</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45686.60939814815</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45305.57791666667</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45567.33017361111</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>44915</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45610.61537037037</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45162</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>44251</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45562.55799768519</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39324,7 +39324,7 @@
         <v>44140</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>45183.65034722222</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39443,7 +39443,7 @@
         <v>45156</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>45253</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45645.58603009259</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39619,7 +39619,7 @@
         <v>45509.66609953704</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45726.51144675926</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>45804.6612962963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45749.56623842593</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>44886</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45593</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45317</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45168.33028935185</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>45805.31606481481</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>45805.27396990741</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>45805.27778935185</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>45748.86240740741</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45804.66229166667</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45804</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>45805.27659722222</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45602.91650462963</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>45614.50349537037</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>45614.505625</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         <v>45012</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>45394.35633101852</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45092.71057870371</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>45852.75837962963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>44810.52567129629</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>44908</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>44573</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41094,7 +41094,7 @@
         <v>45811.55042824074</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>45811.56310185185</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>45146.71684027778</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45079</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>45852.33880787037</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>44551</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>45620.82185185186</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45264.68416666667</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>45412</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>45097</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>44075</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>45811.39115740741</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>45811.39695601852</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>45811.40674768519</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>45236.35502314815</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>44960.36971064815</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>45811.48321759259</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>45811.4892824074</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>45811.57001157408</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>44809</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>45811.56517361111</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45148.62439814815</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>45188.49305555555</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45005</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>44938</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>44908</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>44946.42413194444</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>44945.35765046296</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45482</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45357</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45594.62881944444</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>44712</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45217.3809837963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45686.3184375</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45684.34170138889</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45684.34384259259</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45757.94755787037</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45205.39787037037</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>45205</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43342,7 +43342,7 @@
         <v>45747.39516203704</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43404,7 +43404,7 @@
         <v>45567.37547453704</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43461,7 +43461,7 @@
         <v>45567</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>44603.63212962963</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>44603</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>44603.6434375</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45371.85761574074</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>44070</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45618.61243055556</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45610.60369212963</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45646.67438657407</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45191.55503472222</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45812.59082175926</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45271</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>44942</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>45562.53543981481</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>45509</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>44908</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>44993</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45510</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45247.46569444444</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45677.37925925926</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44616,7 +44616,7 @@
         <v>44160</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>45162.588125</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>45817.39133101852</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>45358</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>45686.51583333333</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>45817.39481481481</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44958,7 +44958,7 @@
         <v>45568.46310185185</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>45817</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45072,7 +45072,7 @@
         <v>44978.59528935186</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>44144</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45212</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>45762.60217592592</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>45518</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>44266</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>45818.66446759259</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>44174</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45629</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45590,7 +45590,7 @@
         <v>45818</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>45818.66649305556</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45704,7 +45704,7 @@
         <v>45617.54989583333</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>45525</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>45225.63304398148</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45225.63777777777</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45099</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45119</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45860</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45301</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45527.44498842592</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45715.56667824074</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>44810.49734953704</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46331,7 +46331,7 @@
         <v>45280</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>45257.57825231482</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45119.58694444445</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>45820</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46564,7 +46564,7 @@
         <v>44454</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46621,7 +46621,7 @@
         <v>45012</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46678,7 +46678,7 @@
         <v>45702.6033912037</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46735,7 +46735,7 @@
         <v>45470</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46792,7 +46792,7 @@
         <v>45126</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>45824.61681712963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46906,7 +46906,7 @@
         <v>45645.58436342593</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>44894.63579861111</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47020,7 +47020,7 @@
         <v>45280</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
         <v>45093</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45084.67444444444</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>45722.31061342593</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47253,7 +47253,7 @@
         <v>45188</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47310,7 +47310,7 @@
         <v>45676.57688657408</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>45483</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47424,7 +47424,7 @@
         <v>45260</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47481,7 +47481,7 @@
         <v>45825.65555555555</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47538,7 +47538,7 @@
         <v>45646.67726851852</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47595,7 +47595,7 @@
         <v>45632.51193287037</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47652,7 +47652,7 @@
         <v>45647</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47709,7 +47709,7 @@
         <v>45647</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45647</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47823,7 +47823,7 @@
         <v>45647</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47880,7 +47880,7 @@
         <v>44181</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>45824.55555555555</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47994,7 +47994,7 @@
         <v>45824.61572916667</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48051,7 +48051,7 @@
         <v>45754.52563657407</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48108,7 +48108,7 @@
         <v>45754.52998842593</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>44806.59946759259</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>45212</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48279,7 +48279,7 @@
         <v>45826</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>45126</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>45339.66177083334</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45617.68131944445</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45328</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45211.63712962963</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45642.57581018518</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45359.49635416667</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45826</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45826.47586805555</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>45793.65984953703</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>45197</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48963,7 +48963,7 @@
         <v>45645.40951388889</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49020,7 +49020,7 @@
         <v>45826.41267361111</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>44923</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49134,7 +49134,7 @@
         <v>45700.51605324074</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49191,7 +49191,7 @@
         <v>45372.7019212963</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49248,7 +49248,7 @@
         <v>45707.64956018519</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>45707.66369212963</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49362,7 +49362,7 @@
         <v>45869</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49424,7 +49424,7 @@
         <v>45831.36892361111</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49481,7 +49481,7 @@
         <v>44446</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>45121.35078703704</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49595,7 +49595,7 @@
         <v>45831.3978587963</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49652,7 +49652,7 @@
         <v>45831.56630787037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>45831.36045138889</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49766,7 +49766,7 @@
         <v>45831.3783912037</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49823,7 +49823,7 @@
         <v>44441</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49880,7 +49880,7 @@
         <v>45343.92605324074</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49937,7 +49937,7 @@
         <v>45831.34712962963</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49994,7 +49994,7 @@
         <v>45869</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50056,7 +50056,7 @@
         <v>45831</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>45831</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50170,7 +50170,7 @@
         <v>45831.35077546296</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>44487</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>45831.57793981482</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50341,7 +50341,7 @@
         <v>45869</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>44743.61965277778</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>44991.53373842593</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50517,7 +50517,7 @@
         <v>45334</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>45112</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
         <v>45604.4971412037</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45869</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50755,7 +50755,7 @@
         <v>45875.64696759259</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50812,7 +50812,7 @@
         <v>45833.73708333333</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45035</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45614.44239583334</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50983,7 +50983,7 @@
         <v>45832.28081018518</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>44903.53118055555</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>44851.60855324074</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>45874.65034722222</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51216,7 +51216,7 @@
         <v>45243</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>44988</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>45833.74201388889</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51387,7 +51387,7 @@
         <v>45705.65206018519</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         <v>45647</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>45647</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>45647</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51615,7 +51615,7 @@
         <v>44670.43472222222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>45877.42953703704</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51729,7 +51729,7 @@
         <v>45875.6449537037</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51786,7 +51786,7 @@
         <v>45875.45658564815</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51843,7 +51843,7 @@
         <v>45530</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>45530.69050925926</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51957,7 +51957,7 @@
         <v>45137.90618055555</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52014,7 +52014,7 @@
         <v>45089</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>45684.45225694445</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45356.68585648148</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>44124.48305555555</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45712</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45769.36023148148</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45323</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52423,7 +52423,7 @@
         <v>45373.59099537037</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>45567</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52537,7 +52537,7 @@
         <v>45754.38893518518</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52594,7 +52594,7 @@
         <v>45167.68207175926</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52651,7 +52651,7 @@
         <v>45754.57372685185</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52708,7 +52708,7 @@
         <v>45470</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52765,7 +52765,7 @@
         <v>44090</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52822,7 +52822,7 @@
         <v>44180</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>44740.92936342592</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52936,7 +52936,7 @@
         <v>45272</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52993,7 +52993,7 @@
         <v>45440.4658449074</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53050,7 +53050,7 @@
         <v>45758.72209490741</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53107,7 +53107,7 @@
         <v>45758.73298611111</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>44337.48540509259</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53221,7 +53221,7 @@
         <v>45207.49881944444</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53278,7 +53278,7 @@
         <v>45077</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53335,7 +53335,7 @@
         <v>45481.49108796296</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         <v>45069.48967592593</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53449,7 +53449,7 @@
         <v>44924.66556712963</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53506,7 +53506,7 @@
         <v>45645</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53563,7 +53563,7 @@
         <v>44357.34482638889</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>45876.62177083334</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53677,7 +53677,7 @@
         <v>44656.61335648148</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>45085.93778935185</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>45835.40136574074</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>45835.39804398148</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53905,7 +53905,7 @@
         <v>45880.56395833333</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53962,7 +53962,7 @@
         <v>45881</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>45355.4612037037</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>45621</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>45881.66684027778</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54190,7 +54190,7 @@
         <v>45838.66364583333</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54247,7 +54247,7 @@
         <v>45645.58762731482</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>44160</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>44991.34855324074</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45880</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54475,7 +54475,7 @@
         <v>45881.31761574074</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54532,7 +54532,7 @@
         <v>45126</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54589,7 +54589,7 @@
         <v>45253.54356481481</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54646,7 +54646,7 @@
         <v>45837.87837962963</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54703,7 +54703,7 @@
         <v>45837.90292824074</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54760,7 +54760,7 @@
         <v>45837.90488425926</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54817,7 +54817,7 @@
         <v>45593</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>44810.56070601852</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>44923.65486111111</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45880.86574074074</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55050,7 +55050,7 @@
         <v>45838.65454861111</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>45162.32709490741</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         <v>45837.91177083334</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         <v>45187.48282407408</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>44908</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55340,7 +55340,7 @@
         <v>45076.30560185185</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>44896.30818287037</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55454,7 +55454,7 @@
         <v>45838.65708333333</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55511,7 +55511,7 @@
         <v>45524.49138888889</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55568,7 +55568,7 @@
         <v>45246.77350694445</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55625,7 +55625,7 @@
         <v>45370.34275462963</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>45215.48378472222</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55739,7 +55739,7 @@
         <v>45546.85369212963</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55801,7 +55801,7 @@
         <v>45840.5487037037</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55858,7 +55858,7 @@
         <v>44424</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55915,7 +55915,7 @@
         <v>45755.48740740741</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55972,7 +55972,7 @@
         <v>45099</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56029,7 +56029,7 @@
         <v>44628.47715277778</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56086,7 +56086,7 @@
         <v>45656.73612268519</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56143,7 +56143,7 @@
         <v>45119.57798611111</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56200,7 +56200,7 @@
         <v>45646</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56257,7 +56257,7 @@
         <v>45033</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56314,7 +56314,7 @@
         <v>45840.55074074074</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56371,7 +56371,7 @@
         <v>44988.85038194444</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56428,7 +56428,7 @@
         <v>44180</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56485,7 +56485,7 @@
         <v>45841.57072916667</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>45734.93418981481</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56599,7 +56599,7 @@
         <v>45634</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56656,7 +56656,7 @@
         <v>44585</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56713,7 +56713,7 @@
         <v>45701.59954861111</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>45845</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>44999.50461805556</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56884,7 +56884,7 @@
         <v>45845</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56941,7 +56941,7 @@
         <v>45842.62019675926</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56998,7 +56998,7 @@
         <v>45842.62362268518</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57055,7 +57055,7 @@
         <v>44887</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57112,7 +57112,7 @@
         <v>45635.84936342593</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57169,7 +57169,7 @@
         <v>44868.56361111111</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57226,7 +57226,7 @@
         <v>45188.49987268518</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57283,7 +57283,7 @@
         <v>45842.45201388889</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57340,7 +57340,7 @@
         <v>45126</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57397,7 +57397,7 @@
         <v>44565.57157407407</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57454,7 +57454,7 @@
         <v>45188.61378472222</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57511,7 +57511,7 @@
         <v>44991.35916666667</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57568,7 +57568,7 @@
         <v>44991</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57625,7 +57625,7 @@
         <v>45884.73457175926</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57682,7 +57682,7 @@
         <v>45546</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57739,7 +57739,7 @@
         <v>45845.48228009259</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57796,7 +57796,7 @@
         <v>45845.48898148148</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57853,7 +57853,7 @@
         <v>45723.54547453704</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57910,7 +57910,7 @@
         <v>44651</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57967,7 +57967,7 @@
         <v>45366.32900462963</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58024,7 +58024,7 @@
         <v>45811.48709490741</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58081,7 +58081,7 @@
         <v>45884.62045138889</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58138,7 +58138,7 @@
         <v>45775.40460648148</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58195,7 +58195,7 @@
         <v>45069.64322916666</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58252,7 +58252,7 @@
         <v>45764.48725694444</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58309,7 +58309,7 @@
         <v>45748.90723379629</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58366,7 +58366,7 @@
         <v>45888.34261574074</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58423,7 +58423,7 @@
         <v>45195.85546296297</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58480,7 +58480,7 @@
         <v>45888.58818287037</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58537,7 +58537,7 @@
         <v>45847</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58594,7 +58594,7 @@
         <v>45323</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58656,7 +58656,7 @@
         <v>45847.3721412037</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58713,7 +58713,7 @@
         <v>45730.61275462963</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58770,7 +58770,7 @@
         <v>45715.5681712963</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58827,7 +58827,7 @@
         <v>45070</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58884,7 +58884,7 @@
         <v>45847.67734953704</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58941,7 +58941,7 @@
         <v>45847.67871527778</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58998,7 +58998,7 @@
         <v>44634.60929398148</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59055,7 +59055,7 @@
         <v>45231</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59112,7 +59112,7 @@
         <v>45012</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59169,7 +59169,7 @@
         <v>45891.64818287037</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59226,7 +59226,7 @@
         <v>45891.65295138889</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59283,7 +59283,7 @@
         <v>44991.51193287037</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59340,7 +59340,7 @@
         <v>44991</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59397,7 +59397,7 @@
         <v>45727.34787037037</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59454,7 +59454,7 @@
         <v>44098</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59511,7 +59511,7 @@
         <v>45181.58791666666</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59568,7 +59568,7 @@
         <v>45530</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59625,7 +59625,7 @@
         <v>44812</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59682,7 +59682,7 @@
         <v>45888</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59739,7 +59739,7 @@
         <v>45679.48483796296</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59796,7 +59796,7 @@
         <v>44187</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59853,7 +59853,7 @@
         <v>45441.54350694444</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59910,7 +59910,7 @@
         <v>45647</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59967,7 +59967,7 @@
         <v>45205</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60024,7 +60024,7 @@
         <v>45742.89054398148</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60081,7 +60081,7 @@
         <v>45889.93328703703</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60138,7 +60138,7 @@
         <v>45848.61030092592</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60195,7 +60195,7 @@
         <v>44959</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60252,7 +60252,7 @@
         <v>44959</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60309,7 +60309,7 @@
         <v>45187.59305555555</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60366,7 +60366,7 @@
         <v>45176</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60428,7 +60428,7 @@
         <v>45181</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60485,7 +60485,7 @@
         <v>45891.65096064815</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60542,7 +60542,7 @@
         <v>45890.37820601852</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60599,7 +60599,7 @@
         <v>45714.80385416667</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>44523.46746527778</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60713,7 +60713,7 @@
         <v>45848.6062962963</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60770,7 +60770,7 @@
         <v>45168.33265046297</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60827,7 +60827,7 @@
         <v>45224.70244212963</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60884,7 +60884,7 @@
         <v>45097</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60941,7 +60941,7 @@
         <v>45685.35516203703</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -60998,7 +60998,7 @@
         <v>44980.62431712963</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>44129</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         <v>44573</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61174,7 +61174,7 @@
         <v>45463.39309027778</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61231,7 +61231,7 @@
         <v>45614.63012731481</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61293,7 +61293,7 @@
         <v>44810</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61350,7 +61350,7 @@
         <v>45231</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61407,7 +61407,7 @@
         <v>45035</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61464,7 +61464,7 @@
         <v>45077.43420138889</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61521,7 +61521,7 @@
         <v>44809.39893518519</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61578,7 +61578,7 @@
         <v>44945.34497685185</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -61635,7 +61635,7 @@
         <v>45594.62287037037</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45594.6306712963</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -61749,7 +61749,7 @@
         <v>44820</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61806,7 +61806,7 @@
         <v>44721.70876157407</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61863,7 +61863,7 @@
         <v>45410</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61920,7 +61920,7 @@
         <v>45679.47949074074</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -61977,7 +61977,7 @@
         <v>45476.50119212963</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62034,7 +62034,7 @@
         <v>45476.50480324074</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62091,7 +62091,7 @@
         <v>45300</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62148,7 +62148,7 @@
         <v>45210</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62205,7 +62205,7 @@
         <v>44903</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62262,7 +62262,7 @@
         <v>45735.66598379629</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62324,7 +62324,7 @@
         <v>45065</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62381,7 +62381,7 @@
         <v>45111</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62438,7 +62438,7 @@
         <v>45672.46096064815</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62495,7 +62495,7 @@
         <v>44846.55085648148</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62552,7 +62552,7 @@
         <v>44894.45888888889</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -62609,7 +62609,7 @@
         <v>45772.59259259259</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -62666,7 +62666,7 @@
         <v>44848.30996527777</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -62723,7 +62723,7 @@
         <v>45775.58704861111</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62780,7 +62780,7 @@
         <v>45224.59289351852</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62837,7 +62837,7 @@
         <v>45089</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62894,7 +62894,7 @@
         <v>44565</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -62951,7 +62951,7 @@
         <v>44565.61265046296</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63008,7 +63008,7 @@
         <v>45236.68318287037</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63065,7 +63065,7 @@
         <v>45730.6487037037</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63122,7 +63122,7 @@
         <v>45068.45921296296</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63179,7 +63179,7 @@
         <v>45315.65375</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63236,7 +63236,7 @@
         <v>44272</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -567,7 +567,7 @@
         <v>45105</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44735</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>45568</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>45820</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>44216</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44343</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>45533</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45357</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>44610</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45194</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>45701.89549768518</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>45224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>45078</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>44258</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>45078</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>45733.64422453703</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>45211</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44151</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44271.71099537037</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44448</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44679</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>44825.70888888889</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44524</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>44495</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44809.40431712963</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44582</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45372.69723379629</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>44461</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>45476.50744212963</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>45749.46063657408</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>44645</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45686.57611111111</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>45558.62674768519</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45181</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>44928</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45274.32131944445</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>45282</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45086</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>45819</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44232</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>45005</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>45642.60756944444</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>45754</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45111</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45527.45695601852</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>44985</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>45555.65903935185</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44082.65943287037</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>44231</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>44357.34326388889</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>44467.6135300926</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44571.63828703704</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44431</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>44309.65885416666</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>44715.33956018519</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>44811.66311342592</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>44119</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>44568</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>44186</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44853.50333333333</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44307.481875</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44508.43092592592</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>44622</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>44272</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>44152</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44271</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44134</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44285.5874537037</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44327.59131944444</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44357</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>44245</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>44224</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44441</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44230</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>44410</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44125.62782407407</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44459</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>44194</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44297</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44510.88893518518</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44809.54884259259</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>44607</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44721.65634259259</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44461</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44461.57160879629</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>44510</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44818</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>44848.3015625</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44297</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>44258</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44277.6141087963</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44230</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44635.93181712963</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>44125</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44503.73802083333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44510.63989583333</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44386.6371412037</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44592.65864583333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>44587.59076388889</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44742.95375</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>44370.39163194445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>44650.495</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44623.46204861111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44714</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44847</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>44847</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44084</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>44257.83641203704</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>44292</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44749</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>44186</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44460</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>44441</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44441</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>44468</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44258</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44460</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>44404</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44259</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44474</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44880.48260416667</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44837.42782407408</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44110</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44861</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44273.62519675926</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44245</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44140</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44221</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44304</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>44482</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>44315</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>44145</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>44806.68451388889</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>44476</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>44476.58800925926</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44211</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44502.34869212963</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>44461.69494212963</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>44267</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>44165</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>44137.73322916667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>44459</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>44441</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>44515</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>44495.68931712963</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>44169</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>44715</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44381</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44384.39226851852</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>44476</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>44169</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44130</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>44576</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>44229</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>44426.34618055556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44421</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>44295</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44882.66891203704</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44449</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44882.6740162037</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>44888.69445601852</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44075</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>44175</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>44322.68579861111</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>44187.74415509259</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44321.51725694445</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>44825.35965277778</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>44460.62309027778</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44147.70520833333</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44363</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44203</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44229</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44764</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44817</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44537.63180555555</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44806</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44712.30428240741</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44809.39019675926</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44165</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44806</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>44820.47135416666</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44606</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44739.3564699074</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44810</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44173</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44565.61417824074</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>44146</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44417.77873842593</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>44369.93123842592</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44610.3157175926</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>44186</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44277.60974537037</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44084</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44446</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44357.34568287037</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44371</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44420.65103009259</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>44246</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44742.71378472223</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>44265</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>44448.45023148148</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>44448</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44715.33355324074</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>44169</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>44127.46831018518</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>44515</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>44592.65989583333</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>44760.74060185185</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>44187</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>44109</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>44069</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>44517</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>44595</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>44204</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>44530</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44228</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>44732.43689814815</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>44237</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>44469</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>44879.61497685185</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>44280</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44295.77248842592</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44497.430625</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44070</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44469</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>44831</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44621.66707175926</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>44495.69234953704</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44209</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44228</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45672.591875</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44152</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44550</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>45748.59457175926</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>45748.91101851852</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>44384.46910879629</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>44536</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>45187</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>45607.36863425926</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>44810.40475694444</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>44810.35575231481</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45775.59978009259</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>45775.60414351852</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45615.57574074074</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44538.40638888889</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>45075.53265046296</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>45572.67497685185</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>44588</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45470</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45594.61994212963</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>44929</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>45614.50907407407</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>44850</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>44515</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>45602.65810185186</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45339</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45097</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44152</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45594.6255787037</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44764</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45103</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>44104</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45223</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>45223</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44845</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>45169</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45715</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         <v>45279</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>44862.38081018518</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>45071.55216435185</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>45071.55913194444</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45097</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45727</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45614.49559027778</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45211.63446759259</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>45275</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>44642.83407407408</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>45109</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>45595.4272337963</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>45359.50059027778</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>44867</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>44852</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>45726.54469907407</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>45301.83475694444</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>44712.32885416667</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45082</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45065</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45195.85668981481</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>45071.54651620371</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45071.54908564815</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>44825.46571759259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>44928.45686342593</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>44881</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45225.49447916666</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>45116.79090277778</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45116.79268518519</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>44377</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45068.66135416667</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45610.36342592593</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>44448</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>45705.5654050926</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>45156</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>45701.90762731482</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>45218.86829861111</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45628.48590277778</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45551</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45749.53158564815</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>44971.45475694445</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>44974.57127314815</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45061</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>45581.49583333333</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45054.85400462963</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>45714.80880787037</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>45754.52788194444</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>45747.78493055556</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>45747.79938657407</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45349</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>45372.68917824074</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>44466.48996527777</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45761</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>45250.44863425926</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>44937.71841435185</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>45629</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45103.67451388889</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45747</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45610.59956018518</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>45610.60157407408</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>45713</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>44620.45334490741</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>45218.47658564815</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>44819.34596064815</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45684.34594907407</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45020</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>45152</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>45334</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>45097</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>45750.94241898148</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45604.47508101852</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>45131</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45742.36822916667</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>45628.49322916667</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45483</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45714.84204861111</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>45603</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>44281</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>45425.69540509259</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45735.46643518518</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
         <v>45301.98247685185</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21992,7 +21992,7 @@
         <v>44874</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45742.61196759259</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>45324.71243055556</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45735.45677083333</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45602</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>44985</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>45698</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>45533</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>45733.43582175926</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45733.44309027777</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45733.57615740741</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45733.60265046296</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>45005</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45266</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45510.89869212963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>45301.98100694444</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22909,7 +22909,7 @@
         <v>45441</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>44820.47260416667</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>45131</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45617.72069444445</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>44617</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45713</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45713.62074074074</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>45188</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>45672.78414351852</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>45615.57407407407</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>45033</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>45307</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45764.52859953704</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45764.48869212963</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>45345</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45181</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45097</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>45356.68475694444</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>44886.51197916667</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44883</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>45758.73520833333</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>45656.78329861111</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45264.68074074074</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>45111</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24292,7 +24292,7 @@
         <v>44895</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>44895</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>44895.58759259259</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>45110</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>45630.32984953704</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>45546.84908564815</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45226.43175925926</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45188.62355324074</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>45306</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45548.38636574074</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>44985</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>44985</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45048</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>45679.49804398148</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>45394.73528935185</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>44995.44344907408</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>45562</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>45773.44608796296</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>45594</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>44078</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>44959.62519675926</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45170</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45762</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>44881</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45272.62565972222</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>45741.47434027777</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         <v>45272</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>45754.56905092593</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>44235</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45713</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45620.46207175926</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>45639</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>45639.58114583333</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44924</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>45628.43445601852</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45643.45525462963</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44823.61398148148</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44657</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>45359.50601851852</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>45600</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>45281.62631944445</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44886</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>45735.46112268518</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>45265.48799768519</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45179</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45756.29621527778</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44160</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44260</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45749.56019675926</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45561.7159837963</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44634</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>45401.69138888889</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>45637.54557870371</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>45610.42850694444</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>45099</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>45099.91826388889</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45747.39719907408</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>44999.50538194444</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>44330.36730324074</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>44900</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>45719</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45301.98575231482</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45637</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45164</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45593</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44508</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45629</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>44858.63208333333</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>45441</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>45775.87377314815</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45534.67689814815</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>45775.87576388889</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>45777.73621527778</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>45777.72737268519</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>45708.48537037037</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>45181.56171296296</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>44852.89560185185</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>44917</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>45483</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44634</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>45617.49510416666</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>44959</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44181</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44435.41690972223</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>45783.71136574074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>45782.33971064815</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>45226.44923611111</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45783.7002662037</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45672.58387731481</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>45396.86226851852</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>45783.74034722222</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>45021</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>45223</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45783.67510416666</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>44882</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>45783.73440972222</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>45714.80106481481</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>45145.58085648148</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>44923</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>44946.62486111111</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>45730.63616898148</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>45700.69467592592</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>45783.72262731481</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>45783.70811342593</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45783.71869212963</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45783.7308912037</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         <v>45239</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>44847.46701388889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>45512.53300925926</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>44851.61237268519</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>45784.74020833334</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>45026</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>44742.71030092592</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45708.4921412037</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45610</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>45236</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45707.66030092593</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45279</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>44974</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45628.46613425926</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>44587.40662037037</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45161</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>45475</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>45734.55042824074</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45372.36653935185</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>45315.65311342593</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>44959.68709490741</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>44959</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>45188.4716550926</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44380</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44380</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>45103</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>45461</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45747.39269675926</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31995,7 +31995,7 @@
         <v>45747.39408564815</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>45747.78081018518</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>45278.88578703703</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>44706</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>45145.57798611111</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>45163.37561342592</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>45644.02509259259</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>45638</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32461,7 +32461,7 @@
         <v>45789.70107638889</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>45166.62002314815</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>45036.6734375</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32632,7 +32632,7 @@
         <v>45756.29003472222</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>45510.89385416666</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         <v>45593</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>44817</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45615.6362037037</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>45483</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45483</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>44421.51063657407</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>44151</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33150,7 +33150,7 @@
         <v>45709.64976851852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>45628.44303240741</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>44146</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>45181</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>45681.62265046296</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         <v>45390</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>44551.38699074074</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>45267.46962962963</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>45744.56912037037</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45510</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>45628.56518518519</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45183.65436342593</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>45204.32359953703</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>44971.69971064815</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33953,7 +33953,7 @@
         <v>45272</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>44750</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>45106.89616898148</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>45510</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45274.57935185185</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>45720.31155092592</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>45446</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>45720.3175462963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34409,7 +34409,7 @@
         <v>45084.51329861111</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>45701.58163194444</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>45701.60341435186</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>45792.30664351852</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>45792.32596064815</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>45793.56537037037</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>45724</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>44126</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>45121.70020833334</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>45188</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45056.31962962963</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>45792.33170138889</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45621</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45272</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>45596.57131944445</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>44927.74953703704</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>45246</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>45700.66474537037</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>45796.56827546296</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>45796.60440972223</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>45470.64299768519</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>45470.64894675926</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>45796.55706018519</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>45796.56221064815</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>44384.39820601852</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>45797</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45712.57320601852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45079</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>45604.54047453704</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44802</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45216.52173611111</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44186</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>45734.57873842592</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45596.44083333333</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45260.32738425926</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45240.67206018518</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45275.30907407407</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>45796.58149305556</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>45441</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>45593</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>44825.46825231481</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>45796.36819444445</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>45796.38582175926</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36905,7 +36905,7 @@
         <v>45796.38944444444</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>44376</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45686.54246527778</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37081,7 +37081,7 @@
         <v>45686.60648148148</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>45686.63332175926</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>44361.5662962963</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>45769.33756944445</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>45119.63947916667</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>45281.63481481482</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>45799.40628472222</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>45273</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45274</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45081</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>45162.65574074074</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>45350.91678240741</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>45350.91932870371</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>45667.4771412037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>45546.84695601852</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45463</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>45202.38372685185</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>45126</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>44158</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>44928</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45656.78905092592</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>44860.93721064815</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>44582.42422453704</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45205</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45215.7849074074</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45561.88243055555</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45798.50189814815</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45055.49951388889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45349.39254629629</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45152.37778935185</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>45739.84453703704</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45686.60939814815</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45305.57791666667</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45567.33017361111</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>44915</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45610.61537037037</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45162</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>44251</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45562.55799768519</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39324,7 +39324,7 @@
         <v>44140</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>45183.65034722222</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39443,7 +39443,7 @@
         <v>45156</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>45253</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45645.58603009259</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39619,7 +39619,7 @@
         <v>45509.66609953704</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45726.51144675926</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>45804.6612962963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45749.56623842593</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>44886</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45593</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45317</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45168.33028935185</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>45805.31606481481</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>45805.27396990741</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>45805.27778935185</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>45748.86240740741</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45804.66229166667</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45804</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>45805.27659722222</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45602.91650462963</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>45614.50349537037</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>45614.505625</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         <v>45012</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>45394.35633101852</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45092.71057870371</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>45852.75837962963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>44810.52567129629</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>44908</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>44573</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41094,7 +41094,7 @@
         <v>45811.55042824074</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>45811.56310185185</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>45146.71684027778</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45079</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>45852.33880787037</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>44551</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>45620.82185185186</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45264.68416666667</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>45412</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>45097</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>44075</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>45811.39115740741</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>45811.39695601852</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>45811.40674768519</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>45236.35502314815</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>44960.36971064815</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>45811.48321759259</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>45811.4892824074</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>45811.57001157408</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>44809</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>45811.56517361111</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45148.62439814815</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>45188.49305555555</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45005</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>44938</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>44908</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>44946.42413194444</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>44945.35765046296</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45482</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45357</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45594.62881944444</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>44712</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45217.3809837963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45686.3184375</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45684.34170138889</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45684.34384259259</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45757.94755787037</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45205.39787037037</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>45205</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43342,7 +43342,7 @@
         <v>45747.39516203704</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43404,7 +43404,7 @@
         <v>45567.37547453704</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43461,7 +43461,7 @@
         <v>45567</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>44603.63212962963</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>44603</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>44603.6434375</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45371.85761574074</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>44070</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45618.61243055556</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45610.60369212963</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45646.67438657407</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45191.55503472222</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45812.59082175926</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45271</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>44942</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>45562.53543981481</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>45509</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>44908</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>44993</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45510</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45247.46569444444</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45677.37925925926</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44616,7 +44616,7 @@
         <v>44160</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>45162.588125</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>45817.39133101852</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>45358</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>45686.51583333333</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>45817.39481481481</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44958,7 +44958,7 @@
         <v>45568.46310185185</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>45817</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45072,7 +45072,7 @@
         <v>44978.59528935186</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>44144</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45212</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>45762.60217592592</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>45518</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>44266</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>45818.66446759259</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>44174</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45629</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45590,7 +45590,7 @@
         <v>45818</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>45818.66649305556</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45704,7 +45704,7 @@
         <v>45617.54989583333</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>45525</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>45225.63304398148</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45225.63777777777</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45099</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45119</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45860</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45301</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45527.44498842592</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45715.56667824074</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>44810.49734953704</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46331,7 +46331,7 @@
         <v>45280</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>45257.57825231482</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45119.58694444445</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>45820</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46564,7 +46564,7 @@
         <v>44454</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46621,7 +46621,7 @@
         <v>45012</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46678,7 +46678,7 @@
         <v>45702.6033912037</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46735,7 +46735,7 @@
         <v>45470</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46792,7 +46792,7 @@
         <v>45126</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>45824.61681712963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46906,7 +46906,7 @@
         <v>45645.58436342593</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>44894.63579861111</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47020,7 +47020,7 @@
         <v>45280</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
         <v>45093</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45084.67444444444</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>45722.31061342593</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47253,7 +47253,7 @@
         <v>45188</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47310,7 +47310,7 @@
         <v>45676.57688657408</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>45483</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47424,7 +47424,7 @@
         <v>45260</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47481,7 +47481,7 @@
         <v>45825.65555555555</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47538,7 +47538,7 @@
         <v>45646.67726851852</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47595,7 +47595,7 @@
         <v>45632.51193287037</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47652,7 +47652,7 @@
         <v>45647</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47709,7 +47709,7 @@
         <v>45647</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45647</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47823,7 +47823,7 @@
         <v>45647</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47880,7 +47880,7 @@
         <v>44181</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>45824.55555555555</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47994,7 +47994,7 @@
         <v>45824.61572916667</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48051,7 +48051,7 @@
         <v>45754.52563657407</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48108,7 +48108,7 @@
         <v>45754.52998842593</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>44806.59946759259</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>45212</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48279,7 +48279,7 @@
         <v>45826</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>45126</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>45339.66177083334</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45617.68131944445</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45328</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45211.63712962963</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45642.57581018518</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45359.49635416667</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45826</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45826.47586805555</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>45793.65984953703</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>45197</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48963,7 +48963,7 @@
         <v>45645.40951388889</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49020,7 +49020,7 @@
         <v>45826.41267361111</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>44923</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49134,7 +49134,7 @@
         <v>45700.51605324074</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49191,7 +49191,7 @@
         <v>45372.7019212963</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49248,7 +49248,7 @@
         <v>45707.64956018519</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>45707.66369212963</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49362,7 +49362,7 @@
         <v>45869</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49424,7 +49424,7 @@
         <v>45831.36892361111</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49481,7 +49481,7 @@
         <v>44446</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>45121.35078703704</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49595,7 +49595,7 @@
         <v>45831.3978587963</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49652,7 +49652,7 @@
         <v>45831.56630787037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>45831.36045138889</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49766,7 +49766,7 @@
         <v>45831.3783912037</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49823,7 +49823,7 @@
         <v>44441</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49880,7 +49880,7 @@
         <v>45343.92605324074</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49937,7 +49937,7 @@
         <v>45831.34712962963</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49994,7 +49994,7 @@
         <v>45869</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50056,7 +50056,7 @@
         <v>45831</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>45831</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50170,7 +50170,7 @@
         <v>45831.35077546296</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>44487</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>45831.57793981482</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50341,7 +50341,7 @@
         <v>45869</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>44743.61965277778</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>44991.53373842593</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50517,7 +50517,7 @@
         <v>45334</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>45112</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
         <v>45604.4971412037</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45869</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50755,7 +50755,7 @@
         <v>45875.64696759259</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50812,7 +50812,7 @@
         <v>45833.73708333333</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45035</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45614.44239583334</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50983,7 +50983,7 @@
         <v>45832.28081018518</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>44903.53118055555</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>44851.60855324074</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>45874.65034722222</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51216,7 +51216,7 @@
         <v>45243</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>44988</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>45833.74201388889</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51387,7 +51387,7 @@
         <v>45705.65206018519</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         <v>45647</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>45647</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>45647</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51615,7 +51615,7 @@
         <v>44670.43472222222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>45877.42953703704</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51729,7 +51729,7 @@
         <v>45875.6449537037</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51786,7 +51786,7 @@
         <v>45875.45658564815</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51843,7 +51843,7 @@
         <v>45530</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>45530.69050925926</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51957,7 +51957,7 @@
         <v>45137.90618055555</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52014,7 +52014,7 @@
         <v>45089</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>45684.45225694445</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45356.68585648148</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>44124.48305555555</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45712</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45769.36023148148</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45323</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52423,7 +52423,7 @@
         <v>45373.59099537037</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>45567</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52537,7 +52537,7 @@
         <v>45754.38893518518</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52594,7 +52594,7 @@
         <v>45167.68207175926</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52651,7 +52651,7 @@
         <v>45754.57372685185</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52708,7 +52708,7 @@
         <v>45470</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52765,7 +52765,7 @@
         <v>44090</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52822,7 +52822,7 @@
         <v>44180</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>44740.92936342592</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52936,7 +52936,7 @@
         <v>45272</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52993,7 +52993,7 @@
         <v>45440.4658449074</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53050,7 +53050,7 @@
         <v>45758.72209490741</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53107,7 +53107,7 @@
         <v>45758.73298611111</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>44337.48540509259</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53221,7 +53221,7 @@
         <v>45207.49881944444</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53278,7 +53278,7 @@
         <v>45077</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53335,7 +53335,7 @@
         <v>45481.49108796296</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         <v>45069.48967592593</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53449,7 +53449,7 @@
         <v>44924.66556712963</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53506,7 +53506,7 @@
         <v>45645</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53563,7 +53563,7 @@
         <v>44357.34482638889</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>45876.62177083334</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53677,7 +53677,7 @@
         <v>44656.61335648148</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>45085.93778935185</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>45835.40136574074</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>45835.39804398148</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53905,7 +53905,7 @@
         <v>45880.56395833333</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53962,7 +53962,7 @@
         <v>45881</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>45355.4612037037</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>45621</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>45881.66684027778</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54190,7 +54190,7 @@
         <v>45838.66364583333</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54247,7 +54247,7 @@
         <v>45645.58762731482</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>44160</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>44991.34855324074</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45880</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54475,7 +54475,7 @@
         <v>45881.31761574074</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54532,7 +54532,7 @@
         <v>45126</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54589,7 +54589,7 @@
         <v>45253.54356481481</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54646,7 +54646,7 @@
         <v>45837.87837962963</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54703,7 +54703,7 @@
         <v>45837.90292824074</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54760,7 +54760,7 @@
         <v>45837.90488425926</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54817,7 +54817,7 @@
         <v>45593</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>44810.56070601852</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>44923.65486111111</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45880.86574074074</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55050,7 +55050,7 @@
         <v>45838.65454861111</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>45162.32709490741</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         <v>45837.91177083334</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         <v>45187.48282407408</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>44908</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55340,7 +55340,7 @@
         <v>45076.30560185185</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>44896.30818287037</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55454,7 +55454,7 @@
         <v>45838.65708333333</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55511,7 +55511,7 @@
         <v>45524.49138888889</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55568,7 +55568,7 @@
         <v>45246.77350694445</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55625,7 +55625,7 @@
         <v>45370.34275462963</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>45215.48378472222</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55739,7 +55739,7 @@
         <v>45546.85369212963</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55801,7 +55801,7 @@
         <v>45840.5487037037</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55858,7 +55858,7 @@
         <v>44424</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55915,7 +55915,7 @@
         <v>45755.48740740741</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55972,7 +55972,7 @@
         <v>45099</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56029,7 +56029,7 @@
         <v>44628.47715277778</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56086,7 +56086,7 @@
         <v>45656.73612268519</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56143,7 +56143,7 @@
         <v>45119.57798611111</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56200,7 +56200,7 @@
         <v>45646</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56257,7 +56257,7 @@
         <v>45033</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56314,7 +56314,7 @@
         <v>45840.55074074074</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56371,7 +56371,7 @@
         <v>44988.85038194444</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56428,7 +56428,7 @@
         <v>44180</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56485,7 +56485,7 @@
         <v>45841.57072916667</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>45734.93418981481</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56599,7 +56599,7 @@
         <v>45634</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56656,7 +56656,7 @@
         <v>44585</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56713,7 +56713,7 @@
         <v>45701.59954861111</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>45845</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>44999.50461805556</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56884,7 +56884,7 @@
         <v>45845</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56941,7 +56941,7 @@
         <v>45842.62019675926</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56998,7 +56998,7 @@
         <v>45842.62362268518</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57055,7 +57055,7 @@
         <v>44887</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57112,7 +57112,7 @@
         <v>45635.84936342593</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57169,7 +57169,7 @@
         <v>44868.56361111111</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57226,7 +57226,7 @@
         <v>45188.49987268518</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57283,7 +57283,7 @@
         <v>45842.45201388889</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57340,7 +57340,7 @@
         <v>45126</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57397,7 +57397,7 @@
         <v>44565.57157407407</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57454,7 +57454,7 @@
         <v>45188.61378472222</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57511,7 +57511,7 @@
         <v>44991.35916666667</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57568,7 +57568,7 @@
         <v>44991</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57625,7 +57625,7 @@
         <v>45884.73457175926</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57682,7 +57682,7 @@
         <v>45546</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57739,7 +57739,7 @@
         <v>45845.48228009259</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57796,7 +57796,7 @@
         <v>45845.48898148148</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57853,7 +57853,7 @@
         <v>45723.54547453704</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57910,7 +57910,7 @@
         <v>44651</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57967,7 +57967,7 @@
         <v>45366.32900462963</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58024,7 +58024,7 @@
         <v>45811.48709490741</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58081,7 +58081,7 @@
         <v>45884.62045138889</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58138,7 +58138,7 @@
         <v>45775.40460648148</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58195,7 +58195,7 @@
         <v>45069.64322916666</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58252,7 +58252,7 @@
         <v>45764.48725694444</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58309,7 +58309,7 @@
         <v>45748.90723379629</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58366,7 +58366,7 @@
         <v>45888.34261574074</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58423,7 +58423,7 @@
         <v>45195.85546296297</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58480,7 +58480,7 @@
         <v>45888.58818287037</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58537,7 +58537,7 @@
         <v>45847</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58594,7 +58594,7 @@
         <v>45323</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58656,7 +58656,7 @@
         <v>45847.3721412037</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58713,7 +58713,7 @@
         <v>45730.61275462963</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58770,7 +58770,7 @@
         <v>45715.5681712963</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58827,7 +58827,7 @@
         <v>45070</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58884,7 +58884,7 @@
         <v>45847.67734953704</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58941,7 +58941,7 @@
         <v>45847.67871527778</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58998,7 +58998,7 @@
         <v>44634.60929398148</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59055,7 +59055,7 @@
         <v>45231</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59112,7 +59112,7 @@
         <v>45012</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59169,7 +59169,7 @@
         <v>45891.64818287037</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59226,7 +59226,7 @@
         <v>45891.65295138889</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59283,7 +59283,7 @@
         <v>44991.51193287037</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59340,7 +59340,7 @@
         <v>44991</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59397,7 +59397,7 @@
         <v>45727.34787037037</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59454,7 +59454,7 @@
         <v>44098</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59511,7 +59511,7 @@
         <v>45181.58791666666</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59568,7 +59568,7 @@
         <v>45530</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59625,7 +59625,7 @@
         <v>44812</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59682,7 +59682,7 @@
         <v>45888</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59739,7 +59739,7 @@
         <v>45679.48483796296</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59796,7 +59796,7 @@
         <v>44187</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59853,7 +59853,7 @@
         <v>45441.54350694444</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59910,7 +59910,7 @@
         <v>45647</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59967,7 +59967,7 @@
         <v>45205</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60024,7 +60024,7 @@
         <v>45742.89054398148</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60081,7 +60081,7 @@
         <v>45889.93328703703</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60138,7 +60138,7 @@
         <v>45848.61030092592</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60195,7 +60195,7 @@
         <v>44959</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60252,7 +60252,7 @@
         <v>44959</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60309,7 +60309,7 @@
         <v>45187.59305555555</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60366,7 +60366,7 @@
         <v>45176</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60428,7 +60428,7 @@
         <v>45181</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60485,7 +60485,7 @@
         <v>45891.65096064815</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60542,7 +60542,7 @@
         <v>45890.37820601852</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60599,7 +60599,7 @@
         <v>45714.80385416667</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>44523.46746527778</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60713,7 +60713,7 @@
         <v>45848.6062962963</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60770,7 +60770,7 @@
         <v>45168.33265046297</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60827,7 +60827,7 @@
         <v>45224.70244212963</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60884,7 +60884,7 @@
         <v>45097</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60941,7 +60941,7 @@
         <v>45685.35516203703</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -60998,7 +60998,7 @@
         <v>44980.62431712963</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>44129</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         <v>44573</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61174,7 +61174,7 @@
         <v>45463.39309027778</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61231,7 +61231,7 @@
         <v>45614.63012731481</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61293,7 +61293,7 @@
         <v>44810</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61350,7 +61350,7 @@
         <v>45231</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61407,7 +61407,7 @@
         <v>45035</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61464,7 +61464,7 @@
         <v>45077.43420138889</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61521,7 +61521,7 @@
         <v>44809.39893518519</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61578,7 +61578,7 @@
         <v>44945.34497685185</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -61635,7 +61635,7 @@
         <v>45594.62287037037</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45594.6306712963</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -61749,7 +61749,7 @@
         <v>44820</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61806,7 +61806,7 @@
         <v>44721.70876157407</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61863,7 +61863,7 @@
         <v>45410</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61920,7 +61920,7 @@
         <v>45679.47949074074</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -61977,7 +61977,7 @@
         <v>45476.50119212963</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62034,7 +62034,7 @@
         <v>45476.50480324074</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62091,7 +62091,7 @@
         <v>45300</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62148,7 +62148,7 @@
         <v>45210</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62205,7 +62205,7 @@
         <v>44903</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62262,7 +62262,7 @@
         <v>45735.66598379629</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62324,7 +62324,7 @@
         <v>45065</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62381,7 +62381,7 @@
         <v>45111</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62438,7 +62438,7 @@
         <v>45672.46096064815</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62495,7 +62495,7 @@
         <v>44846.55085648148</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62552,7 +62552,7 @@
         <v>44894.45888888889</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -62609,7 +62609,7 @@
         <v>45772.59259259259</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -62666,7 +62666,7 @@
         <v>44848.30996527777</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -62723,7 +62723,7 @@
         <v>45775.58704861111</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62780,7 +62780,7 @@
         <v>45224.59289351852</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62837,7 +62837,7 @@
         <v>45089</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62894,7 +62894,7 @@
         <v>44565</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -62951,7 +62951,7 @@
         <v>44565.61265046296</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63008,7 +63008,7 @@
         <v>45236.68318287037</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63065,7 +63065,7 @@
         <v>45730.6487037037</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63122,7 +63122,7 @@
         <v>45068.45921296296</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63179,7 +63179,7 @@
         <v>45315.65375</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63236,7 +63236,7 @@
         <v>44272</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -567,7 +567,7 @@
         <v>45105</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44735</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>45568</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>45820</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>44216</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44343</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>45533</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45733.64422453703</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>44610</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45357</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>45211</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>45224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>44258</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45078</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>45194</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>45078</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>45701.89549768518</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44151</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44271.71099537037</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44448</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44679</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>44825.70888888889</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44524</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>44495</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44809.40431712963</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44582</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45372.69723379629</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45558.62674768519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>45527.45695601852</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44985</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>45686.57611111111</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>45476.50744212963</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44928</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45555.65903935185</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>45642.60756944444</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45819</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>44645</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45274.32131944445</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>45896.9408912037</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>45282</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45111</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44232</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45086</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45181</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44461</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>45005</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45749.46063657408</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>44082.65943287037</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>44357.34326388889</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>44231</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44467.6135300926</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44309.65885416666</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>44571.63828703704</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>44186</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>44431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>44715.33956018519</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>44811.66311342592</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>44119</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>44568</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44853.50333333333</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44307.481875</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>44508.43092592592</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>44622</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>44272</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>44152</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>44271</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44134</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>44285.5874537037</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44327.59131944444</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>44357</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>44224</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>44245</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44441</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>44230</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>44410</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>44125.62782407407</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>44459</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44194</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>44297</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44510.88893518518</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44809.54884259259</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>44461</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>44461.57160879629</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>44721.65634259259</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>44607</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>44510</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44818</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>44125</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>44848.3015625</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         <v>44297</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44277.6141087963</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>44230</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>44258</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>44635.93181712963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44510.63989583333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44503.73802083333</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44386.6371412037</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44587.59076388889</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44742.95375</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44592.65864583333</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44370.39163194445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>44650.495</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44623.46204861111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>44714</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>44847</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>44847</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>44084</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>44257.83641203704</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>44292</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>44749</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>44186</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>44468</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44460</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>44441</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>44441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>44404</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>44460</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>44259</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>44110</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>44258</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>44474</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>44880.48260416667</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44837.42782407408</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44861</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44273.62519675926</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44245</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44140</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>44221</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44304</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>44482</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>44315</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>44145</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>44806.68451388889</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>44476</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>44476.58800925926</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>44211</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>44461.69494212963</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>44502.34869212963</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44267</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>44165</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44137.73322916667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44441</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>44459</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>44515</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>44495.68931712963</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44169</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44715</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>44381</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44384.39226851852</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>44169</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44130</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44476</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44229</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>44576</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>44426.34618055556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>44888.69445601852</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44882.66891203704</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44322.68579861111</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>44075</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>44175</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44825.35965277778</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44460.62309027778</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>44363</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>44187.74415509259</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44147.70520833333</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44321.51725694445</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44764</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>44203</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>44229</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>44165</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>44817</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>44537.63180555555</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>44806</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44712.30428240741</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>44565.61417824074</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44809.39019675926</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>44739.3564699074</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>44806</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>44146</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>44369.93123842592</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>44606</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>44186</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>44820.47135416666</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>44810</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>44173</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>44265</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>44417.77873842593</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>44357.34568287037</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>44448.45023148148</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44448</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>44371</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>44420.65103009259</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>44610.3157175926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44277.60974537037</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>44127.46831018518</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>44742.71378472223</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         <v>44084</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>44760.74060185185</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>44446</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>44246</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44169</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>44515</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>44732.43689814815</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>44592.65989583333</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>44469</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>44715.33355324074</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>44187</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>44517</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>44595</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>44469</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>44530</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>44109</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>44228</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>44237</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44204</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>44879.61497685185</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>44550</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>44280</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44295.77248842592</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44536</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44831</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44810.40475694444</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44810.35575231481</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>44538.40638888889</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>44497.430625</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>44588</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>44295</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44384.46910879629</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44235</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>45773.44608796296</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>44152</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>44845</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44621.66707175926</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>44495.69234953704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44449</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>44882.6740162037</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>44862.38081018518</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
         <v>45272</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>44209</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>45713</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>44421</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>44152</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>45069.48967592593</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>44991.51193287037</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>44991</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>44809</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>45684.34170138889</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>45684.34384259259</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>44974</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45048</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>45126</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>44924</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>45187.48282407408</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45187</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>44819.34596064815</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45735.45677083333</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         <v>44900</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44867</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>45334</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45164</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>44764</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>45035</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>45715</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>45272.62565972222</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>44908</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>44908</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>44825.46571759259</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>45247.46569444444</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>44508</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45679.49804398148</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>45324.71243055556</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>45707.64956018519</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>45707.66369212963</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45724</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>45749.56019675926</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45730.6487037037</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>45441</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>45126</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>45089</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>45085.93778935185</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>45440.4658449074</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>45183.65436342593</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>45223</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>45223</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>45441</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45747.79938657407</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>45614.505625</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45702.6033912037</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>45646</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45764.48869212963</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45181.58791666666</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>44928</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>44446</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>45343.92605324074</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44357.34482638889</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>45775.87377314815</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>45629</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>45534.67689814815</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>45775.87576388889</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>45272</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>45708.48537037037</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45777.73621527778</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45777.72737268519</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>44424</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>44959</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>44810.56070601852</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45300</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>44810.52567129629</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45782.33971064815</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>44181</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>44090</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45239</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45373.59099537037</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>44895</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>44895</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>44895.58759259259</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>45061</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>45783.67510416666</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>45783.7002662037</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>45783.70811342593</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45783.71136574074</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>45783.71869212963</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>45783.7308912037</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45470</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>45783.72262731481</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>45161</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>45750.94241898148</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>45021</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>45097</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>45783.73440972222</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>45783.74034722222</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45784.74020833334</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>45708.4921412037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45197</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45463</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>45512.53300925926</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>45126</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>44551</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>45119.63947916667</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         <v>44946.42413194444</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>44847.46701388889</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>45461</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>45372.68917824074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45481.49108796296</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>45681.62265046296</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>45317</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>44160</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45628.46613425926</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45236</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>45112</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>45359.49635416667</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45306</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22144,7 +22144,7 @@
         <v>44823.61398148148</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>45323</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>45372.36653935185</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>45734.55042824074</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>45119.57798611111</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45720.3175462963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>44860.93721064815</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>44384.39820601852</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22605,7 +22605,7 @@
         <v>45097</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45789.70107638889</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>44075</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>45470</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45278.88578703703</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>45567</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>45510.89385416666</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>45099</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>45720.31155092592</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>45754.56905092593</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23180,7 +23180,7 @@
         <v>45265.48799768519</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>44848.30996527777</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23294,7 +23294,7 @@
         <v>45756.29003472222</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>45166.62002314815</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>45628.56518518519</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45425.69540509259</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44894.63579861111</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>44886.51197916667</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>44850</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>45162.32709490741</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>45615.6362037037</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>45617.72069444445</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>45181</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>45792.30664351852</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>45792.32596064815</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>45390</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45792.33170138889</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>45148.62439814815</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>45168.33265046297</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>45727</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>45188.49305555555</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>44985</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>44985</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>45116.79090277778</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>45116.79268518519</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>45370.34275462963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>45510</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>44937.71841435185</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         <v>45470</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>45273</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45533</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>45561.88243055555</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45593</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
         <v>45593</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>45339.66177083334</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>45483</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>45483</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45509</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>44146</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45266</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>45796.36819444445</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>45796.55706018519</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>45796.56827546296</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>45796.60440972223</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44995.44344907408</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>45796.38944444444</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>44515</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45596.44083333333</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>45734.57873842592</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>45796.38582175926</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45614.63012731481</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45754.52788194444</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45524.49138888889</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>45527.44498842592</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>45600</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>44124.48305555555</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>45349.39254629629</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>44945.34497685185</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>45079</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>45476.50119212963</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>45476.50480324074</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45334</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>45272</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45793.56537037037</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>44186</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>45796.56221064815</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45796.58149305556</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45596.57131944445</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>44817</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45672.58387731481</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45089</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>44999.50538194444</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>45482</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45483</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45797</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>45629</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45798.50189814815</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>44523.46746527778</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45056.31962962963</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>45530</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>44927.74953703704</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>45188.61378472222</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>45610.42850694444</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45637</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>45642.57581018518</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>45604.47508101852</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>44656.61335648148</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>45156</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>45645.58603009259</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>45719</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>45799.40628472222</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>45084.51329861111</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>45644.02509259259</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>45562.55799768519</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44908</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>44435.41690972223</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>44251</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44140</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45714.80106481481</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>44915</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45614.49559027778</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45748.86240740741</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>45216.52173611111</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>45804.66229166667</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45804</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>44603.63212962963</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>44603</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>44603.6434375</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45357</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45345</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45804.6612962963</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>45253</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45137.90618055555</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>44174</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>45805.27778935185</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>45805.31606481481</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>44874</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>44582.42422453704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>44098</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>45646.67438657407</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>45647</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>45647</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>45805.27396990741</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>45805.27659722222</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>45749.56623842593</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45567.33017361111</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>45645.40951388889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>45638</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>44988</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>45610.60369212963</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45371.85761574074</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>45427</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>45176</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>45684.45225694445</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45183.65034722222</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>45215.7849074074</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>45812.59082175926</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>45082</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>45217.3809837963</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45811.39115740741</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>45811.39695601852</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>45811.40674768519</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>45811.55042824074</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45617.68131944445</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>45811.56310185185</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>45811.56517361111</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>45525</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>45610</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>45811.48321759259</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45562</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>45747.39516203704</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>44160</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>44886</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>44144</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>45769.33756944445</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44642.83407407408</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>45359.50059027778</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45628.48590277778</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>45686.54246527778</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44634.60929398148</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>45615.57407407407</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>45350.91678240741</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>45350.91932870371</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>45617.49510416666</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>45628.43445601852</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>45686.51583333333</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>45617.54989583333</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         <v>45817.39481481481</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>45818.66649305556</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>45817.39133101852</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>45818</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45069.64322916666</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44617</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45762.60217592592</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45817</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45518</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>45818.66446759259</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>44942</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45126</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45677.37925925926</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45205</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45820</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33709,7 +33709,7 @@
         <v>45212</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>45510</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33823,7 +33823,7 @@
         <v>45240.67206018518</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33880,7 +33880,7 @@
         <v>44180</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45860</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>45358</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>45372.7019212963</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>45754.38893518518</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34165,7 +34165,7 @@
         <v>45145.57798611111</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34222,7 +34222,7 @@
         <v>44670.43472222222</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34279,7 +34279,7 @@
         <v>44187</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34336,7 +34336,7 @@
         <v>45676.57688657408</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>45179</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>45824.61681712963</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>45246</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>45824.61572916667</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34621,7 +34621,7 @@
         <v>45824.55555555555</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34678,7 +34678,7 @@
         <v>45110</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>44721.70876157407</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>45826.41267361111</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>45167.68207175926</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>45775.58704861111</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34963,7 +34963,7 @@
         <v>45614.44239583334</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>45826</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>44104</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>44851.61237268519</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>45825.65555555555</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35253,7 +35253,7 @@
         <v>45701.60341435186</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35310,7 +35310,7 @@
         <v>45826.47586805555</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35367,7 +35367,7 @@
         <v>45826</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>45869</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35486,7 +35486,7 @@
         <v>45772.59259259259</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>45869</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35605,7 +35605,7 @@
         <v>45686.60648148148</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35662,7 +35662,7 @@
         <v>45686.63332175926</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35719,7 +35719,7 @@
         <v>45071.54651620371</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>45071.54908564815</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35833,7 +35833,7 @@
         <v>45211.63712962963</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>44573</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35952,7 +35952,7 @@
         <v>45793.65984953703</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45869</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45869</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45701.90762731482</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45700.51605324074</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>44628.47715277778</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>45831.3783912037</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>45831.57793981482</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>45831.3978587963</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>45441</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45705.65206018519</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>45446</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>45831</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>45832.28081018518</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>45103</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45831.36892361111</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45831.35077546296</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>45831.34712962963</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45831</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>45205.39787037037</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>45205</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>45205</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>44945.35765046296</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37293,7 +37293,7 @@
         <v>45181</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45567</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45831.36045138889</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>44851.60855324074</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45236.68318287037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>45246.77350694445</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>44181</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37697,7 +37697,7 @@
         <v>45831.56630787037</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45243</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45195.85546296297</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>45005</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45741.47434027777</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>44740.92936342592</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45833.74201388889</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>45739.84453703704</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>45272</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>45833.73708333333</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>45226.43175925926</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>45875.45658564815</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>45163.37561342592</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>44706</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>45188.4716550926</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>44946.62486111111</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>45715.5681712963</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>45126</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>45187.59305555555</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>45271</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>44750</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>45581.49583333333</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45084.67444444444</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>44634</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45875.6449537037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45026</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45225.49447916666</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45707.66030092593</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45131</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45874.65034722222</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>45875.64696759259</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>44959.68709490741</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>44923</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>44923.65486111111</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>45880.86574074074</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>45301.98100694444</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45876.62177083334</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>45207.49881944444</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>44266</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45610.59956018518</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45838.65454861111</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>45756.29621527778</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>45614.50349537037</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>45838.66364583333</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>44959</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40272,7 +40272,7 @@
         <v>45301.83475694444</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>45835.40136574074</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40386,7 +40386,7 @@
         <v>45231</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40443,7 +40443,7 @@
         <v>45628.44303240741</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40500,7 +40500,7 @@
         <v>45880.56395833333</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>45877.42953703704</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40614,7 +40614,7 @@
         <v>45274.57935185185</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40671,7 +40671,7 @@
         <v>45837.87837962963</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>45837.90488425926</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45264.68074074074</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>45835.39804398148</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45735.46112268518</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>45748.59457175926</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>45621</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
         <v>45618.61243055556</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>45840.55074074074</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>45610.61537037037</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>45840.5487037037</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44825.46825231481</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>45881</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>45594.61994212963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41469,7 +41469,7 @@
         <v>45754.57372685185</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>45881.31761574074</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41583,7 +41583,7 @@
         <v>45837.90292824074</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>45837.91177083334</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41697,7 +41697,7 @@
         <v>45881.66684027778</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>45880</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41811,7 +41811,7 @@
         <v>45475</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>45884.62045138889</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45315.65311342593</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>45713</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>45712</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>45280</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>45215.48378472222</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42220,7 +42220,7 @@
         <v>45775.59978009259</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42277,7 +42277,7 @@
         <v>45775.60414351852</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>45328</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42391,7 +42391,7 @@
         <v>45225.63777777777</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42448,7 +42448,7 @@
         <v>44634</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42505,7 +42505,7 @@
         <v>44928.45686342593</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42562,7 +42562,7 @@
         <v>44894.45888888889</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42619,7 +42619,7 @@
         <v>45231</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42676,7 +42676,7 @@
         <v>45257.57825231482</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>45301.98575231482</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>45020</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>45842.62019675926</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>45842.62362268518</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>45593</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43028,7 +43028,7 @@
         <v>45684.34594907407</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>45841.57072916667</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>45012</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43199,7 +43199,7 @@
         <v>45602</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>45162.588125</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43313,7 +43313,7 @@
         <v>45842.45201388889</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
         <v>44988.85038194444</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43427,7 +43427,7 @@
         <v>45323</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45701.59954861111</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43546,7 +43546,7 @@
         <v>45888.58818287037</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>45775.40460648148</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45715.56667824074</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>45152</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45748.91101851852</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43831,7 +43831,7 @@
         <v>45131</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>45888.34261574074</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>45645.58436342593</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>45145.58085648148</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         <v>45811.48709490741</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44116,7 +44116,7 @@
         <v>45845.48898148148</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44173,7 +44173,7 @@
         <v>45845</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44230,7 +44230,7 @@
         <v>45356.68585648148</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>45723.54547453704</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44344,7 +44344,7 @@
         <v>45483</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44401,7 +44401,7 @@
         <v>45845</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44458,7 +44458,7 @@
         <v>45218.86829861111</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>45509.66609953704</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45195.85668981481</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44634,7 +44634,7 @@
         <v>45884.73457175926</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44691,7 +44691,7 @@
         <v>44908</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>45845.48228009259</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>44858.63208333333</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>44999.50461805556</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>45848.6062962963</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>45848.61030092592</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>44802</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>45645.58762731482</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>44743.61965277778</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45847</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45847.3721412037</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>45847.67734953704</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45380,7 +45380,7 @@
         <v>45847.67871527778</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>44852.89560185185</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>45099.91826388889</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>45888</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45608,7 +45608,7 @@
         <v>45730.61275462963</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45665,7 +45665,7 @@
         <v>45889.93328703703</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45722,7 +45722,7 @@
         <v>45890.37820601852</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45811.4892824074</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45712.57320601852</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45893,7 +45893,7 @@
         <v>45742.36822916667</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>45280</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>45672.46096064815</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45279</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45891.64818287037</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45891.65295138889</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45891.65096064815</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45630.32984953704</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45852.33880787037</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45264.68416666667</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45893.60962962963</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45099</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45672.78414351852</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45152.37778935185</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45656.73612268519</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45005</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45895</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45895.41521990741</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46929,7 +46929,7 @@
         <v>45895.57550925926</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46986,7 +46986,7 @@
         <v>45394.73528935185</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47043,7 +47043,7 @@
         <v>45119</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47100,7 +47100,7 @@
         <v>45895.55729166666</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47157,7 +47157,7 @@
         <v>45667.4771412037</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47214,7 +47214,7 @@
         <v>45838.65708333333</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47271,7 +47271,7 @@
         <v>45895.35368055556</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45895</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45895</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45895</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45895</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45895.41074074074</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45895.41686342593</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45852.75837962963</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45647</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45204.32359953703</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45897.61160879629</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45811.57001157408</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45898.49733796297</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45225.63304398148</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>44980.62431712963</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45109</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45530.69050925926</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48255,7 +48255,7 @@
         <v>45896.94550925926</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>44337.48540509259</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48369,7 +48369,7 @@
         <v>45224.59289351852</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48426,7 +48426,7 @@
         <v>45604.54047453704</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>44380</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48540,7 +48540,7 @@
         <v>45727.34787037037</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48597,7 +48597,7 @@
         <v>45510.89869212963</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45734.93418981481</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48711,7 +48711,7 @@
         <v>45747.78081018518</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>45769.36023148148</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>44272</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>45733.60265046296</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>44330.36730324074</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>44651</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45188</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45742.61196759259</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>45275.30907407407</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45224.70244212963</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>45646.67726851852</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45647</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>45647</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49452,7 +49452,7 @@
         <v>45647</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>45647</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>45035</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>45705.5654050926</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>44820</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45747.39719907408</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49799,7 +49799,7 @@
         <v>45628.49322916667</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49856,7 +49856,7 @@
         <v>44380</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>45188.62355324074</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49970,7 +49970,7 @@
         <v>44573</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50032,7 +50032,7 @@
         <v>44712.32885416667</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50089,7 +50089,7 @@
         <v>45033</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50146,7 +50146,7 @@
         <v>45483</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50203,7 +50203,7 @@
         <v>45749.53158564815</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>45168.33028935185</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50317,7 +50317,7 @@
         <v>44377</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50374,7 +50374,7 @@
         <v>44620.45334490741</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50431,7 +50431,7 @@
         <v>45714.80385416667</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>45012</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>44991.53373842593</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50602,7 +50602,7 @@
         <v>45762</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50659,7 +50659,7 @@
         <v>45567.37547453704</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45111</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>45621</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45267.46962962963</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50887,7 +50887,7 @@
         <v>44887</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>44938</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>45643.45525462963</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>44991.35916666667</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>45742.89054398148</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51172,7 +51172,7 @@
         <v>44991</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51229,7 +51229,7 @@
         <v>45761</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>44441</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45212</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>44974.57127314815</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>44959.62519675926</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>44959</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>44959</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45698</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>45055.49951388889</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45236.35502314815</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>44078</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45394.35633101852</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45735.46643518518</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>44565.57157407407</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>44565</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>44812</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>45169</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>44810</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>44810.49734953704</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>44448</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>45714.84204861111</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52436,7 +52436,7 @@
         <v>45188</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>45162.65574074074</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52555,7 +52555,7 @@
         <v>44924.66556712963</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52612,7 +52612,7 @@
         <v>45071.55216435185</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52669,7 +52669,7 @@
         <v>45071.55913194444</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52726,7 +52726,7 @@
         <v>45730.63616898148</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52783,7 +52783,7 @@
         <v>44158</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52845,7 +52845,7 @@
         <v>44903</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52902,7 +52902,7 @@
         <v>44657</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52959,7 +52959,7 @@
         <v>45079</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53016,7 +53016,7 @@
         <v>45076.30560185185</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53073,7 +53073,7 @@
         <v>45077</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>45758.72209490741</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>45758.73298611111</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>44852</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45068.66135416667</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45744.56912037037</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>45764.52859953704</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45218.47658564815</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>44151</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         <v>45260.32738425926</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>44565.61265046296</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45036.6734375</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>44806.59946759259</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>44886</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>44585</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>45620.82185185186</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>44126</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>45191.55503472222</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54109,7 +54109,7 @@
         <v>45070</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>44551.38699074074</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54223,7 +54223,7 @@
         <v>45594</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>45593</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54342,7 +54342,7 @@
         <v>44742.71030092592</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54399,7 +54399,7 @@
         <v>44809.39893518519</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54456,7 +54456,7 @@
         <v>45359.50601851852</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54513,7 +54513,7 @@
         <v>45366.32900462963</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54570,7 +54570,7 @@
         <v>45546.84695601852</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54632,7 +54632,7 @@
         <v>45546.84908564815</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54694,7 +54694,7 @@
         <v>44421.51063657407</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54751,7 +54751,7 @@
         <v>45054.85400462963</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54808,7 +54808,7 @@
         <v>45510</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54865,7 +54865,7 @@
         <v>44180</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54922,7 +54922,7 @@
         <v>45012</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54979,7 +54979,7 @@
         <v>44160</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55036,7 +55036,7 @@
         <v>45356.68475694444</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>44487</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55150,7 +55150,7 @@
         <v>45562.53543981481</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55212,7 +55212,7 @@
         <v>45546.85369212963</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55274,7 +55274,7 @@
         <v>45604.4971412037</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55331,7 +55331,7 @@
         <v>45593</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>45758.73520833333</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>44454</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55507,7 +55507,7 @@
         <v>44260</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         <v>44129</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55621,7 +55621,7 @@
         <v>45226.44923611111</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55678,7 +55678,7 @@
         <v>45629</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55735,7 +55735,7 @@
         <v>45202.38372685185</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>44923</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55849,7 +55849,7 @@
         <v>44846.55085648148</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55906,7 +55906,7 @@
         <v>45645</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55963,7 +55963,7 @@
         <v>45568.46310185185</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>44896.30818287037</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56077,7 +56077,7 @@
         <v>45097</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>45747.78493055556</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56191,7 +56191,7 @@
         <v>45097</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56248,7 +56248,7 @@
         <v>45764.48725694444</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56305,7 +56305,7 @@
         <v>44228</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56362,7 +56362,7 @@
         <v>45081</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56419,7 +56419,7 @@
         <v>44917</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>45093</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56533,7 +56533,7 @@
         <v>45099</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56590,7 +56590,7 @@
         <v>45305.57791666667</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56647,7 +56647,7 @@
         <v>45260</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56704,7 +56704,7 @@
         <v>45092.71057870371</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>45607.36863425926</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>45097</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45033</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45679.47949074074</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45686.60939814815</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>45470.64299768519</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57103,7 +57103,7 @@
         <v>45470.64894675926</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>45103</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>45595.4272337963</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45307</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57331,7 +57331,7 @@
         <v>44281</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57393,7 +57393,7 @@
         <v>45733.43582175926</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57450,7 +57450,7 @@
         <v>45733.44309027777</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45065</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>45733.57615740741</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57621,7 +57621,7 @@
         <v>45747.39269675926</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57683,7 +57683,7 @@
         <v>45747.39408564815</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57745,7 +57745,7 @@
         <v>45726.54469907407</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57802,7 +57802,7 @@
         <v>45121.35078703704</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57859,7 +57859,7 @@
         <v>44985</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>45757.94755787037</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57973,7 +57973,7 @@
         <v>45349</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>44978.59528935186</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>44960.36971064815</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>45396.86226851852</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58201,7 +58201,7 @@
         <v>44712</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58258,7 +58258,7 @@
         <v>44929</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58315,7 +58315,7 @@
         <v>45281.63481481482</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45639.58114583333</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58429,7 +58429,7 @@
         <v>45686.3184375</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58486,7 +58486,7 @@
         <v>45253.54356481481</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58543,7 +58543,7 @@
         <v>45754.52563657407</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58600,7 +58600,7 @@
         <v>45754.52998842593</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58657,7 +58657,7 @@
         <v>44881</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58714,7 +58714,7 @@
         <v>45275</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58776,7 +58776,7 @@
         <v>44991.34855324074</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58833,7 +58833,7 @@
         <v>44971.45475694445</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58890,7 +58890,7 @@
         <v>45594.62881944444</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58947,7 +58947,7 @@
         <v>45111</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59004,7 +59004,7 @@
         <v>45181</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59061,7 +59061,7 @@
         <v>45119.58694444445</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59118,7 +59118,7 @@
         <v>45602.91650462963</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59175,7 +59175,7 @@
         <v>44868.56361111111</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59232,7 +59232,7 @@
         <v>44882</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59289,7 +59289,7 @@
         <v>45188</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59346,7 +59346,7 @@
         <v>45463.39309027778</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59403,7 +59403,7 @@
         <v>45602.65810185186</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59460,7 +59460,7 @@
         <v>45672.591875</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59517,7 +59517,7 @@
         <v>45620.46207175926</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59574,7 +59574,7 @@
         <v>45551</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59636,7 +59636,7 @@
         <v>44883</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59693,7 +59693,7 @@
         <v>44820.47260416667</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59750,7 +59750,7 @@
         <v>45614.50907407407</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59812,7 +59812,7 @@
         <v>45068.45921296296</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59869,7 +59869,7 @@
         <v>45679.48483796296</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59926,7 +59926,7 @@
         <v>45401.69138888889</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59983,7 +59983,7 @@
         <v>45410</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60040,7 +60040,7 @@
         <v>45103.67451388889</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60097,7 +60097,7 @@
         <v>45162</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60154,7 +60154,7 @@
         <v>45170</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60211,7 +60211,7 @@
         <v>45211.63446759259</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60268,7 +60268,7 @@
         <v>45301</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60325,7 +60325,7 @@
         <v>45700.69467592592</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60382,7 +60382,7 @@
         <v>45065</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60439,7 +60439,7 @@
         <v>45121.70020833334</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60496,7 +60496,7 @@
         <v>45615.57574074074</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>45146.71684027778</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45632.51193287037</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45210</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60724,7 +60724,7 @@
         <v>45603</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60786,7 +60786,7 @@
         <v>45748.90723379629</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>45301.98247685185</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60900,7 +60900,7 @@
         <v>44881</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60957,7 +60957,7 @@
         <v>45181.56171296296</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61014,7 +61014,7 @@
         <v>45412</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61071,7 +61071,7 @@
         <v>45561.7159837963</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61128,7 +61128,7 @@
         <v>45755.48740740741</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>44993</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61242,7 +61242,7 @@
         <v>45097</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61299,7 +61299,7 @@
         <v>45709.64976851852</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61356,7 +61356,7 @@
         <v>45223</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61413,7 +61413,7 @@
         <v>45713</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61475,7 +61475,7 @@
         <v>45713.62074074074</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61537,7 +61537,7 @@
         <v>45250.44863425926</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61594,7 +61594,7 @@
         <v>44903.53118055555</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -61651,7 +61651,7 @@
         <v>45106.89616898148</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -61708,7 +61708,7 @@
         <v>45546</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -61765,7 +61765,7 @@
         <v>45355.4612037037</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61822,7 +61822,7 @@
         <v>45315.65375</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61879,7 +61879,7 @@
         <v>45339</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61936,7 +61936,7 @@
         <v>45656.78905092592</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -61993,7 +61993,7 @@
         <v>44466.48996527777</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>44971.69971064815</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62107,7 +62107,7 @@
         <v>45726.51144675926</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>44361.5662962963</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62221,7 +62221,7 @@
         <v>45634</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62278,7 +62278,7 @@
         <v>45610.36342592593</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62335,7 +62335,7 @@
         <v>45281.62631944445</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62392,7 +62392,7 @@
         <v>44587.40662037037</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62449,7 +62449,7 @@
         <v>45279</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62511,7 +62511,7 @@
         <v>45188.49987268518</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62568,7 +62568,7 @@
         <v>45274</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -62625,7 +62625,7 @@
         <v>45548.38636574074</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -62682,7 +62682,7 @@
         <v>45610.60157407408</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -62739,7 +62739,7 @@
         <v>45594.62287037037</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62796,7 +62796,7 @@
         <v>45594.6306712963</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62853,7 +62853,7 @@
         <v>45077.43420138889</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62910,7 +62910,7 @@
         <v>44376</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -62967,7 +62967,7 @@
         <v>45747</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63024,7 +63024,7 @@
         <v>45714.80880787037</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63081,7 +63081,7 @@
         <v>45075.53265046296</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63138,7 +63138,7 @@
         <v>45635.84936342593</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63195,7 +63195,7 @@
         <v>45637.54557870371</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63252,7 +63252,7 @@
         <v>45722.31061342593</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -63309,7 +63309,7 @@
         <v>45639</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -63366,7 +63366,7 @@
         <v>45156</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -567,7 +567,7 @@
         <v>45105</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44735</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>45568</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>45820</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>44216</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44343</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>45533</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45733.64422453703</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>44610</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45357</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>45211</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>45224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>44258</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45078</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>45194</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>45078</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>45701.89549768518</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44151</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44271.71099537037</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44448</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44679</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>44825.70888888889</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44524</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>44495</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44809.40431712963</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44582</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45372.69723379629</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45558.62674768519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>45527.45695601852</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44985</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>45686.57611111111</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>45476.50744212963</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44928</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45555.65903935185</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>45642.60756944444</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45819</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>44645</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45274.32131944445</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>45896.9408912037</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>45282</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45111</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44232</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45086</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45181</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44461</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>45005</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45749.46063657408</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>44082.65943287037</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>44357.34326388889</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>44231</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44467.6135300926</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44309.65885416666</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>44571.63828703704</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>44186</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>44431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>44715.33956018519</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>44811.66311342592</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>44119</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>44568</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44853.50333333333</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44307.481875</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>44508.43092592592</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>44622</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>44272</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>44152</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>44271</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44134</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>44285.5874537037</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44327.59131944444</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>44357</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>44224</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>44245</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44441</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>44230</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>44410</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>44125.62782407407</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>44459</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44194</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>44297</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44510.88893518518</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44809.54884259259</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>44461</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>44461.57160879629</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>44721.65634259259</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>44607</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>44510</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44818</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>44125</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>44848.3015625</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         <v>44297</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44277.6141087963</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>44230</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>44258</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>44635.93181712963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44510.63989583333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44503.73802083333</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44386.6371412037</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44587.59076388889</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44742.95375</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44592.65864583333</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44370.39163194445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>44650.495</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44623.46204861111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>44714</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>44847</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>44847</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>44084</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>44257.83641203704</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>44292</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>44749</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>44186</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>44468</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44460</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>44441</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>44441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>44404</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>44460</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>44259</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>44110</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>44258</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>44474</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>44880.48260416667</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44837.42782407408</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44861</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44273.62519675926</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44245</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44140</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>44221</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44304</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>44482</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>44315</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>44145</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>44806.68451388889</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>44476</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>44476.58800925926</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>44211</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>44461.69494212963</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>44502.34869212963</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44267</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>44165</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44137.73322916667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44441</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>44459</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>44515</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>44495.68931712963</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44169</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44715</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>44381</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44384.39226851852</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>44169</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44130</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44476</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44229</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>44576</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>44426.34618055556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>44888.69445601852</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44882.66891203704</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44322.68579861111</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>44075</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>44175</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44825.35965277778</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44460.62309027778</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>44363</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>44187.74415509259</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44147.70520833333</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44321.51725694445</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44764</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>44203</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>44229</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>44165</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>44817</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>44537.63180555555</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>44806</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44712.30428240741</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>44565.61417824074</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44809.39019675926</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>44739.3564699074</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>44806</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>44146</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>44369.93123842592</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>44606</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>44186</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>44820.47135416666</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>44810</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>44173</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>44265</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>44417.77873842593</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>44357.34568287037</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>44448.45023148148</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44448</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>44371</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>44420.65103009259</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>44610.3157175926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44277.60974537037</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>44127.46831018518</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>44742.71378472223</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         <v>44084</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>44760.74060185185</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>44446</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>44246</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44169</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>44515</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>44732.43689814815</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>44592.65989583333</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>44469</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>44715.33355324074</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>44187</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>44517</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>44595</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>44469</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>44530</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>44109</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>44228</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>44237</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44204</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>44879.61497685185</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>44550</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>44280</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44295.77248842592</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44536</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44831</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44810.40475694444</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44810.35575231481</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>44538.40638888889</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>44497.430625</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>44588</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>44295</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44384.46910879629</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44235</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>45773.44608796296</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>44152</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>44845</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44621.66707175926</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>44495.69234953704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44449</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>44882.6740162037</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>44862.38081018518</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
         <v>45272</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>44209</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>45713</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>44421</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>44152</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>45069.48967592593</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>44991.51193287037</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>44991</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>44809</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>45684.34170138889</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>45684.34384259259</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>44974</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45048</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>45126</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>44924</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>45187.48282407408</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45187</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>44819.34596064815</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45735.45677083333</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         <v>44900</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44867</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>45334</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45164</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>44764</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>45035</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>45715</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>45272.62565972222</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>44908</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>44908</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>44825.46571759259</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>45247.46569444444</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>44508</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45679.49804398148</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>45324.71243055556</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>45707.64956018519</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>45707.66369212963</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45724</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>45749.56019675926</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45730.6487037037</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>45441</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>45126</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>45089</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>45085.93778935185</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>45440.4658449074</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>45183.65436342593</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>45223</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>45223</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>45441</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45747.79938657407</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>45614.505625</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45702.6033912037</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>45646</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45764.48869212963</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45181.58791666666</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>44928</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>44446</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>45343.92605324074</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44357.34482638889</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>45775.87377314815</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>45629</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>45534.67689814815</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>45775.87576388889</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>45272</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>45708.48537037037</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45777.73621527778</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45777.72737268519</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>44424</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>44959</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>44810.56070601852</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45300</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>44810.52567129629</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45782.33971064815</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>44181</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>44090</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45239</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45373.59099537037</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>44895</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>44895</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>44895.58759259259</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>45061</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>45783.67510416666</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>45783.7002662037</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>45783.70811342593</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45783.71136574074</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>45783.71869212963</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>45783.7308912037</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45470</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>45783.72262731481</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>45161</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>45750.94241898148</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>45021</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>45097</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>45783.73440972222</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>45783.74034722222</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45784.74020833334</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>45708.4921412037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45197</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45463</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>45512.53300925926</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>45126</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>44551</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>45119.63947916667</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         <v>44946.42413194444</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>44847.46701388889</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>45461</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>45372.68917824074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45481.49108796296</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>45681.62265046296</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>45317</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>44160</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45628.46613425926</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45236</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>45112</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>45359.49635416667</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45306</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22144,7 +22144,7 @@
         <v>44823.61398148148</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>45323</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>45372.36653935185</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>45734.55042824074</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>45119.57798611111</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45720.3175462963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>44860.93721064815</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>44384.39820601852</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22605,7 +22605,7 @@
         <v>45097</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45789.70107638889</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>44075</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>45470</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45278.88578703703</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>45567</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>45510.89385416666</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>45099</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>45720.31155092592</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>45754.56905092593</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23180,7 +23180,7 @@
         <v>45265.48799768519</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>44848.30996527777</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23294,7 +23294,7 @@
         <v>45756.29003472222</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>45166.62002314815</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>45628.56518518519</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45425.69540509259</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44894.63579861111</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>44886.51197916667</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>44850</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>45162.32709490741</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>45615.6362037037</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>45617.72069444445</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>45181</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>45792.30664351852</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>45792.32596064815</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>45390</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45792.33170138889</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>45148.62439814815</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>45168.33265046297</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>45727</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>45188.49305555555</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>44985</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>44985</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>45116.79090277778</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>45116.79268518519</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>45370.34275462963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>45510</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>44937.71841435185</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         <v>45470</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>45273</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45533</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>45561.88243055555</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45593</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
         <v>45593</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>45339.66177083334</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>45483</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>45483</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45509</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>44146</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45266</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>45796.36819444445</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>45796.55706018519</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>45796.56827546296</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>45796.60440972223</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44995.44344907408</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>45796.38944444444</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>44515</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45596.44083333333</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>45734.57873842592</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>45796.38582175926</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45614.63012731481</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45754.52788194444</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45524.49138888889</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>45527.44498842592</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>45600</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>44124.48305555555</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>45349.39254629629</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>44945.34497685185</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>45079</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>45476.50119212963</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>45476.50480324074</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45334</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>45272</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45793.56537037037</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>44186</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>45796.56221064815</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45796.58149305556</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45596.57131944445</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>44817</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45672.58387731481</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45089</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>44999.50538194444</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>45482</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45483</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45797</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>45629</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45798.50189814815</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>44523.46746527778</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45056.31962962963</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>45530</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>44927.74953703704</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>45188.61378472222</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>45610.42850694444</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45637</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>45642.57581018518</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>45604.47508101852</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>44656.61335648148</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>45156</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>45645.58603009259</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>45719</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>45799.40628472222</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>45084.51329861111</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>45644.02509259259</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>45562.55799768519</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44908</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>44435.41690972223</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>44251</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44140</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45714.80106481481</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>44915</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45614.49559027778</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45748.86240740741</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>45216.52173611111</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>45804.66229166667</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45804</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>44603.63212962963</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>44603</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>44603.6434375</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45357</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45345</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45804.6612962963</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>45253</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45137.90618055555</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>44174</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>45805.27778935185</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>45805.31606481481</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>44874</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>44582.42422453704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>44098</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>45646.67438657407</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>45647</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>45647</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>45805.27396990741</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>45805.27659722222</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>45749.56623842593</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45567.33017361111</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>45645.40951388889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>45638</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>44988</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>45610.60369212963</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45371.85761574074</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>45427</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>45176</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>45684.45225694445</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45183.65034722222</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>45215.7849074074</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>45812.59082175926</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>45082</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>45217.3809837963</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45811.39115740741</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>45811.39695601852</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>45811.40674768519</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>45811.55042824074</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45617.68131944445</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>45811.56310185185</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>45811.56517361111</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>45525</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>45610</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>45811.48321759259</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45562</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>45747.39516203704</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>44160</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>44886</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>44144</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>45769.33756944445</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44642.83407407408</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>45359.50059027778</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45628.48590277778</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>45686.54246527778</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44634.60929398148</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>45615.57407407407</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>45350.91678240741</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>45350.91932870371</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>45617.49510416666</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>45628.43445601852</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>45686.51583333333</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>45617.54989583333</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         <v>45817.39481481481</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>45818.66649305556</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>45817.39133101852</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>45818</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45069.64322916666</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44617</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45762.60217592592</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45817</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45518</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>45818.66446759259</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>44942</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45126</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45677.37925925926</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45205</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45820</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33709,7 +33709,7 @@
         <v>45212</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>45510</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33823,7 +33823,7 @@
         <v>45240.67206018518</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33880,7 +33880,7 @@
         <v>44180</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45860</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>45358</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>45372.7019212963</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>45754.38893518518</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34165,7 +34165,7 @@
         <v>45145.57798611111</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34222,7 +34222,7 @@
         <v>44670.43472222222</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34279,7 +34279,7 @@
         <v>44187</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34336,7 +34336,7 @@
         <v>45676.57688657408</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>45179</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>45824.61681712963</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>45246</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>45824.61572916667</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34621,7 +34621,7 @@
         <v>45824.55555555555</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34678,7 +34678,7 @@
         <v>45110</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>44721.70876157407</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>45826.41267361111</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>45167.68207175926</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>45775.58704861111</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34963,7 +34963,7 @@
         <v>45614.44239583334</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>45826</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>44104</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>44851.61237268519</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>45825.65555555555</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35253,7 +35253,7 @@
         <v>45701.60341435186</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35310,7 +35310,7 @@
         <v>45826.47586805555</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35367,7 +35367,7 @@
         <v>45826</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>45869</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35486,7 +35486,7 @@
         <v>45772.59259259259</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>45869</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35605,7 +35605,7 @@
         <v>45686.60648148148</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35662,7 +35662,7 @@
         <v>45686.63332175926</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35719,7 +35719,7 @@
         <v>45071.54651620371</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>45071.54908564815</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35833,7 +35833,7 @@
         <v>45211.63712962963</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>44573</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35952,7 +35952,7 @@
         <v>45793.65984953703</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45869</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45869</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45701.90762731482</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45700.51605324074</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>44628.47715277778</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>45831.3783912037</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>45831.57793981482</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>45831.3978587963</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>45441</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45705.65206018519</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>45446</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>45831</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>45832.28081018518</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>45103</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45831.36892361111</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45831.35077546296</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>45831.34712962963</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45831</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>45205.39787037037</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>45205</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>45205</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>44945.35765046296</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37293,7 +37293,7 @@
         <v>45181</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45567</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45831.36045138889</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>44851.60855324074</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45236.68318287037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>45246.77350694445</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>44181</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37697,7 +37697,7 @@
         <v>45831.56630787037</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45243</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45195.85546296297</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>45005</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45741.47434027777</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>44740.92936342592</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45833.74201388889</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>45739.84453703704</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>45272</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>45833.73708333333</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>45226.43175925926</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>45875.45658564815</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>45163.37561342592</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>44706</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>45188.4716550926</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>44946.62486111111</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>45715.5681712963</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>45126</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>45187.59305555555</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>45271</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>44750</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>45581.49583333333</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45084.67444444444</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>44634</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45875.6449537037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45026</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45225.49447916666</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45707.66030092593</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45131</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45874.65034722222</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>45875.64696759259</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>44959.68709490741</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>44923</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>44923.65486111111</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>45880.86574074074</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>45301.98100694444</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45876.62177083334</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>45207.49881944444</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>44266</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45610.59956018518</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45838.65454861111</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>45756.29621527778</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>45614.50349537037</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>45838.66364583333</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>44959</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40272,7 +40272,7 @@
         <v>45301.83475694444</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>45835.40136574074</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40386,7 +40386,7 @@
         <v>45231</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40443,7 +40443,7 @@
         <v>45628.44303240741</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40500,7 +40500,7 @@
         <v>45880.56395833333</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>45877.42953703704</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40614,7 +40614,7 @@
         <v>45274.57935185185</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40671,7 +40671,7 @@
         <v>45837.87837962963</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>45837.90488425926</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45264.68074074074</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>45835.39804398148</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45735.46112268518</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>45748.59457175926</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>45621</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
         <v>45618.61243055556</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>45840.55074074074</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>45610.61537037037</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>45840.5487037037</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44825.46825231481</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>45881</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>45594.61994212963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41469,7 +41469,7 @@
         <v>45754.57372685185</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>45881.31761574074</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41583,7 +41583,7 @@
         <v>45837.90292824074</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>45837.91177083334</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41697,7 +41697,7 @@
         <v>45881.66684027778</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>45880</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41811,7 +41811,7 @@
         <v>45475</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>45884.62045138889</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45315.65311342593</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>45713</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>45712</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>45280</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>45215.48378472222</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42220,7 +42220,7 @@
         <v>45775.59978009259</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42277,7 +42277,7 @@
         <v>45775.60414351852</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>45328</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42391,7 +42391,7 @@
         <v>45225.63777777777</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42448,7 +42448,7 @@
         <v>44634</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42505,7 +42505,7 @@
         <v>44928.45686342593</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42562,7 +42562,7 @@
         <v>44894.45888888889</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42619,7 +42619,7 @@
         <v>45231</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42676,7 +42676,7 @@
         <v>45257.57825231482</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>45301.98575231482</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>45020</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>45842.62019675926</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>45842.62362268518</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>45593</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43028,7 +43028,7 @@
         <v>45684.34594907407</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>45841.57072916667</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>45012</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43199,7 +43199,7 @@
         <v>45602</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>45162.588125</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43313,7 +43313,7 @@
         <v>45842.45201388889</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
         <v>44988.85038194444</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43427,7 +43427,7 @@
         <v>45323</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45701.59954861111</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43546,7 +43546,7 @@
         <v>45888.58818287037</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>45775.40460648148</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45715.56667824074</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>45152</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45748.91101851852</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43831,7 +43831,7 @@
         <v>45131</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>45888.34261574074</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>45645.58436342593</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>45145.58085648148</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         <v>45811.48709490741</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44116,7 +44116,7 @@
         <v>45845.48898148148</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44173,7 +44173,7 @@
         <v>45845</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44230,7 +44230,7 @@
         <v>45356.68585648148</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>45723.54547453704</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44344,7 +44344,7 @@
         <v>45483</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44401,7 +44401,7 @@
         <v>45845</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44458,7 +44458,7 @@
         <v>45218.86829861111</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>45509.66609953704</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45195.85668981481</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44634,7 +44634,7 @@
         <v>45884.73457175926</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44691,7 +44691,7 @@
         <v>44908</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>45845.48228009259</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>44858.63208333333</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>44999.50461805556</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>45848.6062962963</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>45848.61030092592</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>44802</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>45645.58762731482</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>44743.61965277778</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45847</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45847.3721412037</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>45847.67734953704</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45380,7 +45380,7 @@
         <v>45847.67871527778</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>44852.89560185185</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>45099.91826388889</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>45888</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45608,7 +45608,7 @@
         <v>45730.61275462963</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45665,7 +45665,7 @@
         <v>45889.93328703703</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45722,7 +45722,7 @@
         <v>45890.37820601852</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45811.4892824074</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45712.57320601852</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45893,7 +45893,7 @@
         <v>45742.36822916667</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>45280</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>45672.46096064815</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45279</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45891.64818287037</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45891.65295138889</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45891.65096064815</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45630.32984953704</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45852.33880787037</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45264.68416666667</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45893.60962962963</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45099</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45672.78414351852</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45152.37778935185</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45656.73612268519</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45005</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45895</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45895.41521990741</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46929,7 +46929,7 @@
         <v>45895.57550925926</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46986,7 +46986,7 @@
         <v>45394.73528935185</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47043,7 +47043,7 @@
         <v>45119</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47100,7 +47100,7 @@
         <v>45895.55729166666</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47157,7 +47157,7 @@
         <v>45667.4771412037</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47214,7 +47214,7 @@
         <v>45838.65708333333</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47271,7 +47271,7 @@
         <v>45895.35368055556</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45895</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45895</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45895</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45895</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45895.41074074074</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45895.41686342593</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45852.75837962963</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45647</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45204.32359953703</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45897.61160879629</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45811.57001157408</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45898.49733796297</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45225.63304398148</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>44980.62431712963</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45109</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45530.69050925926</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48255,7 +48255,7 @@
         <v>45896.94550925926</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>44337.48540509259</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48369,7 +48369,7 @@
         <v>45224.59289351852</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48426,7 +48426,7 @@
         <v>45604.54047453704</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>44380</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48540,7 +48540,7 @@
         <v>45727.34787037037</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48597,7 +48597,7 @@
         <v>45510.89869212963</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45734.93418981481</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48711,7 +48711,7 @@
         <v>45747.78081018518</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>45769.36023148148</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>44272</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>45733.60265046296</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>44330.36730324074</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>44651</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45188</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45742.61196759259</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>45275.30907407407</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45224.70244212963</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>45646.67726851852</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45647</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>45647</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49452,7 +49452,7 @@
         <v>45647</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>45647</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>45035</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>45705.5654050926</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>44820</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45747.39719907408</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49799,7 +49799,7 @@
         <v>45628.49322916667</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49856,7 +49856,7 @@
         <v>44380</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>45188.62355324074</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49970,7 +49970,7 @@
         <v>44573</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50032,7 +50032,7 @@
         <v>44712.32885416667</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50089,7 +50089,7 @@
         <v>45033</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50146,7 +50146,7 @@
         <v>45483</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50203,7 +50203,7 @@
         <v>45749.53158564815</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>45168.33028935185</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50317,7 +50317,7 @@
         <v>44377</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50374,7 +50374,7 @@
         <v>44620.45334490741</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50431,7 +50431,7 @@
         <v>45714.80385416667</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>45012</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>44991.53373842593</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50602,7 +50602,7 @@
         <v>45762</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50659,7 +50659,7 @@
         <v>45567.37547453704</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45111</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>45621</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45267.46962962963</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50887,7 +50887,7 @@
         <v>44887</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>44938</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>45643.45525462963</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>44991.35916666667</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>45742.89054398148</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51172,7 +51172,7 @@
         <v>44991</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51229,7 +51229,7 @@
         <v>45761</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>44441</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45212</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>44974.57127314815</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>44959.62519675926</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>44959</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>44959</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45698</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>45055.49951388889</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45236.35502314815</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>44078</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45394.35633101852</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45735.46643518518</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>44565.57157407407</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>44565</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>44812</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>45169</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>44810</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>44810.49734953704</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>44448</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>45714.84204861111</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52436,7 +52436,7 @@
         <v>45188</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>45162.65574074074</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52555,7 +52555,7 @@
         <v>44924.66556712963</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52612,7 +52612,7 @@
         <v>45071.55216435185</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52669,7 +52669,7 @@
         <v>45071.55913194444</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52726,7 +52726,7 @@
         <v>45730.63616898148</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52783,7 +52783,7 @@
         <v>44158</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52845,7 +52845,7 @@
         <v>44903</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52902,7 +52902,7 @@
         <v>44657</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52959,7 +52959,7 @@
         <v>45079</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53016,7 +53016,7 @@
         <v>45076.30560185185</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53073,7 +53073,7 @@
         <v>45077</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>45758.72209490741</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>45758.73298611111</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>44852</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45068.66135416667</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45744.56912037037</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>45764.52859953704</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45218.47658564815</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>44151</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         <v>45260.32738425926</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>44565.61265046296</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45036.6734375</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>44806.59946759259</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>44886</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>44585</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>45620.82185185186</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>44126</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>45191.55503472222</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54109,7 +54109,7 @@
         <v>45070</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>44551.38699074074</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54223,7 +54223,7 @@
         <v>45594</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>45593</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54342,7 +54342,7 @@
         <v>44742.71030092592</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54399,7 +54399,7 @@
         <v>44809.39893518519</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54456,7 +54456,7 @@
         <v>45359.50601851852</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54513,7 +54513,7 @@
         <v>45366.32900462963</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54570,7 +54570,7 @@
         <v>45546.84695601852</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54632,7 +54632,7 @@
         <v>45546.84908564815</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54694,7 +54694,7 @@
         <v>44421.51063657407</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54751,7 +54751,7 @@
         <v>45054.85400462963</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54808,7 +54808,7 @@
         <v>45510</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54865,7 +54865,7 @@
         <v>44180</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54922,7 +54922,7 @@
         <v>45012</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54979,7 +54979,7 @@
         <v>44160</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55036,7 +55036,7 @@
         <v>45356.68475694444</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>44487</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55150,7 +55150,7 @@
         <v>45562.53543981481</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55212,7 +55212,7 @@
         <v>45546.85369212963</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55274,7 +55274,7 @@
         <v>45604.4971412037</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55331,7 +55331,7 @@
         <v>45593</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>45758.73520833333</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>44454</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55507,7 +55507,7 @@
         <v>44260</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         <v>44129</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55621,7 +55621,7 @@
         <v>45226.44923611111</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55678,7 +55678,7 @@
         <v>45629</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55735,7 +55735,7 @@
         <v>45202.38372685185</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>44923</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55849,7 +55849,7 @@
         <v>44846.55085648148</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55906,7 +55906,7 @@
         <v>45645</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55963,7 +55963,7 @@
         <v>45568.46310185185</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>44896.30818287037</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56077,7 +56077,7 @@
         <v>45097</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>45747.78493055556</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56191,7 +56191,7 @@
         <v>45097</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56248,7 +56248,7 @@
         <v>45764.48725694444</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56305,7 +56305,7 @@
         <v>44228</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56362,7 +56362,7 @@
         <v>45081</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56419,7 +56419,7 @@
         <v>44917</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>45093</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56533,7 +56533,7 @@
         <v>45099</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56590,7 +56590,7 @@
         <v>45305.57791666667</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56647,7 +56647,7 @@
         <v>45260</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56704,7 +56704,7 @@
         <v>45092.71057870371</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>45607.36863425926</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>45097</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45033</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45679.47949074074</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45686.60939814815</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>45470.64299768519</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57103,7 +57103,7 @@
         <v>45470.64894675926</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>45103</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>45595.4272337963</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45307</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57331,7 +57331,7 @@
         <v>44281</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57393,7 +57393,7 @@
         <v>45733.43582175926</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57450,7 +57450,7 @@
         <v>45733.44309027777</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45065</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>45733.57615740741</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57621,7 +57621,7 @@
         <v>45747.39269675926</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57683,7 +57683,7 @@
         <v>45747.39408564815</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57745,7 +57745,7 @@
         <v>45726.54469907407</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57802,7 +57802,7 @@
         <v>45121.35078703704</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57859,7 +57859,7 @@
         <v>44985</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>45757.94755787037</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57973,7 +57973,7 @@
         <v>45349</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>44978.59528935186</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>44960.36971064815</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>45396.86226851852</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58201,7 +58201,7 @@
         <v>44712</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58258,7 +58258,7 @@
         <v>44929</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58315,7 +58315,7 @@
         <v>45281.63481481482</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45639.58114583333</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58429,7 +58429,7 @@
         <v>45686.3184375</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58486,7 +58486,7 @@
         <v>45253.54356481481</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58543,7 +58543,7 @@
         <v>45754.52563657407</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58600,7 +58600,7 @@
         <v>45754.52998842593</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58657,7 +58657,7 @@
         <v>44881</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58714,7 +58714,7 @@
         <v>45275</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58776,7 +58776,7 @@
         <v>44991.34855324074</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58833,7 +58833,7 @@
         <v>44971.45475694445</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58890,7 +58890,7 @@
         <v>45594.62881944444</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58947,7 +58947,7 @@
         <v>45111</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59004,7 +59004,7 @@
         <v>45181</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59061,7 +59061,7 @@
         <v>45119.58694444445</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59118,7 +59118,7 @@
         <v>45602.91650462963</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59175,7 +59175,7 @@
         <v>44868.56361111111</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59232,7 +59232,7 @@
         <v>44882</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59289,7 +59289,7 @@
         <v>45188</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59346,7 +59346,7 @@
         <v>45463.39309027778</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59403,7 +59403,7 @@
         <v>45602.65810185186</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59460,7 +59460,7 @@
         <v>45672.591875</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59517,7 +59517,7 @@
         <v>45620.46207175926</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59574,7 +59574,7 @@
         <v>45551</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59636,7 +59636,7 @@
         <v>44883</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59693,7 +59693,7 @@
         <v>44820.47260416667</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59750,7 +59750,7 @@
         <v>45614.50907407407</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59812,7 +59812,7 @@
         <v>45068.45921296296</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59869,7 +59869,7 @@
         <v>45679.48483796296</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59926,7 +59926,7 @@
         <v>45401.69138888889</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59983,7 +59983,7 @@
         <v>45410</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60040,7 +60040,7 @@
         <v>45103.67451388889</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60097,7 +60097,7 @@
         <v>45162</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60154,7 +60154,7 @@
         <v>45170</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60211,7 +60211,7 @@
         <v>45211.63446759259</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60268,7 +60268,7 @@
         <v>45301</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60325,7 +60325,7 @@
         <v>45700.69467592592</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60382,7 +60382,7 @@
         <v>45065</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60439,7 +60439,7 @@
         <v>45121.70020833334</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60496,7 +60496,7 @@
         <v>45615.57574074074</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>45146.71684027778</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45632.51193287037</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45210</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60724,7 +60724,7 @@
         <v>45603</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60786,7 +60786,7 @@
         <v>45748.90723379629</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>45301.98247685185</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60900,7 +60900,7 @@
         <v>44881</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60957,7 +60957,7 @@
         <v>45181.56171296296</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61014,7 +61014,7 @@
         <v>45412</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61071,7 +61071,7 @@
         <v>45561.7159837963</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61128,7 +61128,7 @@
         <v>45755.48740740741</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>44993</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61242,7 +61242,7 @@
         <v>45097</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61299,7 +61299,7 @@
         <v>45709.64976851852</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61356,7 +61356,7 @@
         <v>45223</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61413,7 +61413,7 @@
         <v>45713</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61475,7 +61475,7 @@
         <v>45713.62074074074</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61537,7 +61537,7 @@
         <v>45250.44863425926</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61594,7 +61594,7 @@
         <v>44903.53118055555</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -61651,7 +61651,7 @@
         <v>45106.89616898148</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -61708,7 +61708,7 @@
         <v>45546</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -61765,7 +61765,7 @@
         <v>45355.4612037037</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61822,7 +61822,7 @@
         <v>45315.65375</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61879,7 +61879,7 @@
         <v>45339</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61936,7 +61936,7 @@
         <v>45656.78905092592</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -61993,7 +61993,7 @@
         <v>44466.48996527777</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>44971.69971064815</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62107,7 +62107,7 @@
         <v>45726.51144675926</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>44361.5662962963</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62221,7 +62221,7 @@
         <v>45634</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62278,7 +62278,7 @@
         <v>45610.36342592593</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62335,7 +62335,7 @@
         <v>45281.62631944445</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62392,7 +62392,7 @@
         <v>44587.40662037037</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62449,7 +62449,7 @@
         <v>45279</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62511,7 +62511,7 @@
         <v>45188.49987268518</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62568,7 +62568,7 @@
         <v>45274</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -62625,7 +62625,7 @@
         <v>45548.38636574074</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -62682,7 +62682,7 @@
         <v>45610.60157407408</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -62739,7 +62739,7 @@
         <v>45594.62287037037</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62796,7 +62796,7 @@
         <v>45594.6306712963</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62853,7 +62853,7 @@
         <v>45077.43420138889</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62910,7 +62910,7 @@
         <v>44376</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -62967,7 +62967,7 @@
         <v>45747</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63024,7 +63024,7 @@
         <v>45714.80880787037</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63081,7 +63081,7 @@
         <v>45075.53265046296</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63138,7 +63138,7 @@
         <v>45635.84936342593</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63195,7 +63195,7 @@
         <v>45637.54557870371</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63252,7 +63252,7 @@
         <v>45722.31061342593</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -63309,7 +63309,7 @@
         <v>45639</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -63366,7 +63366,7 @@
         <v>45156</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -567,7 +567,7 @@
         <v>45105</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44735</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>45568</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>45820</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>44216</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44343</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>45533</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45701.89549768518</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>45194</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>44258</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>45078</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>45224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45078</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45733.64422453703</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>45211</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>44610</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>45357</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44151</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44271.71099537037</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44448</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44679</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>44825.70888888889</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44524</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>44495</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44809.40431712963</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44582</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45476.50744212963</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>44645</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>45558.62674768519</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>45686.57611111111</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>45181</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44928</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>45274.32131944445</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45152.37778935185</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45282</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45819</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45896.9408912037</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>45905.39171296296</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>44232</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>45086</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>45005</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>45111</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>45527.45695601852</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45642.60756944444</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>45555.65903935185</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44985</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45372.69723379629</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>44461</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45749.46063657408</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>44082.65943287037</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44357.34326388889</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44231</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>44467.6135300926</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>44309.65885416666</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44571.63828703704</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>44431</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>44715.33956018519</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>44119</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44811.66311342592</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44186</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44568</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>44853.50333333333</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>44307.481875</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>44508.43092592592</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44622</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44272</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44134</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44152</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44271</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>44285.5874537037</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>44327.59131944444</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44357</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44245</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>44224</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44441</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44125.62782407407</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>44410</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44459</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44230</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44194</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>44297</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44510.88893518518</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44809.54884259259</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44461</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>44461.57160879629</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44607</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>44510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44721.65634259259</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>44818</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44848.3015625</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44125</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44297</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>44258</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44277.6141087963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44230</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44635.93181712963</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44503.73802083333</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44510.63989583333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>44386.6371412037</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44587.59076388889</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>44592.65864583333</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44742.95375</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44370.39163194445</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44650.495</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>44623.46204861111</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44714</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>44847</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>44847</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44084</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>44257.83641203704</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44292</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>44749</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44460</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>44186</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44441</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>44468</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44258</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44460</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44404</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44110</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44259</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44474</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44880.48260416667</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44837.42782407408</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44861</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44273.62519675926</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44245</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>44221</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>44140</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>44304</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>44482</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>44315</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44145</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>44476</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>44476.58800925926</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>44806.68451388889</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>44211</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>44502.34869212963</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>44461.69494212963</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>44267</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>44165</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>44459</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>44137.73322916667</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>44441</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>44515</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44495.68931712963</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44169</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>44715</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>44476</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44169</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>44130</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>44384.39226851852</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>44381</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44576</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>44229</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44426.34618055556</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44888.69445601852</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44322.68579861111</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>44175</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44187.74415509259</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>44825.35965277778</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>44460.62309027778</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>44147.70520833333</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44321.51725694445</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>44363</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>44203</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44229</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44817</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44764</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44537.63180555555</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44165</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44565.61417824074</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44806</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44739.3564699074</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44712.30428240741</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44809.39019675926</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44186</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44146</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>44369.93123842592</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44606</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44265</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44448.45023148148</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44448</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44127.46831018518</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>44357.34568287037</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44371</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>44806</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44820.47135416666</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>44420.65103009259</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44760.74060185185</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44810</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44173</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44742.71378472223</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44610.3157175926</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44417.77873842593</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>44084</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44732.43689814815</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>44446</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>44469</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>44277.60974537037</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44169</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>44515</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>44715.33355324074</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>44592.65989583333</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>44246</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>44187</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>44517</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>44595</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>44228</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44109</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>44204</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>44879.61497685185</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>44530</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44831</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>44237</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>44280</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>44295.77248842592</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>44469</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>44295</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44497.430625</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44550</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44882.66891203704</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44384.46910879629</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>44621.66707175926</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44495.69234953704</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>44536</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44209</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>45761</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>44810.40475694444</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44810.35575231481</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44538.40638888889</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>44588</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>45103.67451388889</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>45713</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>45218.47658564815</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>45684.34594907407</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>44152</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>44152</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>44845</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>44862.38081018518</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>44449</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>44882.6740162037</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>45714.84204861111</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>45748.59457175926</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>44421</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>45748.91101851852</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>45735.46643518518</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>45187</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>45775.59978009259</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>45775.60414351852</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>44881</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>44874</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45754.56905092593</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45620.46207175926</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>45639</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45639.58114583333</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>45735.46112268518</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45602</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>44985</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45698</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44999.50538194444</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44330.36730324074</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>45637</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45164</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         <v>44929</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>45614.50907407407</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>45629</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45775.87377314815</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>45534.67689814815</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>45775.87576388889</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45777.73621527778</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45005</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>45777.72737268519</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>44850</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45708.48537037037</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45281.62631944445</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>44886</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>44959</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45265.48799768519</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>44181</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>45783.71136574074</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>45782.33971064815</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>45179</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>45783.7002662037</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>45756.29621527778</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>45783.74034722222</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>45617.72069444445</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>44617</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>45021</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>45783.67510416666</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>45783.73440972222</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45188</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>44260</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>45783.72262731481</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45783.70811342593</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>45783.71869212963</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>45783.7308912037</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>45561.7159837963</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>44847.46701388889</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>45512.53300925926</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>44515</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>45345</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45784.74020833334</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>44883</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45708.4921412037</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>45111</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45110</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>44764</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45103</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>45401.69138888889</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>45628.46613425926</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45279</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45394.73528935185</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45097</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45773.44608796296</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>45161</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44852</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>45734.55042824074</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>45372.36653935185</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45637.54557870371</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44959.62519675926</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45610.42850694444</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45065</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>44900</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>44235</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45301.98575231482</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>44508</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>44825.46571759259</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45789.70107638889</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>45166.62002314815</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>45756.29003472222</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>45617.49510416666</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>45510.89385416666</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>45714.80106481481</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>45145.58085648148</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>44928.45686342593</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>44946.62486111111</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>45239</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>44881</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>44377</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>45068.66135416667</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45643.45525462963</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>44823.61398148148</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45359.50601851852</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>45681.62265046296</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>45600</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45551</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>44974.57127314815</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45026</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>45054.85400462963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>44742.71030092592</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45610</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>44160</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45236</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>45749.56019675926</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>45510</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>45628.56518518519</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>44974</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>44634</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>44587.40662037037</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>45315.65311342593</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>44959.68709490741</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>44959</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45720.31155092592</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>45099</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>45099.91826388889</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>45720.3175462963</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45747.78081018518</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23303,7 +23303,7 @@
         <v>45747.39719907408</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45792.30664351852</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>45792.32596064815</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>45793.56537037037</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>45719</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>45593</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>44858.63208333333</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45036.6734375</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>45441</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45593</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45615.6362037037</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45483</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45483</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>45181.56171296296</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>44852.89560185185</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>44421.51063657407</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>44917</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45483</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44151</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>44634</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45628.44303240741</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45792.33170138889</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>44435.41690972223</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>45272</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>45181</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45596.57131944445</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>44927.74953703704</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45226.44923611111</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45390</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44551.38699074074</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>45267.46962962963</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>45796.56827546296</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>45796.60440972223</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>45672.58387731481</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>45396.86226851852</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>45796.55706018519</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>45796.56221064815</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45223</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>45797</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>44882</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45204.32359953703</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>44971.69971064815</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>44750</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>44923</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>45730.63616898148</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>44186</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
         <v>45734.57873842592</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>45596.44083333333</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>45700.69467592592</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>44851.61237268519</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45707.66030092593</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>45279</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>45084.51329861111</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>45701.60341435186</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>45796.58149305556</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>45475</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>45796.36819444445</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>45796.38582175926</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>45796.38944444444</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         <v>45121.70020833334</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>45188</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45056.31962962963</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45188.4716550926</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>44380</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>44380</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>45103</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45461</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>45621</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45747.39269675926</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27316,7 +27316,7 @@
         <v>45747.39408564815</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>45278.88578703703</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>44706</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>45145.57798611111</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>45163.37561342592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45644.02509259259</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45799.40628472222</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>45638</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45470.64299768519</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         <v>45470.64894675926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44817</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>44384.39820601852</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>45798.50189814815</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28067,7 +28067,7 @@
         <v>45712.57320601852</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>45079</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45604.54047453704</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28238,7 +28238,7 @@
         <v>44802</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>45709.64976851852</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>44146</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>45240.67206018518</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>45275.30907407407</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28523,7 +28523,7 @@
         <v>45744.56912037037</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         <v>44251</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>45183.65436342593</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>45441</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45562.55799768519</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>44140</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28875,7 +28875,7 @@
         <v>45593</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         <v>44825.46825231481</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45272</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>44376</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45156</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45106.89616898148</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45510</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>45769.33756944445</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>45119.63947916667</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>45253</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29455,7 +29455,7 @@
         <v>45274.57935185185</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29512,7 +29512,7 @@
         <v>45446</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45645.58603009259</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>45273</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>45274</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>45081</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>45724</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>45162.65574074074</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>44126</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>45463</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>45804.6612962963</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45749.56623842593</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>44860.93721064815</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>45246</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45205</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>45805.31606481481</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>45805.27396990741</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>45805.27778935185</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30501,7 +30501,7 @@
         <v>45748.86240740741</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30558,7 +30558,7 @@
         <v>45804.66229166667</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>45804</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>45805.27659722222</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>45055.49951388889</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45349.39254629629</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45216.52173611111</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>45739.84453703704</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45686.60939814815</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>44915</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>45260.32738425926</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45610.61537037037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>45183.65034722222</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>45811.55042824074</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31304,7 +31304,7 @@
         <v>45811.56310185185</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>45686.54246527778</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>45686.60648148148</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>45686.63332175926</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>45509.66609953704</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>45726.51144675926</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>44361.5662962963</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>45281.63481481482</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>45811.39115740741</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>45811.39695601852</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>45811.40674768519</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>45593</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>45168.33028935185</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>45811.48321759259</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>45350.91678240741</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>45350.91932870371</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>45546.84695601852</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45811.56517361111</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>45614.50349537037</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         <v>45614.505625</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>45202.38372685185</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>45126</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45012</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>45092.71057870371</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32697,7 +32697,7 @@
         <v>44158</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45371.85761574074</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>44573</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44928</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>45146.71684027778</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>44551</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>45620.82185185186</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>45656.78905092592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>45812.59082175926</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45236.35502314815</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>44960.36971064815</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>44582.42422453704</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>45188.49305555555</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>45005</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>45817.39133101852</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>44938</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33619,7 +33619,7 @@
         <v>44908</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>44946.42413194444</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45686.51583333333</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45817.39481481481</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>45817</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>45215.7849074074</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>45482</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>45357</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>44712</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45762.60217592592</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>45518</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>45217.3809837963</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45686.3184375</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>45818.66446759259</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>45818</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>45818.66649305556</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34536,7 +34536,7 @@
         <v>45617.54989583333</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>45567.37547453704</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>45567</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45561.88243055555</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>45305.57791666667</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>45567.33017361111</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>45162</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>45618.61243055556</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>45820</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>45824.61681712963</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>45562.53543981481</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45509</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>44908</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>45676.57688657408</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>45825.65555555555</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35411,7 +35411,7 @@
         <v>45824.55555555555</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>45824.61572916667</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45826</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>44886</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>45211.63712962963</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>45826</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>45826.47586805555</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45793.65984953703</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>45826.41267361111</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>45869</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45831.36892361111</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45831.3978587963</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>45831.56630787037</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>45831.36045138889</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36219,7 +36219,7 @@
         <v>45831.3783912037</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>45317</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>45831.34712962963</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>45869</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>45831</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>45831</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36566,7 +36566,7 @@
         <v>45831.35077546296</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>45831.57793981482</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36680,7 +36680,7 @@
         <v>45869</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>45869</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>45875.64696759259</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36861,7 +36861,7 @@
         <v>45833.73708333333</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36918,7 +36918,7 @@
         <v>45832.28081018518</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>45247.46569444444</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37032,7 +37032,7 @@
         <v>45602.91650462963</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37089,7 +37089,7 @@
         <v>45874.65034722222</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
         <v>45677.37925925926</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37203,7 +37203,7 @@
         <v>45833.74201388889</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>45877.42953703704</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37317,7 +37317,7 @@
         <v>45875.6449537037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37374,7 +37374,7 @@
         <v>45875.45658564815</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>45394.35633101852</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37488,7 +37488,7 @@
         <v>44810.52567129629</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37545,7 +37545,7 @@
         <v>44908</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>44160</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>45876.62177083334</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37721,7 +37721,7 @@
         <v>45835.40136574074</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>45835.39804398148</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>45880.56395833333</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>45881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>45881.66684027778</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>45838.66364583333</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>45568.46310185185</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38120,7 +38120,7 @@
         <v>45880</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>45881.31761574074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38234,7 +38234,7 @@
         <v>45837.87837962963</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38291,7 +38291,7 @@
         <v>45837.90292824074</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>45837.90488425926</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38405,7 +38405,7 @@
         <v>45880.86574074074</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>45838.65454861111</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>45837.91177083334</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>45079</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>45840.5487037037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>45264.68416666667</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>45412</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38804,7 +38804,7 @@
         <v>45840.55074074074</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38861,7 +38861,7 @@
         <v>45841.57072916667</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>45097</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>45701.59954861111</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>44978.59528935186</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>45845</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>45845</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>45842.62019675926</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39260,7 +39260,7 @@
         <v>45842.62362268518</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>44144</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>45842.45201388889</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>44266</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39488,7 +39488,7 @@
         <v>45884.73457175926</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>44174</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39607,7 +39607,7 @@
         <v>45845.48228009259</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>45845.48898148148</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39721,7 +39721,7 @@
         <v>45723.54547453704</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39778,7 +39778,7 @@
         <v>45811.48709490741</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39835,7 +39835,7 @@
         <v>45884.62045138889</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45775.40460648148</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>45888.34261574074</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40006,7 +40006,7 @@
         <v>45888.58818287037</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40063,7 +40063,7 @@
         <v>45847</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40120,7 +40120,7 @@
         <v>45847.3721412037</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40177,7 +40177,7 @@
         <v>45730.61275462963</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40234,7 +40234,7 @@
         <v>45119</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40291,7 +40291,7 @@
         <v>45847.67734953704</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40348,7 +40348,7 @@
         <v>45847.67871527778</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>44809</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45889.93328703703</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45848.61030092592</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40576,7 +40576,7 @@
         <v>45891.65096064815</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40633,7 +40633,7 @@
         <v>45890.37820601852</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>45848.6062962963</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>45895.41074074074</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45811.4892824074</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>45891.64818287037</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>45891.65295138889</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45852.75837962963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>45148.62439814815</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41094,7 +41094,7 @@
         <v>45895</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45895</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>45852.33880787037</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>45893.60962962963</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>45895.41686342593</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>44454</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>45895.35368055556</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>45895</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41560,7 +41560,7 @@
         <v>45895</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>45895</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>45895.41521990741</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>45838.65708333333</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>45895.57550925926</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41855,7 +41855,7 @@
         <v>45896.94550925926</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41912,7 +41912,7 @@
         <v>45895.55729166666</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>45897.61160879629</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42026,7 +42026,7 @@
         <v>45667.4771412037</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42083,7 +42083,7 @@
         <v>44945.35765046296</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42140,7 +42140,7 @@
         <v>45594.62881944444</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
         <v>45109</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42254,7 +42254,7 @@
         <v>45684.34170138889</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42311,7 +42311,7 @@
         <v>45684.34384259259</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42368,7 +42368,7 @@
         <v>45757.94755787037</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42425,7 +42425,7 @@
         <v>45898.49733796297</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>45530.69050925926</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42539,7 +42539,7 @@
         <v>45811.57001157408</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>45702.6033912037</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42653,7 +42653,7 @@
         <v>45470</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42710,7 +42710,7 @@
         <v>45126</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>45903.51604166667</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42824,7 +42824,7 @@
         <v>45205.39787037037</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>45205</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42958,7 +42958,7 @@
         <v>45747.39516203704</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>45902.60481481482</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45280</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45860</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43196,7 +43196,7 @@
         <v>45902.3184375</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43253,7 +43253,7 @@
         <v>45084.67444444444</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>45722.31061342593</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>45902.66104166667</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>45902.6025</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43481,7 +43481,7 @@
         <v>45188</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>44603.63212962963</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>44603</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>44603.6434375</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43709,7 +43709,7 @@
         <v>45483</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43766,7 +43766,7 @@
         <v>45888</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43823,7 +43823,7 @@
         <v>45684.45225694445</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43885,7 +43885,7 @@
         <v>44181</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43942,7 +43942,7 @@
         <v>45754.52563657407</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43999,7 +43999,7 @@
         <v>45754.52998842593</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44056,7 +44056,7 @@
         <v>45610.60369212963</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>44806.59946759259</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45212</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44227,7 +44227,7 @@
         <v>45646.67438657407</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44284,7 +44284,7 @@
         <v>45191.55503472222</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>45126</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45271</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44512,7 +44512,7 @@
         <v>45905.50523148148</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45905.45804398148</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45642.57581018518</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45359.49635416667</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>44993</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44797,7 +44797,7 @@
         <v>45645.40951388889</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44854,7 +44854,7 @@
         <v>45510</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44911,7 +44911,7 @@
         <v>45372.7019212963</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44968,7 +44968,7 @@
         <v>45707.64956018519</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45707.66369212963</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>45162.588125</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>44446</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>45121.35078703704</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45253,7 +45253,7 @@
         <v>45358</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45310,7 +45310,7 @@
         <v>45343.92605324074</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45367,7 +45367,7 @@
         <v>44743.61965277778</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45424,7 +45424,7 @@
         <v>44991.53373842593</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45481,7 +45481,7 @@
         <v>45334</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45543,7 +45543,7 @@
         <v>45212</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>45035</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
         <v>45614.44239583334</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>45629</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45771,7 +45771,7 @@
         <v>45525</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45225.63304398148</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45885,7 +45885,7 @@
         <v>45225.63777777777</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>44851.60855324074</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45301</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>45527.44498842592</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>45715.56667824074</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>44810.49734953704</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45280</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>45257.57825231482</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46403,7 +46403,7 @@
         <v>44988</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46460,7 +46460,7 @@
         <v>45705.65206018519</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46517,7 +46517,7 @@
         <v>45119.58694444445</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46574,7 +46574,7 @@
         <v>45089</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>45356.68585648148</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46688,7 +46688,7 @@
         <v>45012</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46745,7 +46745,7 @@
         <v>45645.58436342593</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>44124.48305555555</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>45712</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>44894.63579861111</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45093</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47030,7 +47030,7 @@
         <v>45769.36023148148</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47087,7 +47087,7 @@
         <v>45323</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47149,7 +47149,7 @@
         <v>45373.59099537037</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45260</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>45754.38893518518</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45754.57372685185</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45646.67726851852</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>45632.51193287037</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45647</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>45647</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45647</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>45647</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>45339.66177083334</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47776,7 +47776,7 @@
         <v>45481.49108796296</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47833,7 +47833,7 @@
         <v>45617.68131944445</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47890,7 +47890,7 @@
         <v>45328</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47947,7 +47947,7 @@
         <v>44924.66556712963</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48004,7 +48004,7 @@
         <v>45197</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48061,7 +48061,7 @@
         <v>44923</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48118,7 +48118,7 @@
         <v>45645</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48175,7 +48175,7 @@
         <v>45700.51605324074</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48232,7 +48232,7 @@
         <v>44441</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48289,7 +48289,7 @@
         <v>44487</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48346,7 +48346,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>45604.4971412037</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>44903.53118055555</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>45243</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>45647</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>45647</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>44670.43472222222</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45530</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48802,7 +48802,7 @@
         <v>45137.90618055555</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48859,7 +48859,7 @@
         <v>45621</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48916,7 +48916,7 @@
         <v>45126</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48973,7 +48973,7 @@
         <v>45253.54356481481</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49030,7 +49030,7 @@
         <v>44810.56070601852</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49087,7 +49087,7 @@
         <v>44923.65486111111</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49144,7 +49144,7 @@
         <v>45567</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49201,7 +49201,7 @@
         <v>45187.48282407408</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>45167.68207175926</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49315,7 +49315,7 @@
         <v>45076.30560185185</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49372,7 +49372,7 @@
         <v>45470</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49429,7 +49429,7 @@
         <v>44090</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49486,7 +49486,7 @@
         <v>44180</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49543,7 +49543,7 @@
         <v>45524.49138888889</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49600,7 +49600,7 @@
         <v>45246.77350694445</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49657,7 +49657,7 @@
         <v>44740.92936342592</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49714,7 +49714,7 @@
         <v>45272</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49771,7 +49771,7 @@
         <v>45440.4658449074</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49828,7 +49828,7 @@
         <v>45758.72209490741</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49885,7 +49885,7 @@
         <v>45758.73298611111</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49942,7 +49942,7 @@
         <v>44337.48540509259</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49999,7 +49999,7 @@
         <v>44424</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50056,7 +50056,7 @@
         <v>45207.49881944444</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>45077</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50170,7 +50170,7 @@
         <v>45099</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>44628.47715277778</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>45069.48967592593</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50341,7 +50341,7 @@
         <v>45119.57798611111</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45646</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50455,7 +50455,7 @@
         <v>44357.34482638889</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>45033</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>44988.85038194444</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>44656.61335648148</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>45085.93778935185</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>45355.4612037037</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50797,7 +50797,7 @@
         <v>45645.58762731482</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         <v>44160</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50911,7 +50911,7 @@
         <v>44887</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50968,7 +50968,7 @@
         <v>44991.34855324074</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51025,7 +51025,7 @@
         <v>45593</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51087,7 +51087,7 @@
         <v>44868.56361111111</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51144,7 +51144,7 @@
         <v>45188.49987268518</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51201,7 +51201,7 @@
         <v>45126</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51258,7 +51258,7 @@
         <v>44565.57157407407</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51315,7 +51315,7 @@
         <v>45188.61378472222</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51372,7 +51372,7 @@
         <v>45162.32709490741</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51429,7 +51429,7 @@
         <v>45546</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51486,7 +51486,7 @@
         <v>44908</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51548,7 +51548,7 @@
         <v>44896.30818287037</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51605,7 +51605,7 @@
         <v>44651</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45370.34275462963</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51719,7 +51719,7 @@
         <v>45215.48378472222</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>45546.85369212963</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>45755.48740740741</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45323</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51957,7 +51957,7 @@
         <v>44180</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52014,7 +52014,7 @@
         <v>45715.5681712963</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>45734.93418981481</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52128,7 +52128,7 @@
         <v>45634</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52185,7 +52185,7 @@
         <v>44585</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52242,7 +52242,7 @@
         <v>45012</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52299,7 +52299,7 @@
         <v>44999.50461805556</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52356,7 +52356,7 @@
         <v>45727.34787037037</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52413,7 +52413,7 @@
         <v>44098</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52470,7 +52470,7 @@
         <v>45181.58791666666</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52527,7 +52527,7 @@
         <v>44812</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>45635.84936342593</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52641,7 +52641,7 @@
         <v>45647</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>45205</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>45742.89054398148</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52812,7 +52812,7 @@
         <v>44991.35916666667</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52869,7 +52869,7 @@
         <v>44991</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52926,7 +52926,7 @@
         <v>45366.32900462963</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52983,7 +52983,7 @@
         <v>45069.64322916666</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53040,7 +53040,7 @@
         <v>44980.62431712963</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53097,7 +53097,7 @@
         <v>45764.48725694444</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53154,7 +53154,7 @@
         <v>45748.90723379629</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53211,7 +53211,7 @@
         <v>45195.85546296297</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53268,7 +53268,7 @@
         <v>44810</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53325,7 +53325,7 @@
         <v>45231</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53382,7 +53382,7 @@
         <v>45035</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53439,7 +53439,7 @@
         <v>45077.43420138889</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53496,7 +53496,7 @@
         <v>44809.39893518519</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53553,7 +53553,7 @@
         <v>45070</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53610,7 +53610,7 @@
         <v>44945.34497685185</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53667,7 +53667,7 @@
         <v>44634.60929398148</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53724,7 +53724,7 @@
         <v>45231</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53781,7 +53781,7 @@
         <v>45594.62287037037</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53838,7 +53838,7 @@
         <v>45594.6306712963</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53895,7 +53895,7 @@
         <v>44991.51193287037</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53952,7 +53952,7 @@
         <v>44991</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54009,7 +54009,7 @@
         <v>45679.48483796296</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54066,7 +54066,7 @@
         <v>44187</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54123,7 +54123,7 @@
         <v>44959</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54180,7 +54180,7 @@
         <v>44959</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54237,7 +54237,7 @@
         <v>45187.59305555555</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54294,7 +54294,7 @@
         <v>45176</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>45181</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54413,7 +54413,7 @@
         <v>45714.80385416667</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54470,7 +54470,7 @@
         <v>44523.46746527778</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
         <v>44721.70876157407</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>45168.33265046297</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45410</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54698,7 +54698,7 @@
         <v>45224.70244212963</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54755,7 +54755,7 @@
         <v>45097</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54812,7 +54812,7 @@
         <v>44129</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45300</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45210</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>44573</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55045,7 +55045,7 @@
         <v>45463.39309027778</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55102,7 +55102,7 @@
         <v>44903</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55159,7 +55159,7 @@
         <v>45614.63012731481</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         <v>45065</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>45672.46096064815</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>44894.45888888889</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55392,7 +55392,7 @@
         <v>45775.58704861111</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55449,7 +55449,7 @@
         <v>45224.59289351852</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         <v>45607.36863425926</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55563,7 +55563,7 @@
         <v>45075.53265046296</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         <v>44104</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55677,7 +55677,7 @@
         <v>45223</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         <v>45223</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55791,7 +55791,7 @@
         <v>45715</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         <v>45071.55216435185</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         <v>45071.55913194444</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55962,7 +55962,7 @@
         <v>44820</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56019,7 +56019,7 @@
         <v>45727</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56076,7 +56076,7 @@
         <v>45211.63446759259</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>44642.83407407408</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56190,7 +56190,7 @@
         <v>45679.47949074074</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>45476.50119212963</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>45476.50480324074</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         <v>45726.54469907407</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56418,7 +56418,7 @@
         <v>45111</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56475,7 +56475,7 @@
         <v>44846.55085648148</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56532,7 +56532,7 @@
         <v>45301.83475694444</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56589,7 +56589,7 @@
         <v>44712.32885416667</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56646,7 +56646,7 @@
         <v>45772.59259259259</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         <v>44848.30996527777</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56760,7 +56760,7 @@
         <v>45195.85668981481</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56817,7 +56817,7 @@
         <v>45089</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56874,7 +56874,7 @@
         <v>44565</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56931,7 +56931,7 @@
         <v>44565.61265046296</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56988,7 +56988,7 @@
         <v>45236.68318287037</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57045,7 +57045,7 @@
         <v>45071.54651620371</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57102,7 +57102,7 @@
         <v>45071.54908564815</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57159,7 +57159,7 @@
         <v>45730.6487037037</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57216,7 +57216,7 @@
         <v>45068.45921296296</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57273,7 +57273,7 @@
         <v>44448</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57335,7 +57335,7 @@
         <v>45315.65375</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57392,7 +57392,7 @@
         <v>45705.5654050926</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57449,7 +57449,7 @@
         <v>45701.90762731482</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57506,7 +57506,7 @@
         <v>45628.48590277778</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57563,7 +57563,7 @@
         <v>44272</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57620,7 +57620,7 @@
         <v>45061</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57677,7 +57677,7 @@
         <v>45581.49583333333</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57734,7 +57734,7 @@
         <v>44228</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57791,7 +57791,7 @@
         <v>45672.591875</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57848,7 +57848,7 @@
         <v>45372.68917824074</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57905,7 +57905,7 @@
         <v>45250.44863425926</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57962,7 +57962,7 @@
         <v>45615.57574074074</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58019,7 +58019,7 @@
         <v>44819.34596064815</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58076,7 +58076,7 @@
         <v>45470</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58133,7 +58133,7 @@
         <v>45594.61994212963</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58190,7 +58190,7 @@
         <v>45020</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58252,7 +58252,7 @@
         <v>45152</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58309,7 +58309,7 @@
         <v>45334</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58366,7 +58366,7 @@
         <v>45097</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58423,7 +58423,7 @@
         <v>45750.94241898148</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58480,7 +58480,7 @@
         <v>45602.65810185186</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58537,7 +58537,7 @@
         <v>45339</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58594,7 +58594,7 @@
         <v>45131</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58651,7 +58651,7 @@
         <v>45097</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58708,7 +58708,7 @@
         <v>45742.36822916667</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58765,7 +58765,7 @@
         <v>45169</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58822,7 +58822,7 @@
         <v>45614.49559027778</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58884,7 +58884,7 @@
         <v>45275</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         <v>45595.4272337963</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         <v>45359.50059027778</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>44867</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         <v>45441</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59174,7 +59174,7 @@
         <v>45427</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59231,7 +59231,7 @@
         <v>45131</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>45713</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59350,7 +59350,7 @@
         <v>45713.62074074074</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59412,7 +59412,7 @@
         <v>45672.78414351852</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59469,7 +59469,7 @@
         <v>45615.57407407407</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59526,7 +59526,7 @@
         <v>45033</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59583,7 +59583,7 @@
         <v>45307</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59640,7 +59640,7 @@
         <v>45225.49447916666</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59697,7 +59697,7 @@
         <v>45116.79090277778</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59754,7 +59754,7 @@
         <v>45116.79268518519</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59811,7 +59811,7 @@
         <v>45610.36342592593</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59868,7 +59868,7 @@
         <v>45156</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59925,7 +59925,7 @@
         <v>45218.86829861111</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59982,7 +59982,7 @@
         <v>45764.48869212963</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60039,7 +60039,7 @@
         <v>45749.53158564815</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60096,7 +60096,7 @@
         <v>44971.45475694445</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60153,7 +60153,7 @@
         <v>45714.80880787037</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60210,7 +60210,7 @@
         <v>45754.52788194444</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60267,7 +60267,7 @@
         <v>45747.78493055556</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60324,7 +60324,7 @@
         <v>45747.79938657407</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60381,7 +60381,7 @@
         <v>45349</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60438,7 +60438,7 @@
         <v>44466.48996527777</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
         <v>44886.51197916667</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60552,7 +60552,7 @@
         <v>44937.71841435185</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60609,7 +60609,7 @@
         <v>45758.73520833333</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60666,7 +60666,7 @@
         <v>45629</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60723,7 +60723,7 @@
         <v>45610.59956018518</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60780,7 +60780,7 @@
         <v>45610.60157407408</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60837,7 +60837,7 @@
         <v>44620.45334490741</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60894,7 +60894,7 @@
         <v>45604.47508101852</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60951,7 +60951,7 @@
         <v>45226.43175925926</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61008,7 +61008,7 @@
         <v>45628.49322916667</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61065,7 +61065,7 @@
         <v>45483</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61122,7 +61122,7 @@
         <v>45188.62355324074</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61179,7 +61179,7 @@
         <v>45603</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>45306</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61298,7 +61298,7 @@
         <v>45548.38636574074</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61355,7 +61355,7 @@
         <v>44985</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>44985</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61469,7 +61469,7 @@
         <v>44281</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61531,7 +61531,7 @@
         <v>45679.49804398148</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>44995.44344907408</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61645,7 +61645,7 @@
         <v>45562</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -61702,7 +61702,7 @@
         <v>45594</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -61759,7 +61759,7 @@
         <v>45425.69540509259</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -61816,7 +61816,7 @@
         <v>45301.98247685185</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61873,7 +61873,7 @@
         <v>45170</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45762</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61987,7 +61987,7 @@
         <v>45742.61196759259</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62044,7 +62044,7 @@
         <v>45272.62565972222</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62101,7 +62101,7 @@
         <v>45741.47434027777</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62158,7 +62158,7 @@
         <v>45272</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62215,7 +62215,7 @@
         <v>45324.71243055556</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62272,7 +62272,7 @@
         <v>45713</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62334,7 +62334,7 @@
         <v>45735.45677083333</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62391,7 +62391,7 @@
         <v>45533</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62453,7 +62453,7 @@
         <v>45733.43582175926</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62510,7 +62510,7 @@
         <v>45733.44309027777</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62567,7 +62567,7 @@
         <v>45733.60265046296</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62624,7 +62624,7 @@
         <v>44924</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -62681,7 +62681,7 @@
         <v>45266</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -62738,7 +62738,7 @@
         <v>45510.89869212963</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -62795,7 +62795,7 @@
         <v>45628.43445601852</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62852,7 +62852,7 @@
         <v>44657</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62909,7 +62909,7 @@
         <v>45301.98100694444</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62966,7 +62966,7 @@
         <v>44820.47260416667</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63023,7 +63023,7 @@
         <v>45764.52859953704</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63080,7 +63080,7 @@
         <v>45181</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63137,7 +63137,7 @@
         <v>45097</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63194,7 +63194,7 @@
         <v>45356.68475694444</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63251,7 +63251,7 @@
         <v>45264.68074074074</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63308,7 +63308,7 @@
         <v>44895</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -63365,7 +63365,7 @@
         <v>44895</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -63422,7 +63422,7 @@
         <v>44895.58759259259</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -63479,7 +63479,7 @@
         <v>45630.32984953704</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -63536,7 +63536,7 @@
         <v>45546.84908564815</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -63598,7 +63598,7 @@
         <v>45048</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -567,7 +567,7 @@
         <v>45105</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44735</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>45568</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>45820</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>44216</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44343</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>45533</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45733.64422453703</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>44610</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45211</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>45357</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>45224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>44258</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45078</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>45194</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>45078</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>45701.89549768518</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44151</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44271.71099537037</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44448</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44679</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>44825.70888888889</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44524</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>44495</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44809.40431712963</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44582</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45372.69723379629</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45558.62674768519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>45527.45695601852</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>45686.57611111111</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44985</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>45476.50744212963</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>45642.60756944444</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>44928</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45555.65903935185</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45819</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>44645</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45274.32131944445</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>45152.37778935185</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>45111</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45086</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>45282</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>45896.9408912037</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>44232</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45905.39171296296</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>45181</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>44461</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>45005</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45749.46063657408</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>44357.34326388889</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44231</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44431</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>44715.33956018519</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>44119</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>44571.63828703704</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>44186</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>44467.6135300926</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>44309.65885416666</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44811.66311342592</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44568</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44853.50333333333</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>44307.481875</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>44508.43092592592</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>44272</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44152</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44134</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44271</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44285.5874537037</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44327.59131944444</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>44622</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>44357</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44224</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44245</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>44441</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44230</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44410</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>44125.62782407407</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44459</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44194</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44297</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>44510.88893518518</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44461</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44461.57160879629</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44607</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>44809.54884259259</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44721.65634259259</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>44510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44818</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>44848.3015625</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44125</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44297</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44277.6141087963</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>44230</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44258</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44635.93181712963</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44510.63989583333</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44503.73802083333</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44386.6371412037</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>44587.59076388889</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44742.95375</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>44592.65864583333</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44370.39163194445</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44650.495</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44623.46204861111</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>44714</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44847</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>44847</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>44257.83641203704</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44292</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>44749</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44186</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>44468</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44460</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>44441</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44404</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>44259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44460</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44110</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44258</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44474</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44880.48260416667</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44837.42782407408</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44861</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44273.62519675926</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44245</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44221</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44140</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>44304</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>44482</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>44315</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>44806.68451388889</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>44476</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>44476.58800925926</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44145</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44211</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>44502.34869212963</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>44461.69494212963</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>44267</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>44165</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>44137.73322916667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>44459</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>44441</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>44515</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>44495.68931712963</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>44169</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44715</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44476</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>44169</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>44130</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44384.39226851852</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>44381</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>44576</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>44229</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44426.34618055556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>44888.69445601852</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44882.66891203704</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44322.68579861111</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44363</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>44825.35965277778</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44460.62309027778</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>44147.70520833333</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>44764</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>44806</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44712.30428240741</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>44809.39019675926</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>44165</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44175</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44606</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44739.3564699074</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44187.74415509259</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44146</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44369.93123842592</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44565.61417824074</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44321.51725694445</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44610.3157175926</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44446</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44186</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44203</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>44265</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44448.45023148148</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44448</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44229</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44817</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44357.34568287037</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>44371</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44127.46831018518</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>44420.65103009259</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44715.33355324074</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>44537.63180555555</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44742.71378472223</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44760.74060185185</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44806</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44169</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44515</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44109</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>44592.65989583333</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>44732.43689814815</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>44187</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>44204</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>44469</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>44820.47135416666</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>44517</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>44595</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>44469</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>44228</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>44810</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>44879.61497685185</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>44497.430625</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>44831</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44550</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>44173</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>44536</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>44295</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44810.40475694444</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>44621.66707175926</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>44495.69234953704</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>44810.35575231481</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>44538.40638888889</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>44209</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>45724</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44417.77873842593</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44235</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45773.44608796296</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>44152</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44588</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>44991.51193287037</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44991</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44809</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45272</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44277.60974537037</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>45684.34170138889</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>45684.34384259259</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>45048</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45713</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45069.48967592593</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>44152</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>45187.48282407408</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>44845</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>45187</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>44862.38081018518</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>44900</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>44867</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>44819.34596064815</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>45735.45677083333</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>44421</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>44908</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>44908</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>45334</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>44764</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>44825.46571759259</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>45324.71243055556</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45089</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45085.93778935185</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>45715</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45440.4658449074</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>45247.46569444444</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45441</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45164</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>44974</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         <v>45126</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>44924</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45702.6033912037</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45764.48869212963</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>44928</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>44246</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>44508</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>45679.49804398148</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44446</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>45707.64956018519</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>45707.66369212963</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45035</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17625,7 +17625,7 @@
         <v>44357.34482638889</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17682,7 +17682,7 @@
         <v>45272.62565972222</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>45749.56019675926</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>45730.6487037037</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>45441</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>45126</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>45183.65436342593</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45223</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45223</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>45614.505625</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>45747.79938657407</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>44424</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>45646</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>45181.58791666666</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>45343.92605324074</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>44810.56070601852</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>45300</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>44810.52567129629</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45775.87377314815</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>45629</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45239</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45272</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>45534.67689814815</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>45373.59099537037</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>44895</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>44895</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45775.87576388889</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>44895.58759259259</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45061</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45708.48537037037</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45777.73621527778</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45777.72737268519</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>44959</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>44090</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45782.33971064815</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>44181</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45470</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45750.94241898148</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>45097</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45197</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>45783.7002662037</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>45783.70811342593</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>45783.71136574074</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>45783.71869212963</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45783.7308912037</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>45783.72262731481</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>45463</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>45161</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45021</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45126</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>44551</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45783.73440972222</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45783.74034722222</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45784.74020833334</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>45119.63947916667</v>
       </c>
       <c r="C328" s="1" t="n">